--- a/frontend/public/data/daily_2026_5.xlsx
+++ b/frontend/public/data/daily_2026_5.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026年5月_日次データ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商品別" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,6 +43,11 @@
     <font>
       <b val="1"/>
       <color rgb="0000F5A0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF9F1C"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -94,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -128,6 +134,16 @@
     </xf>
     <xf numFmtId="3" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2845,4 +2861,4506 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L96"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="12" t="n"/>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>FOOD</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>DRINK</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>日付</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>曜日</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>順位</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>F商品名</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>F単価</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>F数量</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>F金額</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>D商品名</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>D単価</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>D数量</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>D金額</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/01</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>1位</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>宴会コース</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>48000</v>
+      </c>
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>プレミアムモルツ生</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="n">
+        <v>880</v>
+      </c>
+      <c r="K3" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="L3" s="10" t="n">
+        <v>14960</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/01</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>2位</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>あさり膳ハーフ</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>37500</v>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>赤霧島ボトル</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>7500</v>
+      </c>
+      <c r="K4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="10" t="n">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/01</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>3位</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>和牛ヒレ</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>11000</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>22000</v>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>角ハイボール</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="n">
+        <v>680</v>
+      </c>
+      <c r="K5" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L5" s="10" t="n">
+        <v>4760</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/02</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>1位</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>宴会コース</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>72000</v>
+      </c>
+      <c r="I6" s="15" t="inlineStr">
+        <is>
+          <t>プレミアムモルツ生</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>880</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="L6" s="6" t="n">
+        <v>10560</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/02</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>2位</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>あさり膳ハーフ</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="I7" s="15" t="inlineStr">
+        <is>
+          <t>プレミアムモルツ中瓶</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>980</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>8820</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/02</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>3位</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>宝家膳</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>ウーロン茶</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>400</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="L8" s="6" t="n">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/03</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>1位</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>あさり膳ハーフ</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>63</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>157500</v>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>山崎ボトル</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>29800</v>
+      </c>
+      <c r="K9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="10" t="n">
+        <v>29800</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/03</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>2位</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>宴会コース</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>60000</v>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>プレミアムモルツ生</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>880</v>
+      </c>
+      <c r="K10" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="L10" s="10" t="n">
+        <v>20240</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/03</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>3位</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>あさり膳ハーフ夜</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>3500</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>49000</v>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>オールフリー</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>680</v>
+      </c>
+      <c r="K11" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="L11" s="10" t="n">
+        <v>10200</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/04</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>1位</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>あさり膳ハーフ</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>65000</v>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>プレミアムモルツ生</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>880</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="L12" s="6" t="n">
+        <v>24640</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/04</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>2位</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>あさり膳ハーフ夜</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>3500</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>49000</v>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>Free日本酒</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>980</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="L13" s="6" t="n">
+        <v>7840</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/04</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>3位</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>あさり膳刺身</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>2400</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>31200</v>
+      </c>
+      <c r="I14" s="15" t="inlineStr">
+        <is>
+          <t>ウーロン茶</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>400</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="L14" s="6" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/05</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>1位</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>あさり膳ハーフ</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G15" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>105000</v>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>プレミアムモルツ生</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>880</v>
+      </c>
+      <c r="K15" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="L15" s="10" t="n">
+        <v>16720</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/05</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>2位</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>宝家膳</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>6500</v>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>39000</v>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>オールフリー</t>
+        </is>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>680</v>
+      </c>
+      <c r="K16" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="L16" s="10" t="n">
+        <v>15640</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/05</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>3位</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>Freeゲストハウス</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>17000</v>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>34000</v>
+      </c>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>吉四六ボトル</t>
+        </is>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>7980</v>
+      </c>
+      <c r="K17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="10" t="n">
+        <v>7980</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/06</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>1位</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>あさり膳ハーフ</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>110000</v>
+      </c>
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>プレミアムモルツ生</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>880</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="L18" s="6" t="n">
+        <v>14080</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/06</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>2位</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>あさり膳串揚げ</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>2400</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>26400</v>
+      </c>
+      <c r="I19" s="15" t="inlineStr">
+        <is>
+          <t>角ハイボール</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>680</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="L19" s="6" t="n">
+        <v>12240</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/06</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>3位</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>あさり膳刺身</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>2400</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>24000</v>
+      </c>
+      <c r="I20" s="15" t="inlineStr">
+        <is>
+          <t>オールフリー</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>680</v>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="L20" s="6" t="n">
+        <v>9520</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/07</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>1位</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr"/>
+      <c r="F21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="14" t="inlineStr"/>
+      <c r="J21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/07</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>2位</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr"/>
+      <c r="F22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="14" t="inlineStr"/>
+      <c r="J22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/07</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>3位</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr"/>
+      <c r="F23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="14" t="inlineStr"/>
+      <c r="J23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>1位</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>宴会コース</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>85000</v>
+      </c>
+      <c r="I24" s="15" t="inlineStr">
+        <is>
+          <t>プレミアムモルツ生</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>880</v>
+      </c>
+      <c r="K24" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="L24" s="6" t="n">
+        <v>18480</v>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>2位</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>あさり膳ハーフ</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>57500</v>
+      </c>
+      <c r="I25" s="15" t="inlineStr">
+        <is>
+          <t>オールフリー</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>680</v>
+      </c>
+      <c r="K25" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="L25" s="6" t="n">
+        <v>13600</v>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>3位</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>季節の一品</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>1980</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>21780</v>
+      </c>
+      <c r="I26" s="15" t="inlineStr">
+        <is>
+          <t>角ハイボール</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>680</v>
+      </c>
+      <c r="K26" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="L26" s="6" t="n">
+        <v>8840</v>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/09</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>1位</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>あさり膳ハーフ</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G27" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="H27" s="10" t="n">
+        <v>75000</v>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>プレミアムモルツ生</t>
+        </is>
+      </c>
+      <c r="J27" s="10" t="n">
+        <v>880</v>
+      </c>
+      <c r="K27" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="L27" s="10" t="n">
+        <v>31680</v>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/09</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>2位</t>
+        </is>
+      </c>
+      <c r="E28" s="14" t="inlineStr">
+        <is>
+          <t>宴会コース</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G28" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" s="10" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>飲み放題</t>
+        </is>
+      </c>
+      <c r="J28" s="10" t="n">
+        <v>4000</v>
+      </c>
+      <c r="K28" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L28" s="10" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/09</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>3位</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>Freeゲストハウス</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G29" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" s="10" t="n">
+        <v>36000</v>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>吉四六ボトル</t>
+        </is>
+      </c>
+      <c r="J29" s="10" t="n">
+        <v>7980</v>
+      </c>
+      <c r="K29" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L29" s="10" t="n">
+        <v>15960</v>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/10</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>1位</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>宴会コース</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>65000</v>
+      </c>
+      <c r="I30" s="15" t="inlineStr">
+        <is>
+          <t>プレミアムモルツ生</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>880</v>
+      </c>
+      <c r="K30" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="L30" s="6" t="n">
+        <v>17600</v>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/10</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>2位</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>あさり膳刺身</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>2400</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>55200</v>
+      </c>
+      <c r="I31" s="15" t="inlineStr">
+        <is>
+          <t>プレミアムモルツ中瓶</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="n">
+        <v>980</v>
+      </c>
+      <c r="K31" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="L31" s="6" t="n">
+        <v>4900</v>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/10</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>3位</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>あさり膳ハーフ</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I32" s="15" t="inlineStr">
+        <is>
+          <t>オールフリー</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="n">
+        <v>680</v>
+      </c>
+      <c r="K32" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L32" s="6" t="n">
+        <v>4080</v>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/11</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>1位</t>
+        </is>
+      </c>
+      <c r="E33" s="14" t="inlineStr"/>
+      <c r="F33" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="14" t="inlineStr"/>
+      <c r="J33" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/11</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>2位</t>
+        </is>
+      </c>
+      <c r="E34" s="14" t="inlineStr"/>
+      <c r="F34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="14" t="inlineStr"/>
+      <c r="J34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/11</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>3位</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr"/>
+      <c r="F35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="14" t="inlineStr"/>
+      <c r="J35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/12</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>1位</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="inlineStr">
+        <is>
+          <t>宴会コース</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>240000</v>
+      </c>
+      <c r="I36" s="15" t="inlineStr">
+        <is>
+          <t>プレミアムモルツ生</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="n">
+        <v>880</v>
+      </c>
+      <c r="K36" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="L36" s="6" t="n">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/12</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>2位</t>
+        </is>
+      </c>
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>外販</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>100000</v>
+      </c>
+      <c r="I37" s="15" t="inlineStr">
+        <is>
+          <t>あらごし梅酒</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="n">
+        <v>650</v>
+      </c>
+      <c r="K37" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="L37" s="6" t="n">
+        <v>10400</v>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/12</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>3位</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>あさり膳ハーフ</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>2400</v>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>81600</v>
+      </c>
+      <c r="I38" s="15" t="inlineStr">
+        <is>
+          <t>峰の精四合</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="n">
+        <v>8480</v>
+      </c>
+      <c r="K38" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" s="6" t="n">
+        <v>8480</v>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/13</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>1位</t>
+        </is>
+      </c>
+      <c r="E39" s="14" t="inlineStr">
+        <is>
+          <t>宴会コース</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="n">
+        <v>24000</v>
+      </c>
+      <c r="G39" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H39" s="10" t="n">
+        <v>96000</v>
+      </c>
+      <c r="I39" s="14" t="inlineStr">
+        <is>
+          <t>ＦｒｅｅワインＢ</t>
+        </is>
+      </c>
+      <c r="J39" s="10" t="n">
+        <v>27800</v>
+      </c>
+      <c r="K39" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" s="10" t="n">
+        <v>27800</v>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/13</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>2位</t>
+        </is>
+      </c>
+      <c r="E40" s="14" t="inlineStr">
+        <is>
+          <t>宴会コース</t>
+        </is>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G40" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H40" s="10" t="n">
+        <v>64000</v>
+      </c>
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>プレミアムモルツ生</t>
+        </is>
+      </c>
+      <c r="J40" s="10" t="n">
+        <v>880</v>
+      </c>
+      <c r="K40" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="L40" s="10" t="n">
+        <v>17600</v>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/13</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>3位</t>
+        </is>
+      </c>
+      <c r="E41" s="14" t="inlineStr">
+        <is>
+          <t>宴会コース</t>
+        </is>
+      </c>
+      <c r="F41" s="10" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G41" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H41" s="10" t="n">
+        <v>60000</v>
+      </c>
+      <c r="I41" s="14" t="inlineStr">
+        <is>
+          <t>角ハイボール</t>
+        </is>
+      </c>
+      <c r="J41" s="10" t="n">
+        <v>680</v>
+      </c>
+      <c r="K41" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="L41" s="10" t="n">
+        <v>4080</v>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>1位</t>
+        </is>
+      </c>
+      <c r="E42" s="15" t="inlineStr">
+        <is>
+          <t>宝家膳</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="H42" s="6" t="n">
+        <v>180000</v>
+      </c>
+      <c r="I42" s="15" t="inlineStr">
+        <is>
+          <t>飲み放題</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K42" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="L42" s="6" t="n">
+        <v>42000</v>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>2位</t>
+        </is>
+      </c>
+      <c r="E43" s="15" t="inlineStr">
+        <is>
+          <t>宴会コース</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="H43" s="6" t="n">
+        <v>90000</v>
+      </c>
+      <c r="I43" s="15" t="inlineStr">
+        <is>
+          <t>プレミアムモルツ生</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="n">
+        <v>880</v>
+      </c>
+      <c r="K43" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="L43" s="6" t="n">
+        <v>28160</v>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>3位</t>
+        </is>
+      </c>
+      <c r="E44" s="15" t="inlineStr">
+        <is>
+          <t>宴会コース</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>15500</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H44" s="6" t="n">
+        <v>62000</v>
+      </c>
+      <c r="I44" s="15" t="inlineStr">
+        <is>
+          <t>プレミアムモルツ中瓶</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="n">
+        <v>980</v>
+      </c>
+      <c r="K44" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="L44" s="6" t="n">
+        <v>16660</v>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/15</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>1位</t>
+        </is>
+      </c>
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t>宴会コース</t>
+        </is>
+      </c>
+      <c r="F45" s="10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G45" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="H45" s="10" t="n">
+        <v>190000</v>
+      </c>
+      <c r="I45" s="14" t="inlineStr">
+        <is>
+          <t>飲み放題</t>
+        </is>
+      </c>
+      <c r="J45" s="10" t="n">
+        <v>3500</v>
+      </c>
+      <c r="K45" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="L45" s="10" t="n">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/15</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>2位</t>
+        </is>
+      </c>
+      <c r="E46" s="14" t="inlineStr">
+        <is>
+          <t>あさり膳ハーフ</t>
+        </is>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G46" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="H46" s="10" t="n">
+        <v>67500</v>
+      </c>
+      <c r="I46" s="14" t="inlineStr">
+        <is>
+          <t>プレミアムモルツ生</t>
+        </is>
+      </c>
+      <c r="J46" s="10" t="n">
+        <v>880</v>
+      </c>
+      <c r="K46" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="L46" s="10" t="n">
+        <v>31680</v>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/15</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>3位</t>
+        </is>
+      </c>
+      <c r="E47" s="14" t="inlineStr">
+        <is>
+          <t>季節の一品</t>
+        </is>
+      </c>
+      <c r="F47" s="10" t="n">
+        <v>1980</v>
+      </c>
+      <c r="G47" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="H47" s="10" t="n">
+        <v>59400</v>
+      </c>
+      <c r="I47" s="14" t="inlineStr">
+        <is>
+          <t>知多ハイボール</t>
+        </is>
+      </c>
+      <c r="J47" s="10" t="n">
+        <v>980</v>
+      </c>
+      <c r="K47" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="L47" s="10" t="n">
+        <v>24500</v>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/16</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>1位</t>
+        </is>
+      </c>
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>あさり膳かき揚げ</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>2400</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="H48" s="6" t="n">
+        <v>91200</v>
+      </c>
+      <c r="I48" s="15" t="inlineStr">
+        <is>
+          <t>プレミアムモルツ生</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="n">
+        <v>880</v>
+      </c>
+      <c r="K48" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="L48" s="6" t="n">
+        <v>19360</v>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/16</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>2位</t>
+        </is>
+      </c>
+      <c r="E49" s="15" t="inlineStr">
+        <is>
+          <t>宴会コース</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>90000</v>
+      </c>
+      <c r="I49" s="15" t="inlineStr">
+        <is>
+          <t>吉四六ボトル</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="n">
+        <v>7980</v>
+      </c>
+      <c r="K49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" s="6" t="n">
+        <v>7980</v>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/16</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>3位</t>
+        </is>
+      </c>
+      <c r="E50" s="15" t="inlineStr">
+        <is>
+          <t>あさり膳ハーフ</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="H50" s="6" t="n">
+        <v>65000</v>
+      </c>
+      <c r="I50" s="15" t="inlineStr">
+        <is>
+          <t>プレミアムモルツ中瓶</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="n">
+        <v>980</v>
+      </c>
+      <c r="K50" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="L50" s="6" t="n">
+        <v>7840</v>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/17</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>1位</t>
+        </is>
+      </c>
+      <c r="E51" s="14" t="inlineStr">
+        <is>
+          <t>宴会コース</t>
+        </is>
+      </c>
+      <c r="F51" s="10" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G51" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="H51" s="10" t="n">
+        <v>95000</v>
+      </c>
+      <c r="I51" s="14" t="inlineStr">
+        <is>
+          <t>飲み放題</t>
+        </is>
+      </c>
+      <c r="J51" s="10" t="n">
+        <v>3300</v>
+      </c>
+      <c r="K51" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="L51" s="10" t="n">
+        <v>62700</v>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/17</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>2位</t>
+        </is>
+      </c>
+      <c r="E52" s="14" t="inlineStr">
+        <is>
+          <t>あさり膳ハーフ夜</t>
+        </is>
+      </c>
+      <c r="F52" s="10" t="n">
+        <v>3500</v>
+      </c>
+      <c r="G52" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="H52" s="10" t="n">
+        <v>70000</v>
+      </c>
+      <c r="I52" s="14" t="inlineStr">
+        <is>
+          <t>プレミアムモルツ生</t>
+        </is>
+      </c>
+      <c r="J52" s="10" t="n">
+        <v>880</v>
+      </c>
+      <c r="K52" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="L52" s="10" t="n">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/17</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>3位</t>
+        </is>
+      </c>
+      <c r="E53" s="14" t="inlineStr">
+        <is>
+          <t>あさり膳刺身</t>
+        </is>
+      </c>
+      <c r="F53" s="10" t="n">
+        <v>2400</v>
+      </c>
+      <c r="G53" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="H53" s="10" t="n">
+        <v>64800</v>
+      </c>
+      <c r="I53" s="14" t="inlineStr">
+        <is>
+          <t>オールフリー</t>
+        </is>
+      </c>
+      <c r="J53" s="10" t="n">
+        <v>680</v>
+      </c>
+      <c r="K53" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="L53" s="10" t="n">
+        <v>8160</v>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/18</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>1位</t>
+        </is>
+      </c>
+      <c r="E54" s="15" t="inlineStr"/>
+      <c r="F54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="15" t="inlineStr"/>
+      <c r="J54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/18</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>2位</t>
+        </is>
+      </c>
+      <c r="E55" s="15" t="inlineStr"/>
+      <c r="F55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="15" t="inlineStr"/>
+      <c r="J55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/18</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>3位</t>
+        </is>
+      </c>
+      <c r="E56" s="15" t="inlineStr"/>
+      <c r="F56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="15" t="inlineStr"/>
+      <c r="J56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>1位</t>
+        </is>
+      </c>
+      <c r="E57" s="14" t="inlineStr">
+        <is>
+          <t>宴会コース</t>
+        </is>
+      </c>
+      <c r="F57" s="10" t="n">
+        <v>19000</v>
+      </c>
+      <c r="G57" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H57" s="10" t="n">
+        <v>114000</v>
+      </c>
+      <c r="I57" s="14" t="inlineStr">
+        <is>
+          <t>プレミアムモルツ生</t>
+        </is>
+      </c>
+      <c r="J57" s="10" t="n">
+        <v>880</v>
+      </c>
+      <c r="K57" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="L57" s="10" t="n">
+        <v>33440</v>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>2位</t>
+        </is>
+      </c>
+      <c r="E58" s="14" t="inlineStr">
+        <is>
+          <t>あさり膳ハーフ</t>
+        </is>
+      </c>
+      <c r="F58" s="10" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G58" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="H58" s="10" t="n">
+        <v>70000</v>
+      </c>
+      <c r="I58" s="14" t="inlineStr">
+        <is>
+          <t>ﾍﾞﾘﾝｼﾞｼﾞｬｰｼｬﾙﾄﾞﾈ</t>
+        </is>
+      </c>
+      <c r="J58" s="10" t="n">
+        <v>9800</v>
+      </c>
+      <c r="K58" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L58" s="10" t="n">
+        <v>9800</v>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>3位</t>
+        </is>
+      </c>
+      <c r="E59" s="14" t="inlineStr">
+        <is>
+          <t>宴会コース</t>
+        </is>
+      </c>
+      <c r="F59" s="10" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G59" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="H59" s="10" t="n">
+        <v>56000</v>
+      </c>
+      <c r="I59" s="14" t="inlineStr">
+        <is>
+          <t>吉四六ボトル</t>
+        </is>
+      </c>
+      <c r="J59" s="10" t="n">
+        <v>7980</v>
+      </c>
+      <c r="K59" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L59" s="10" t="n">
+        <v>7980</v>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>1位</t>
+        </is>
+      </c>
+      <c r="E60" s="15" t="inlineStr">
+        <is>
+          <t>あさり膳ハーフ</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="H60" s="6" t="n">
+        <v>75000</v>
+      </c>
+      <c r="I60" s="15" t="inlineStr">
+        <is>
+          <t>吉四六ボトル</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="n">
+        <v>7980</v>
+      </c>
+      <c r="K60" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L60" s="6" t="n">
+        <v>15960</v>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>2位</t>
+        </is>
+      </c>
+      <c r="E61" s="15" t="inlineStr">
+        <is>
+          <t>あさり膳ハーフ夜</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>3500</v>
+      </c>
+      <c r="G61" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H61" s="6" t="n">
+        <v>17500</v>
+      </c>
+      <c r="I61" s="15" t="inlineStr">
+        <is>
+          <t>プレミアムモルツ生</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="n">
+        <v>880</v>
+      </c>
+      <c r="K61" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="L61" s="6" t="n">
+        <v>11440</v>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>3位</t>
+        </is>
+      </c>
+      <c r="E62" s="15" t="inlineStr">
+        <is>
+          <t>宴会コース</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G62" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H62" s="6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I62" s="15" t="inlineStr">
+        <is>
+          <t>オールフリー</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="n">
+        <v>680</v>
+      </c>
+      <c r="K62" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="L62" s="6" t="n">
+        <v>6120</v>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/21</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>1位</t>
+        </is>
+      </c>
+      <c r="E63" s="14" t="inlineStr">
+        <is>
+          <t>宴会コース</t>
+        </is>
+      </c>
+      <c r="F63" s="10" t="n">
+        <v>5500</v>
+      </c>
+      <c r="G63" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="H63" s="10" t="n">
+        <v>137500</v>
+      </c>
+      <c r="I63" s="14" t="inlineStr">
+        <is>
+          <t>Freeウィスキー</t>
+        </is>
+      </c>
+      <c r="J63" s="10" t="n">
+        <v>1500</v>
+      </c>
+      <c r="K63" s="10" t="n">
+        <v>62</v>
+      </c>
+      <c r="L63" s="10" t="n">
+        <v>93000</v>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/21</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>2位</t>
+        </is>
+      </c>
+      <c r="E64" s="14" t="inlineStr">
+        <is>
+          <t>あさり膳ハーフ</t>
+        </is>
+      </c>
+      <c r="F64" s="10" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G64" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="H64" s="10" t="n">
+        <v>85000</v>
+      </c>
+      <c r="I64" s="14" t="inlineStr">
+        <is>
+          <t>飲み放題</t>
+        </is>
+      </c>
+      <c r="J64" s="10" t="n">
+        <v>3500</v>
+      </c>
+      <c r="K64" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="L64" s="10" t="n">
+        <v>87500</v>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/21</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>3位</t>
+        </is>
+      </c>
+      <c r="E65" s="14" t="inlineStr">
+        <is>
+          <t>季節の一品</t>
+        </is>
+      </c>
+      <c r="F65" s="10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G65" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H65" s="10" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I65" s="14" t="inlineStr">
+        <is>
+          <t>ＦｒｅｅワインＢ</t>
+        </is>
+      </c>
+      <c r="J65" s="10" t="n">
+        <v>55000</v>
+      </c>
+      <c r="K65" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L65" s="10" t="n">
+        <v>55000</v>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>1位</t>
+        </is>
+      </c>
+      <c r="E66" s="15" t="inlineStr">
+        <is>
+          <t>宴会コース</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G66" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H66" s="6" t="n">
+        <v>112000</v>
+      </c>
+      <c r="I66" s="15" t="inlineStr">
+        <is>
+          <t>プレミアムモルツ中瓶</t>
+        </is>
+      </c>
+      <c r="J66" s="6" t="n">
+        <v>980</v>
+      </c>
+      <c r="K66" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="L66" s="6" t="n">
+        <v>29400</v>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>2位</t>
+        </is>
+      </c>
+      <c r="E67" s="15" t="inlineStr">
+        <is>
+          <t>外販料理</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G67" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="H67" s="6" t="n">
+        <v>74000</v>
+      </c>
+      <c r="I67" s="15" t="inlineStr">
+        <is>
+          <t>吟辛1合</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="n">
+        <v>950</v>
+      </c>
+      <c r="K67" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="L67" s="6" t="n">
+        <v>16150</v>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>3位</t>
+        </is>
+      </c>
+      <c r="E68" s="15" t="inlineStr">
+        <is>
+          <t>宴会コース</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="G68" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="H68" s="6" t="n">
+        <v>56000</v>
+      </c>
+      <c r="I68" s="15" t="inlineStr">
+        <is>
+          <t>吉四六ボトル</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="n">
+        <v>7980</v>
+      </c>
+      <c r="K68" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L68" s="6" t="n">
+        <v>15960</v>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/23</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>1位</t>
+        </is>
+      </c>
+      <c r="E69" s="14" t="inlineStr">
+        <is>
+          <t>宴会コース</t>
+        </is>
+      </c>
+      <c r="F69" s="10" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G69" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="H69" s="10" t="n">
+        <v>155000</v>
+      </c>
+      <c r="I69" s="14" t="inlineStr">
+        <is>
+          <t>プレミアムモルツ生</t>
+        </is>
+      </c>
+      <c r="J69" s="10" t="n">
+        <v>880</v>
+      </c>
+      <c r="K69" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="L69" s="10" t="n">
+        <v>32560</v>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/23</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>2位</t>
+        </is>
+      </c>
+      <c r="E70" s="14" t="inlineStr">
+        <is>
+          <t>あさり膳ハーフ</t>
+        </is>
+      </c>
+      <c r="F70" s="10" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G70" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="H70" s="10" t="n">
+        <v>60000</v>
+      </c>
+      <c r="I70" s="14" t="inlineStr">
+        <is>
+          <t>オールフリー</t>
+        </is>
+      </c>
+      <c r="J70" s="10" t="n">
+        <v>680</v>
+      </c>
+      <c r="K70" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="L70" s="10" t="n">
+        <v>18360</v>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/23</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>3位</t>
+        </is>
+      </c>
+      <c r="E71" s="14" t="inlineStr">
+        <is>
+          <t>宝家膳</t>
+        </is>
+      </c>
+      <c r="F71" s="10" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G71" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H71" s="10" t="n">
+        <v>60000</v>
+      </c>
+      <c r="I71" s="14" t="inlineStr">
+        <is>
+          <t>ＦｒｅｅワインＢ</t>
+        </is>
+      </c>
+      <c r="J71" s="10" t="n">
+        <v>12800</v>
+      </c>
+      <c r="K71" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L71" s="10" t="n">
+        <v>12800</v>
+      </c>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/24</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>1位</t>
+        </is>
+      </c>
+      <c r="E72" s="15" t="inlineStr">
+        <is>
+          <t>宴会コース</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G72" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="H72" s="6" t="n">
+        <v>108000</v>
+      </c>
+      <c r="I72" s="15" t="inlineStr">
+        <is>
+          <t>プレミアムモルツ生</t>
+        </is>
+      </c>
+      <c r="J72" s="6" t="n">
+        <v>880</v>
+      </c>
+      <c r="K72" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="L72" s="6" t="n">
+        <v>32560</v>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/24</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>2位</t>
+        </is>
+      </c>
+      <c r="E73" s="15" t="inlineStr">
+        <is>
+          <t>あさり膳刺身</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="n">
+        <v>2400</v>
+      </c>
+      <c r="G73" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="H73" s="6" t="n">
+        <v>81600</v>
+      </c>
+      <c r="I73" s="15" t="inlineStr">
+        <is>
+          <t>プレミアムモルツ中瓶</t>
+        </is>
+      </c>
+      <c r="J73" s="6" t="n">
+        <v>980</v>
+      </c>
+      <c r="K73" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="L73" s="6" t="n">
+        <v>14700</v>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/24</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>3位</t>
+        </is>
+      </c>
+      <c r="E74" s="15" t="inlineStr">
+        <is>
+          <t>宴会コース</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="n">
+        <v>19000</v>
+      </c>
+      <c r="G74" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H74" s="6" t="n">
+        <v>76000</v>
+      </c>
+      <c r="I74" s="15" t="inlineStr">
+        <is>
+          <t>ウーロン茶</t>
+        </is>
+      </c>
+      <c r="J74" s="6" t="n">
+        <v>400</v>
+      </c>
+      <c r="K74" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="L74" s="6" t="n">
+        <v>8400</v>
+      </c>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>1位</t>
+        </is>
+      </c>
+      <c r="E75" s="14" t="inlineStr"/>
+      <c r="F75" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="14" t="inlineStr"/>
+      <c r="J75" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>2位</t>
+        </is>
+      </c>
+      <c r="E76" s="14" t="inlineStr"/>
+      <c r="F76" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="14" t="inlineStr"/>
+      <c r="J76" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>3位</t>
+        </is>
+      </c>
+      <c r="E77" s="14" t="inlineStr"/>
+      <c r="F77" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="14" t="inlineStr"/>
+      <c r="J77" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/26</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>1位</t>
+        </is>
+      </c>
+      <c r="E78" s="15" t="inlineStr">
+        <is>
+          <t>あさり膳ハーフ</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G78" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="H78" s="6" t="n">
+        <v>80000</v>
+      </c>
+      <c r="I78" s="15" t="inlineStr">
+        <is>
+          <t>プレミアムモルツ生</t>
+        </is>
+      </c>
+      <c r="J78" s="6" t="n">
+        <v>880</v>
+      </c>
+      <c r="K78" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="L78" s="6" t="n">
+        <v>14080</v>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/26</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>2位</t>
+        </is>
+      </c>
+      <c r="E79" s="15" t="inlineStr">
+        <is>
+          <t>宴会コース</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G79" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H79" s="6" t="n">
+        <v>70000</v>
+      </c>
+      <c r="I79" s="15" t="inlineStr">
+        <is>
+          <t>プレミアムモルツ中瓶</t>
+        </is>
+      </c>
+      <c r="J79" s="6" t="n">
+        <v>980</v>
+      </c>
+      <c r="K79" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="L79" s="6" t="n">
+        <v>8820</v>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/26</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>3位</t>
+        </is>
+      </c>
+      <c r="E80" s="15" t="inlineStr">
+        <is>
+          <t>宴会コース</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="n">
+        <v>5200</v>
+      </c>
+      <c r="G80" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H80" s="6" t="n">
+        <v>62400</v>
+      </c>
+      <c r="I80" s="15" t="inlineStr">
+        <is>
+          <t>角ハイボール</t>
+        </is>
+      </c>
+      <c r="J80" s="6" t="n">
+        <v>680</v>
+      </c>
+      <c r="K80" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="L80" s="6" t="n">
+        <v>5440</v>
+      </c>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/27</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>1位</t>
+        </is>
+      </c>
+      <c r="E81" s="14" t="inlineStr">
+        <is>
+          <t>宴会コース</t>
+        </is>
+      </c>
+      <c r="F81" s="10" t="n">
+        <v>7000</v>
+      </c>
+      <c r="G81" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="H81" s="10" t="n">
+        <v>98000</v>
+      </c>
+      <c r="I81" s="14" t="inlineStr">
+        <is>
+          <t>飲み放題</t>
+        </is>
+      </c>
+      <c r="J81" s="10" t="n">
+        <v>3500</v>
+      </c>
+      <c r="K81" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="L81" s="10" t="n">
+        <v>49000</v>
+      </c>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/27</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>2位</t>
+        </is>
+      </c>
+      <c r="E82" s="14" t="inlineStr">
+        <is>
+          <t>特選牛の網や焼き膳</t>
+        </is>
+      </c>
+      <c r="F82" s="10" t="n">
+        <v>2700</v>
+      </c>
+      <c r="G82" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="H82" s="10" t="n">
+        <v>54000</v>
+      </c>
+      <c r="I82" s="14" t="inlineStr">
+        <is>
+          <t>プレミアムモルツ中瓶</t>
+        </is>
+      </c>
+      <c r="J82" s="10" t="n">
+        <v>980</v>
+      </c>
+      <c r="K82" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="L82" s="10" t="n">
+        <v>21560</v>
+      </c>
+    </row>
+    <row r="83" ht="18" customHeight="1">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/27</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>3位</t>
+        </is>
+      </c>
+      <c r="E83" s="14" t="inlineStr">
+        <is>
+          <t>あさり膳ハーフ</t>
+        </is>
+      </c>
+      <c r="F83" s="10" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G83" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="H83" s="10" t="n">
+        <v>45000</v>
+      </c>
+      <c r="I83" s="14" t="inlineStr">
+        <is>
+          <t>プレミアムモルツ生</t>
+        </is>
+      </c>
+      <c r="J83" s="10" t="n">
+        <v>880</v>
+      </c>
+      <c r="K83" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="L83" s="10" t="n">
+        <v>9680</v>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/28</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>1位</t>
+        </is>
+      </c>
+      <c r="E84" s="15" t="inlineStr">
+        <is>
+          <t>宴会コース</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G84" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="H84" s="6" t="n">
+        <v>90000</v>
+      </c>
+      <c r="I84" s="15" t="inlineStr">
+        <is>
+          <t>飲み放題</t>
+        </is>
+      </c>
+      <c r="J84" s="6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K84" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="L84" s="6" t="n">
+        <v>54000</v>
+      </c>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/28</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>2位</t>
+        </is>
+      </c>
+      <c r="E85" s="15" t="inlineStr">
+        <is>
+          <t>玉代</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="n">
+        <v>14000</v>
+      </c>
+      <c r="G85" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H85" s="6" t="n">
+        <v>70000</v>
+      </c>
+      <c r="I85" s="15" t="inlineStr">
+        <is>
+          <t>プレミアムモルツ中瓶</t>
+        </is>
+      </c>
+      <c r="J85" s="6" t="n">
+        <v>980</v>
+      </c>
+      <c r="K85" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="L85" s="6" t="n">
+        <v>6860</v>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/28</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>3位</t>
+        </is>
+      </c>
+      <c r="E86" s="15" t="inlineStr">
+        <is>
+          <t>あさり膳ハーフ</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G86" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="H86" s="6" t="n">
+        <v>32500</v>
+      </c>
+      <c r="I86" s="15" t="inlineStr">
+        <is>
+          <t>グールガゾーｼｬﾙﾄﾞﾈ</t>
+        </is>
+      </c>
+      <c r="J86" s="6" t="n">
+        <v>5800</v>
+      </c>
+      <c r="K86" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L86" s="6" t="n">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>1位</t>
+        </is>
+      </c>
+      <c r="E87" s="14" t="inlineStr">
+        <is>
+          <t>宴会コース</t>
+        </is>
+      </c>
+      <c r="F87" s="10" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G87" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H87" s="10" t="n">
+        <v>180000</v>
+      </c>
+      <c r="I87" s="14" t="inlineStr">
+        <is>
+          <t>飲み放題</t>
+        </is>
+      </c>
+      <c r="J87" s="10" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K87" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="L87" s="10" t="n">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>2位</t>
+        </is>
+      </c>
+      <c r="E88" s="14" t="inlineStr">
+        <is>
+          <t>あさり膳ハーフ</t>
+        </is>
+      </c>
+      <c r="F88" s="10" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G88" s="10" t="n">
+        <v>57</v>
+      </c>
+      <c r="H88" s="10" t="n">
+        <v>142500</v>
+      </c>
+      <c r="I88" s="14" t="inlineStr">
+        <is>
+          <t>ﾍﾞﾘﾝｼﾞｼﾞｬｰｼｬﾙﾄﾞﾈ</t>
+        </is>
+      </c>
+      <c r="J88" s="10" t="n">
+        <v>9800</v>
+      </c>
+      <c r="K88" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L88" s="10" t="n">
+        <v>9800</v>
+      </c>
+    </row>
+    <row r="89" ht="18" customHeight="1">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>3位</t>
+        </is>
+      </c>
+      <c r="E89" s="14" t="inlineStr">
+        <is>
+          <t>宴会コース</t>
+        </is>
+      </c>
+      <c r="F89" s="10" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G89" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="H89" s="10" t="n">
+        <v>126000</v>
+      </c>
+      <c r="I89" s="14" t="inlineStr">
+        <is>
+          <t>プレミアムモルツ生</t>
+        </is>
+      </c>
+      <c r="J89" s="10" t="n">
+        <v>880</v>
+      </c>
+      <c r="K89" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="L89" s="10" t="n">
+        <v>8800</v>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/30</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>1位</t>
+        </is>
+      </c>
+      <c r="E90" s="15" t="inlineStr">
+        <is>
+          <t>宴会コース</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="n">
+        <v>11500</v>
+      </c>
+      <c r="G90" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H90" s="6" t="n">
+        <v>69000</v>
+      </c>
+      <c r="I90" s="15" t="inlineStr">
+        <is>
+          <t>プレミアムモルツ生</t>
+        </is>
+      </c>
+      <c r="J90" s="6" t="n">
+        <v>880</v>
+      </c>
+      <c r="K90" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="L90" s="6" t="n">
+        <v>29040</v>
+      </c>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/30</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>2位</t>
+        </is>
+      </c>
+      <c r="E91" s="15" t="inlineStr">
+        <is>
+          <t>季節の一品</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="n">
+        <v>1780</v>
+      </c>
+      <c r="G91" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="H91" s="6" t="n">
+        <v>64080</v>
+      </c>
+      <c r="I91" s="15" t="inlineStr">
+        <is>
+          <t>ウーロン茶</t>
+        </is>
+      </c>
+      <c r="J91" s="6" t="n">
+        <v>400</v>
+      </c>
+      <c r="K91" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="L91" s="6" t="n">
+        <v>12800</v>
+      </c>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>2026/05/30</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>3位</t>
+        </is>
+      </c>
+      <c r="E92" s="15" t="inlineStr">
+        <is>
+          <t>宝家膳上</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="n">
+        <v>6500</v>
+      </c>
+      <c r="G92" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H92" s="6" t="n">
+        <v>58500</v>
+      </c>
+      <c r="I92" s="15" t="inlineStr">
+        <is>
+          <t>プレミアムモルツ中瓶</t>
+        </is>
+      </c>
+      <c r="J92" s="6" t="n">
+        <v>980</v>
+      </c>
+      <c r="K92" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="L92" s="6" t="n">
+        <v>10780</v>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/31</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>1位</t>
+        </is>
+      </c>
+      <c r="E93" s="14" t="inlineStr">
+        <is>
+          <t>宴会コース</t>
+        </is>
+      </c>
+      <c r="F93" s="10" t="n">
+        <v>500</v>
+      </c>
+      <c r="G93" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="H93" s="10" t="n">
+        <v>10500</v>
+      </c>
+      <c r="I93" s="14" t="inlineStr">
+        <is>
+          <t>プレミアムモルツ生</t>
+        </is>
+      </c>
+      <c r="J93" s="10" t="n">
+        <v>880</v>
+      </c>
+      <c r="K93" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="L93" s="10" t="n">
+        <v>27280</v>
+      </c>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/31</t>
+        </is>
+      </c>
+      <c r="B94" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>2位</t>
+        </is>
+      </c>
+      <c r="E94" s="14" t="inlineStr">
+        <is>
+          <t>あさり膳刺身</t>
+        </is>
+      </c>
+      <c r="F94" s="10" t="n">
+        <v>2400</v>
+      </c>
+      <c r="G94" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="H94" s="10" t="n">
+        <v>72000</v>
+      </c>
+      <c r="I94" s="14" t="inlineStr">
+        <is>
+          <t>角ハイボール</t>
+        </is>
+      </c>
+      <c r="J94" s="10" t="n">
+        <v>680</v>
+      </c>
+      <c r="K94" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="L94" s="10" t="n">
+        <v>12240</v>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/31</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>3位</t>
+        </is>
+      </c>
+      <c r="E95" s="14" t="inlineStr">
+        <is>
+          <t>宴会コース</t>
+        </is>
+      </c>
+      <c r="F95" s="10" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G95" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="H95" s="10" t="n">
+        <v>45000</v>
+      </c>
+      <c r="I95" s="14" t="inlineStr">
+        <is>
+          <t>ウーロン茶</t>
+        </is>
+      </c>
+      <c r="J95" s="10" t="n">
+        <v>400</v>
+      </c>
+      <c r="K95" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="L95" s="10" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>合 計</t>
+        </is>
+      </c>
+      <c r="E96" s="12" t="n"/>
+      <c r="F96" s="12" t="n"/>
+      <c r="G96" s="11" t="n">
+        <v>1517</v>
+      </c>
+      <c r="H96" s="11" t="n">
+        <v>6023660</v>
+      </c>
+      <c r="I96" s="12" t="n"/>
+      <c r="J96" s="12" t="n"/>
+      <c r="K96" s="11" t="n">
+        <v>1310</v>
+      </c>
+      <c r="L96" s="11" t="n">
+        <v>1703750</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="I1:L1"/>
+    <mergeCell ref="A96:D96"/>
+    <mergeCell ref="E1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/frontend/public/data/daily_2026_5.xlsx
+++ b/frontend/public/data/daily_2026_5.xlsx
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V34"/>
+  <dimension ref="A1:X34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -518,23 +518,25 @@
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -572,85 +574,95 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
+          <t>天気</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>天気概況</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
           <t>総売上高</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>純売上高</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>現金</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>JCB</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>千葉銀行</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>アクアコイン</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>PayPay</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>ふるさと納税</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>売掛金</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>FOOD</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>DRINK</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>売店</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>昼食客数</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>夕食客数</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="W2" s="2" t="inlineStr">
         <is>
           <t>昼食売上</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>夕食売上</t>
         </is>
@@ -672,55 +684,65 @@
       </c>
       <c r="D3" s="5" t="inlineStr"/>
       <c r="E3" s="5" t="inlineStr"/>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>雨</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>雨のち晴</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="n">
         <v>499613</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="I3" s="6" t="n">
         <v>454329</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="J3" s="6" t="n">
         <v>211160</v>
       </c>
-      <c r="I3" s="6" t="n">
+      <c r="K3" s="6" t="n">
         <v>35549</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="L3" s="6" t="n">
         <v>111102</v>
       </c>
-      <c r="K3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="6" t="n">
+      <c r="M3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="6" t="n">
         <v>51778</v>
       </c>
-      <c r="M3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" s="6" t="n">
+      <c r="O3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="6" t="n">
         <v>90024</v>
       </c>
-      <c r="O3" s="6" t="n">
+      <c r="Q3" s="6" t="n">
         <v>379200</v>
       </c>
-      <c r="P3" s="6" t="n">
+      <c r="R3" s="6" t="n">
         <v>64960</v>
       </c>
-      <c r="Q3" s="6" t="n">
+      <c r="S3" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="R3" s="6" t="n">
+      <c r="T3" s="6" t="n">
         <v>52653</v>
       </c>
-      <c r="S3" s="6" t="n">
+      <c r="U3" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="T3" s="6" t="n">
+      <c r="V3" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="U3" s="6" t="n">
+      <c r="W3" s="6" t="n">
         <v>146538</v>
       </c>
-      <c r="V3" s="6" t="n">
+      <c r="X3" s="6" t="n">
         <v>353075</v>
       </c>
     </row>
@@ -740,55 +762,65 @@
       </c>
       <c r="D4" s="9" t="inlineStr"/>
       <c r="E4" s="9" t="inlineStr"/>
-      <c r="F4" s="10" t="n">
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>晴のち曇</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="n">
         <v>765280</v>
       </c>
-      <c r="G4" s="10" t="n">
+      <c r="I4" s="10" t="n">
         <v>696016</v>
       </c>
-      <c r="H4" s="10" t="n">
+      <c r="J4" s="10" t="n">
         <v>209533</v>
       </c>
-      <c r="I4" s="10" t="n">
+      <c r="K4" s="10" t="n">
         <v>115718</v>
       </c>
-      <c r="J4" s="10" t="n">
+      <c r="L4" s="10" t="n">
         <v>359914</v>
       </c>
-      <c r="K4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="10" t="n">
+      <c r="M4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="10" t="n">
         <v>80115</v>
       </c>
-      <c r="M4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="O4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="10" t="n">
         <v>615550</v>
       </c>
-      <c r="P4" s="10" t="n">
+      <c r="R4" s="10" t="n">
         <v>65180</v>
       </c>
-      <c r="Q4" s="10" t="n">
+      <c r="S4" s="10" t="n">
         <v>11130</v>
       </c>
-      <c r="R4" s="10" t="n">
+      <c r="T4" s="10" t="n">
         <v>73420</v>
       </c>
-      <c r="S4" s="10" t="n">
+      <c r="U4" s="10" t="n">
         <v>113</v>
       </c>
-      <c r="T4" s="10" t="n">
+      <c r="V4" s="10" t="n">
         <v>62</v>
       </c>
-      <c r="U4" s="10" t="n">
+      <c r="W4" s="10" t="n">
         <v>438470</v>
       </c>
-      <c r="V4" s="10" t="n">
+      <c r="X4" s="10" t="n">
         <v>326810</v>
       </c>
     </row>
@@ -812,55 +844,65 @@
           <t>祝</t>
         </is>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>曇</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>曇のち雨</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="n">
         <v>980555</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="I5" s="6" t="n">
         <v>891802</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="J5" s="6" t="n">
         <v>421724</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="K5" s="6" t="n">
         <v>240432</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="L5" s="6" t="n">
         <v>248934</v>
       </c>
-      <c r="K5" s="6" t="n">
+      <c r="M5" s="6" t="n">
         <v>26705</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="N5" s="6" t="n">
         <v>42760</v>
       </c>
-      <c r="M5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="O5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="6" t="n">
         <v>766130</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="R5" s="6" t="n">
         <v>100960</v>
       </c>
-      <c r="Q5" s="6" t="n">
+      <c r="S5" s="6" t="n">
         <v>12650</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="T5" s="6" t="n">
         <v>100815</v>
       </c>
-      <c r="S5" s="6" t="n">
+      <c r="U5" s="6" t="n">
         <v>155</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="V5" s="6" t="n">
         <v>62</v>
       </c>
-      <c r="U5" s="6" t="n">
+      <c r="W5" s="6" t="n">
         <v>545222</v>
       </c>
-      <c r="V5" s="6" t="n">
+      <c r="X5" s="6" t="n">
         <v>435333</v>
       </c>
     </row>
@@ -884,55 +926,65 @@
           <t>祝</t>
         </is>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>曇</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>曇時々雨</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="n">
         <v>674091</v>
       </c>
-      <c r="G6" s="10" t="n">
+      <c r="I6" s="10" t="n">
         <v>612910</v>
       </c>
-      <c r="H6" s="10" t="n">
+      <c r="J6" s="10" t="n">
         <v>249308</v>
       </c>
-      <c r="I6" s="10" t="n">
+      <c r="K6" s="10" t="n">
         <v>141596</v>
       </c>
-      <c r="J6" s="10" t="n">
+      <c r="L6" s="10" t="n">
         <v>181060</v>
       </c>
-      <c r="K6" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="10" t="n">
+      <c r="M6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="10" t="n">
         <v>102127</v>
       </c>
-      <c r="M6" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="O6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="10" t="n">
         <v>530470</v>
       </c>
-      <c r="P6" s="10" t="n">
+      <c r="R6" s="10" t="n">
         <v>88760</v>
       </c>
-      <c r="Q6" s="10" t="n">
+      <c r="S6" s="10" t="n">
         <v>2800</v>
       </c>
-      <c r="R6" s="10" t="n">
+      <c r="T6" s="10" t="n">
         <v>52061</v>
       </c>
-      <c r="S6" s="10" t="n">
+      <c r="U6" s="10" t="n">
         <v>101</v>
       </c>
-      <c r="T6" s="10" t="n">
+      <c r="V6" s="10" t="n">
         <v>58</v>
       </c>
-      <c r="U6" s="10" t="n">
+      <c r="W6" s="10" t="n">
         <v>312196</v>
       </c>
-      <c r="V6" s="10" t="n">
+      <c r="X6" s="10" t="n">
         <v>361895</v>
       </c>
     </row>
@@ -956,55 +1008,65 @@
           <t>祝</t>
         </is>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>曇</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>曇のち晴</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="n">
         <v>1166590</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="I7" s="6" t="n">
         <v>1060626</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="J7" s="6" t="n">
         <v>264278</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="K7" s="6" t="n">
         <v>409193</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="L7" s="6" t="n">
         <v>410274</v>
       </c>
-      <c r="K7" s="6" t="n">
+      <c r="M7" s="6" t="n">
         <v>68245</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="N7" s="6" t="n">
         <v>14600</v>
       </c>
-      <c r="M7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="O7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="6" t="n">
         <v>952030</v>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="R7" s="6" t="n">
         <v>97280</v>
       </c>
-      <c r="Q7" s="6" t="n">
+      <c r="S7" s="6" t="n">
         <v>3420</v>
       </c>
-      <c r="R7" s="6" t="n">
+      <c r="T7" s="6" t="n">
         <v>113860</v>
       </c>
-      <c r="S7" s="6" t="n">
+      <c r="U7" s="6" t="n">
         <v>151</v>
       </c>
-      <c r="T7" s="6" t="n">
+      <c r="V7" s="6" t="n">
         <v>95</v>
       </c>
-      <c r="U7" s="6" t="n">
+      <c r="W7" s="6" t="n">
         <v>560265</v>
       </c>
-      <c r="V7" s="6" t="n">
+      <c r="X7" s="6" t="n">
         <v>606325</v>
       </c>
     </row>
@@ -1028,55 +1090,65 @@
           <t>振</t>
         </is>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="n">
         <v>457199</v>
       </c>
-      <c r="G8" s="10" t="n">
+      <c r="I8" s="10" t="n">
         <v>415759</v>
       </c>
-      <c r="H8" s="10" t="n">
+      <c r="J8" s="10" t="n">
         <v>265539</v>
       </c>
-      <c r="I8" s="10" t="n">
+      <c r="K8" s="10" t="n">
         <v>48837</v>
       </c>
-      <c r="J8" s="10" t="n">
+      <c r="L8" s="10" t="n">
         <v>120495</v>
       </c>
-      <c r="K8" s="10" t="n">
+      <c r="M8" s="10" t="n">
         <v>4900</v>
       </c>
-      <c r="L8" s="10" t="n">
+      <c r="N8" s="10" t="n">
         <v>17428</v>
       </c>
-      <c r="M8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="O8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="10" t="n">
         <v>344540</v>
       </c>
-      <c r="P8" s="10" t="n">
+      <c r="R8" s="10" t="n">
         <v>79940</v>
       </c>
-      <c r="Q8" s="10" t="n">
+      <c r="S8" s="10" t="n">
         <v>2100</v>
       </c>
-      <c r="R8" s="10" t="n">
+      <c r="T8" s="10" t="n">
         <v>30619</v>
       </c>
-      <c r="S8" s="10" t="n">
+      <c r="U8" s="10" t="n">
         <v>95</v>
       </c>
-      <c r="T8" s="10" t="n">
+      <c r="V8" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="U8" s="10" t="n">
+      <c r="W8" s="10" t="n">
         <v>311799</v>
       </c>
-      <c r="V8" s="10" t="n">
+      <c r="X8" s="10" t="n">
         <v>145400</v>
       </c>
     </row>
@@ -1100,11 +1172,15 @@
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr"/>
-      <c r="F9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>0</v>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>曇</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>曇一時雨</t>
+        </is>
       </c>
       <c r="H9" s="6" t="n">
         <v>0</v>
@@ -1149,6 +1225,12 @@
         <v>0</v>
       </c>
       <c r="V9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1168,55 +1250,65 @@
       </c>
       <c r="D10" s="9" t="inlineStr"/>
       <c r="E10" s="9" t="inlineStr"/>
-      <c r="F10" s="10" t="n">
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>曇</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>曇</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="n">
         <v>486530</v>
       </c>
-      <c r="G10" s="10" t="n">
+      <c r="I10" s="10" t="n">
         <v>442430</v>
       </c>
-      <c r="H10" s="10" t="n">
+      <c r="J10" s="10" t="n">
         <v>218257</v>
       </c>
-      <c r="I10" s="10" t="n">
+      <c r="K10" s="10" t="n">
         <v>88404</v>
       </c>
-      <c r="J10" s="10" t="n">
+      <c r="L10" s="10" t="n">
         <v>156661</v>
       </c>
-      <c r="K10" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="10" t="n">
+      <c r="M10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="10" t="n">
         <v>23208</v>
       </c>
-      <c r="M10" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="O10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="10" t="n">
         <v>357990</v>
       </c>
-      <c r="P10" s="10" t="n">
+      <c r="R10" s="10" t="n">
         <v>67600</v>
       </c>
-      <c r="Q10" s="10" t="n">
+      <c r="S10" s="10" t="n">
         <v>1500</v>
       </c>
-      <c r="R10" s="10" t="n">
+      <c r="T10" s="10" t="n">
         <v>59440</v>
       </c>
-      <c r="S10" s="10" t="n">
+      <c r="U10" s="10" t="n">
         <v>62</v>
       </c>
-      <c r="T10" s="10" t="n">
+      <c r="V10" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="U10" s="10" t="n">
+      <c r="W10" s="10" t="n">
         <v>275206</v>
       </c>
-      <c r="V10" s="10" t="n">
+      <c r="X10" s="10" t="n">
         <v>211324</v>
       </c>
     </row>
@@ -1236,55 +1328,65 @@
       </c>
       <c r="D11" s="5" t="inlineStr"/>
       <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>曇</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>曇のち晴</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="n">
         <v>833405</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="I11" s="6" t="n">
         <v>758053</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="J11" s="6" t="n">
         <v>147213</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="K11" s="6" t="n">
         <v>342521</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="L11" s="6" t="n">
         <v>218549</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="M11" s="6" t="n">
         <v>24594</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="N11" s="6" t="n">
         <v>100528</v>
       </c>
-      <c r="M11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="O11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="6" t="n">
         <v>605600</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="R11" s="6" t="n">
         <v>113960</v>
       </c>
-      <c r="Q11" s="6" t="n">
+      <c r="S11" s="6" t="n">
         <v>11000</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="T11" s="6" t="n">
         <v>102845</v>
       </c>
-      <c r="S11" s="6" t="n">
+      <c r="U11" s="6" t="n">
         <v>78</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="V11" s="6" t="n">
         <v>84</v>
       </c>
-      <c r="U11" s="6" t="n">
+      <c r="W11" s="6" t="n">
         <v>241664</v>
       </c>
-      <c r="V11" s="6" t="n">
+      <c r="X11" s="6" t="n">
         <v>591741</v>
       </c>
     </row>
@@ -1304,55 +1406,65 @@
       </c>
       <c r="D12" s="9" t="inlineStr"/>
       <c r="E12" s="9" t="inlineStr"/>
-      <c r="F12" s="10" t="n">
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="n">
         <v>649148</v>
       </c>
-      <c r="G12" s="10" t="n">
+      <c r="I12" s="10" t="n">
         <v>591125</v>
       </c>
-      <c r="H12" s="10" t="n">
+      <c r="J12" s="10" t="n">
         <v>443278</v>
       </c>
-      <c r="I12" s="10" t="n">
+      <c r="K12" s="10" t="n">
         <v>43819</v>
       </c>
-      <c r="J12" s="10" t="n">
+      <c r="L12" s="10" t="n">
         <v>88768</v>
       </c>
-      <c r="K12" s="10" t="n">
+      <c r="M12" s="10" t="n">
         <v>21939</v>
       </c>
-      <c r="L12" s="10" t="n">
+      <c r="N12" s="10" t="n">
         <v>51344</v>
       </c>
-      <c r="M12" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="O12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="10" t="n">
         <v>490610</v>
       </c>
-      <c r="P12" s="10" t="n">
+      <c r="R12" s="10" t="n">
         <v>52770</v>
       </c>
-      <c r="Q12" s="10" t="n">
+      <c r="S12" s="10" t="n">
         <v>14000</v>
       </c>
-      <c r="R12" s="10" t="n">
+      <c r="T12" s="10" t="n">
         <v>91768</v>
       </c>
-      <c r="S12" s="10" t="n">
+      <c r="U12" s="10" t="n">
         <v>121</v>
       </c>
-      <c r="T12" s="10" t="n">
+      <c r="V12" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="U12" s="10" t="n">
+      <c r="W12" s="10" t="n">
         <v>452742</v>
       </c>
-      <c r="V12" s="10" t="n">
+      <c r="X12" s="10" t="n">
         <v>196406</v>
       </c>
     </row>
@@ -1376,11 +1488,15 @@
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr"/>
-      <c r="F13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>0</v>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
       </c>
       <c r="H13" s="6" t="n">
         <v>0</v>
@@ -1425,6 +1541,12 @@
         <v>0</v>
       </c>
       <c r="V13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1444,55 +1566,65 @@
       </c>
       <c r="D14" s="9" t="inlineStr"/>
       <c r="E14" s="9" t="inlineStr"/>
-      <c r="F14" s="10" t="n">
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="n">
         <v>800419</v>
       </c>
-      <c r="G14" s="10" t="n">
+      <c r="I14" s="10" t="n">
         <v>730315</v>
       </c>
-      <c r="H14" s="10" t="n">
+      <c r="J14" s="10" t="n">
         <v>533858</v>
       </c>
-      <c r="I14" s="10" t="n">
+      <c r="K14" s="10" t="n">
         <v>52935</v>
       </c>
-      <c r="J14" s="10" t="n">
+      <c r="L14" s="10" t="n">
         <v>92720</v>
       </c>
-      <c r="K14" s="10" t="n">
+      <c r="M14" s="10" t="n">
         <v>30590</v>
       </c>
-      <c r="L14" s="10" t="n">
+      <c r="N14" s="10" t="n">
         <v>55756</v>
       </c>
-      <c r="M14" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="10" t="n">
+      <c r="O14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="10" t="n">
         <v>34560</v>
       </c>
-      <c r="O14" s="10" t="n">
+      <c r="Q14" s="10" t="n">
         <v>532270</v>
       </c>
-      <c r="P14" s="10" t="n">
+      <c r="R14" s="10" t="n">
         <v>81340</v>
       </c>
-      <c r="Q14" s="10" t="n">
+      <c r="S14" s="10" t="n">
         <v>4900</v>
       </c>
-      <c r="R14" s="10" t="n">
+      <c r="T14" s="10" t="n">
         <v>181909</v>
       </c>
-      <c r="S14" s="10" t="n">
+      <c r="U14" s="10" t="n">
         <v>72</v>
       </c>
-      <c r="T14" s="10" t="n">
+      <c r="V14" s="10" t="n">
         <v>148</v>
       </c>
-      <c r="U14" s="10" t="n">
+      <c r="W14" s="10" t="n">
         <v>264150</v>
       </c>
-      <c r="V14" s="10" t="n">
+      <c r="X14" s="10" t="n">
         <v>536269</v>
       </c>
     </row>
@@ -1512,55 +1644,65 @@
       </c>
       <c r="D15" s="5" t="inlineStr"/>
       <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="6" t="n">
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>晴のち曇</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="n">
         <v>639456</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="I15" s="6" t="n">
         <v>581484</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="J15" s="6" t="n">
         <v>198301</v>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="K15" s="6" t="n">
         <v>126708</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="L15" s="6" t="n">
         <v>129461</v>
       </c>
-      <c r="K15" s="6" t="n">
+      <c r="M15" s="6" t="n">
         <v>5148</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="N15" s="6" t="n">
         <v>25031</v>
       </c>
-      <c r="M15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="6" t="n">
+      <c r="O15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="6" t="n">
         <v>154807</v>
       </c>
-      <c r="O15" s="6" t="n">
+      <c r="Q15" s="6" t="n">
         <v>478020</v>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="R15" s="6" t="n">
         <v>84710</v>
       </c>
-      <c r="Q15" s="6" t="n">
+      <c r="S15" s="6" t="n">
         <v>7000</v>
       </c>
-      <c r="R15" s="6" t="n">
+      <c r="T15" s="6" t="n">
         <v>69726</v>
       </c>
-      <c r="S15" s="6" t="n">
+      <c r="U15" s="6" t="n">
         <v>74</v>
       </c>
-      <c r="T15" s="6" t="n">
+      <c r="V15" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="U15" s="6" t="n">
+      <c r="W15" s="6" t="n">
         <v>219079</v>
       </c>
-      <c r="V15" s="6" t="n">
+      <c r="X15" s="6" t="n">
         <v>420377</v>
       </c>
     </row>
@@ -1580,55 +1722,65 @@
       </c>
       <c r="D16" s="9" t="inlineStr"/>
       <c r="E16" s="9" t="inlineStr"/>
-      <c r="F16" s="10" t="n">
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>曇</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>曇</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="n">
         <v>855834</v>
       </c>
-      <c r="G16" s="10" t="n">
+      <c r="I16" s="10" t="n">
         <v>778282</v>
       </c>
-      <c r="H16" s="10" t="n">
+      <c r="J16" s="10" t="n">
         <v>576310</v>
       </c>
-      <c r="I16" s="10" t="n">
+      <c r="K16" s="10" t="n">
         <v>118397</v>
       </c>
-      <c r="J16" s="10" t="n">
+      <c r="L16" s="10" t="n">
         <v>134247</v>
       </c>
-      <c r="K16" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="10" t="n">
+      <c r="M16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="10" t="n">
         <v>26880</v>
       </c>
-      <c r="M16" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="O16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="10" t="n">
         <v>611540</v>
       </c>
-      <c r="P16" s="10" t="n">
+      <c r="R16" s="10" t="n">
         <v>148470</v>
       </c>
-      <c r="Q16" s="10" t="n">
+      <c r="S16" s="10" t="n">
         <v>17792</v>
       </c>
-      <c r="R16" s="10" t="n">
+      <c r="T16" s="10" t="n">
         <v>78032</v>
       </c>
-      <c r="S16" s="10" t="n">
+      <c r="U16" s="10" t="n">
         <v>94</v>
       </c>
-      <c r="T16" s="10" t="n">
+      <c r="V16" s="10" t="n">
         <v>44</v>
       </c>
-      <c r="U16" s="10" t="n">
+      <c r="W16" s="10" t="n">
         <v>415078</v>
       </c>
-      <c r="V16" s="10" t="n">
+      <c r="X16" s="10" t="n">
         <v>440756</v>
       </c>
     </row>
@@ -1648,55 +1800,65 @@
       </c>
       <c r="D17" s="5" t="inlineStr"/>
       <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="6" t="n">
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>曇</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>曇のち晴</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="n">
         <v>890323</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="I17" s="6" t="n">
         <v>809403</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="J17" s="6" t="n">
         <v>28994</v>
       </c>
-      <c r="I17" s="6" t="n">
+      <c r="K17" s="6" t="n">
         <v>335459</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="L17" s="6" t="n">
         <v>513132</v>
       </c>
-      <c r="K17" s="6" t="n">
+      <c r="M17" s="6" t="n">
         <v>4900</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="N17" s="6" t="n">
         <v>7838</v>
       </c>
-      <c r="M17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="O17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="6" t="n">
         <v>642970</v>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="R17" s="6" t="n">
         <v>165370</v>
       </c>
-      <c r="Q17" s="6" t="n">
+      <c r="S17" s="6" t="n">
         <v>700</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="T17" s="6" t="n">
         <v>81283</v>
       </c>
-      <c r="S17" s="6" t="n">
+      <c r="U17" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="V17" s="6" t="n">
         <v>99</v>
       </c>
-      <c r="U17" s="6" t="n">
+      <c r="W17" s="6" t="n">
         <v>106190</v>
       </c>
-      <c r="V17" s="6" t="n">
+      <c r="X17" s="6" t="n">
         <v>784133</v>
       </c>
     </row>
@@ -1716,55 +1878,65 @@
       </c>
       <c r="D18" s="9" t="inlineStr"/>
       <c r="E18" s="9" t="inlineStr"/>
-      <c r="F18" s="10" t="n">
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="n">
         <v>1008132</v>
       </c>
-      <c r="G18" s="10" t="n">
+      <c r="I18" s="10" t="n">
         <v>917550</v>
       </c>
-      <c r="H18" s="10" t="n">
+      <c r="J18" s="10" t="n">
         <v>629414</v>
       </c>
-      <c r="I18" s="10" t="n">
+      <c r="K18" s="10" t="n">
         <v>62580</v>
       </c>
-      <c r="J18" s="10" t="n">
+      <c r="L18" s="10" t="n">
         <v>281876</v>
       </c>
-      <c r="K18" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="10" t="n">
+      <c r="M18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="10" t="n">
         <v>34262</v>
       </c>
-      <c r="M18" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="O18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="10" t="n">
         <v>734500</v>
       </c>
-      <c r="P18" s="10" t="n">
+      <c r="R18" s="10" t="n">
         <v>121570</v>
       </c>
-      <c r="Q18" s="10" t="n">
+      <c r="S18" s="10" t="n">
         <v>49100</v>
       </c>
-      <c r="R18" s="10" t="n">
+      <c r="T18" s="10" t="n">
         <v>102962</v>
       </c>
-      <c r="S18" s="10" t="n">
+      <c r="U18" s="10" t="n">
         <v>197</v>
       </c>
-      <c r="T18" s="10" t="n">
+      <c r="V18" s="10" t="n">
         <v>56</v>
       </c>
-      <c r="U18" s="10" t="n">
+      <c r="W18" s="10" t="n">
         <v>497480</v>
       </c>
-      <c r="V18" s="10" t="n">
+      <c r="X18" s="10" t="n">
         <v>510652</v>
       </c>
     </row>
@@ -1784,55 +1956,65 @@
       </c>
       <c r="D19" s="5" t="inlineStr"/>
       <c r="E19" s="5" t="inlineStr"/>
-      <c r="F19" s="6" t="n">
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="n">
         <v>836061</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="I19" s="6" t="n">
         <v>760517</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="J19" s="6" t="n">
         <v>469044</v>
       </c>
-      <c r="I19" s="6" t="n">
+      <c r="K19" s="6" t="n">
         <v>122711</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="L19" s="6" t="n">
         <v>207963</v>
       </c>
-      <c r="K19" s="6" t="n">
+      <c r="M19" s="6" t="n">
         <v>10800</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="N19" s="6" t="n">
         <v>25540</v>
       </c>
-      <c r="M19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="O19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="6" t="n">
         <v>622570</v>
       </c>
-      <c r="P19" s="6" t="n">
+      <c r="R19" s="6" t="n">
         <v>128580</v>
       </c>
-      <c r="Q19" s="6" t="n">
+      <c r="S19" s="6" t="n">
         <v>14750</v>
       </c>
-      <c r="R19" s="6" t="n">
+      <c r="T19" s="6" t="n">
         <v>70161</v>
       </c>
-      <c r="S19" s="6" t="n">
+      <c r="U19" s="6" t="n">
         <v>179</v>
       </c>
-      <c r="T19" s="6" t="n">
+      <c r="V19" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="U19" s="6" t="n">
+      <c r="W19" s="6" t="n">
         <v>559411</v>
       </c>
-      <c r="V19" s="6" t="n">
+      <c r="X19" s="6" t="n">
         <v>276650</v>
       </c>
     </row>
@@ -1856,11 +2038,15 @@
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr"/>
-      <c r="F20" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="10" t="n">
-        <v>0</v>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
       </c>
       <c r="H20" s="10" t="n">
         <v>0</v>
@@ -1905,6 +2091,12 @@
         <v>0</v>
       </c>
       <c r="V20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1924,55 +2116,65 @@
       </c>
       <c r="D21" s="5" t="inlineStr"/>
       <c r="E21" s="5" t="inlineStr"/>
-      <c r="F21" s="6" t="n">
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>晴のち曇</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="n">
         <v>656558</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="I21" s="6" t="n">
         <v>596921</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="J21" s="6" t="n">
         <v>221169</v>
       </c>
-      <c r="I21" s="6" t="n">
+      <c r="K21" s="6" t="n">
         <v>171740</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="L21" s="6" t="n">
         <v>69682</v>
       </c>
-      <c r="K21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="6" t="n">
+      <c r="M21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="6" t="n">
         <v>32930</v>
       </c>
-      <c r="M21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="6" t="n">
+      <c r="O21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="6" t="n">
         <v>161037</v>
       </c>
-      <c r="O21" s="6" t="n">
+      <c r="Q21" s="6" t="n">
         <v>457120</v>
       </c>
-      <c r="P21" s="6" t="n">
+      <c r="R21" s="6" t="n">
         <v>93190</v>
       </c>
-      <c r="Q21" s="6" t="n">
+      <c r="S21" s="6" t="n">
         <v>2100</v>
       </c>
-      <c r="R21" s="6" t="n">
+      <c r="T21" s="6" t="n">
         <v>104148</v>
       </c>
-      <c r="S21" s="6" t="n">
+      <c r="U21" s="6" t="n">
         <v>61</v>
       </c>
-      <c r="T21" s="6" t="n">
+      <c r="V21" s="6" t="n">
         <v>37</v>
       </c>
-      <c r="U21" s="6" t="n">
+      <c r="W21" s="6" t="n">
         <v>189226</v>
       </c>
-      <c r="V21" s="6" t="n">
+      <c r="X21" s="6" t="n">
         <v>467332</v>
       </c>
     </row>
@@ -1992,55 +2194,65 @@
       </c>
       <c r="D22" s="9" t="inlineStr"/>
       <c r="E22" s="9" t="inlineStr"/>
-      <c r="F22" s="10" t="n">
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>曇</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>曇のち雨</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="n">
         <v>322120</v>
       </c>
-      <c r="G22" s="10" t="n">
+      <c r="I22" s="10" t="n">
         <v>293087</v>
       </c>
-      <c r="H22" s="10" t="n">
+      <c r="J22" s="10" t="n">
         <v>147756</v>
       </c>
-      <c r="I22" s="10" t="n">
+      <c r="K22" s="10" t="n">
         <v>36099</v>
       </c>
-      <c r="J22" s="10" t="n">
+      <c r="L22" s="10" t="n">
         <v>63308</v>
       </c>
-      <c r="K22" s="10" t="n">
+      <c r="M22" s="10" t="n">
         <v>59279</v>
       </c>
-      <c r="L22" s="10" t="n">
+      <c r="N22" s="10" t="n">
         <v>15678</v>
       </c>
-      <c r="M22" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="O22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="10" t="n">
         <v>231040</v>
       </c>
-      <c r="P22" s="10" t="n">
+      <c r="R22" s="10" t="n">
         <v>54270</v>
       </c>
-      <c r="Q22" s="10" t="n">
+      <c r="S22" s="10" t="n">
         <v>1400</v>
       </c>
-      <c r="R22" s="10" t="n">
+      <c r="T22" s="10" t="n">
         <v>35410</v>
       </c>
-      <c r="S22" s="10" t="n">
+      <c r="U22" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="T22" s="10" t="n">
+      <c r="V22" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="U22" s="10" t="n">
+      <c r="W22" s="10" t="n">
         <v>186595</v>
       </c>
-      <c r="V22" s="10" t="n">
+      <c r="X22" s="10" t="n">
         <v>135525</v>
       </c>
     </row>
@@ -2060,55 +2272,65 @@
       </c>
       <c r="D23" s="5" t="inlineStr"/>
       <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="6" t="n">
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>雨</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>雨</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="n">
         <v>851000</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="I23" s="6" t="n">
         <v>773884</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="J23" s="6" t="n">
         <v>506886</v>
       </c>
-      <c r="I23" s="6" t="n">
+      <c r="K23" s="6" t="n">
         <v>152221</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="L23" s="6" t="n">
         <v>149626</v>
       </c>
-      <c r="K23" s="6" t="n">
+      <c r="M23" s="6" t="n">
         <v>7326</v>
       </c>
-      <c r="L23" s="6" t="n">
+      <c r="N23" s="6" t="n">
         <v>34941</v>
       </c>
-      <c r="M23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="O23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="6" t="n">
         <v>448340</v>
       </c>
-      <c r="P23" s="6" t="n">
+      <c r="R23" s="6" t="n">
         <v>341560</v>
       </c>
-      <c r="Q23" s="6" t="n">
+      <c r="S23" s="6" t="n">
         <v>4250</v>
       </c>
-      <c r="R23" s="6" t="n">
+      <c r="T23" s="6" t="n">
         <v>56850</v>
       </c>
-      <c r="S23" s="6" t="n">
+      <c r="U23" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="T23" s="6" t="n">
+      <c r="V23" s="6" t="n">
         <v>53</v>
       </c>
-      <c r="U23" s="6" t="n">
+      <c r="W23" s="6" t="n">
         <v>153613</v>
       </c>
-      <c r="V23" s="6" t="n">
+      <c r="X23" s="6" t="n">
         <v>697387</v>
       </c>
     </row>
@@ -2128,55 +2350,65 @@
       </c>
       <c r="D24" s="9" t="inlineStr"/>
       <c r="E24" s="9" t="inlineStr"/>
-      <c r="F24" s="10" t="n">
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>雨</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>雨のち曇</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="n">
         <v>958119</v>
       </c>
-      <c r="G24" s="10" t="n">
+      <c r="I24" s="10" t="n">
         <v>873275</v>
       </c>
-      <c r="H24" s="10" t="n">
+      <c r="J24" s="10" t="n">
         <v>233353</v>
       </c>
-      <c r="I24" s="10" t="n">
+      <c r="K24" s="10" t="n">
         <v>98106</v>
       </c>
-      <c r="J24" s="10" t="n">
+      <c r="L24" s="10" t="n">
         <v>111397</v>
       </c>
-      <c r="K24" s="10" t="n">
+      <c r="M24" s="10" t="n">
         <v>13270</v>
       </c>
-      <c r="L24" s="10" t="n">
+      <c r="N24" s="10" t="n">
         <v>107372</v>
       </c>
-      <c r="M24" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="10" t="n">
+      <c r="O24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="10" t="n">
         <v>394621</v>
       </c>
-      <c r="O24" s="10" t="n">
+      <c r="Q24" s="10" t="n">
         <v>497210</v>
       </c>
-      <c r="P24" s="10" t="n">
+      <c r="R24" s="10" t="n">
         <v>140240</v>
       </c>
-      <c r="Q24" s="10" t="n">
+      <c r="S24" s="10" t="n">
         <v>13468</v>
       </c>
-      <c r="R24" s="10" t="n">
+      <c r="T24" s="10" t="n">
         <v>307201</v>
       </c>
-      <c r="S24" s="10" t="n">
+      <c r="U24" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="T24" s="10" t="n">
+      <c r="V24" s="10" t="n">
         <v>92</v>
       </c>
-      <c r="U24" s="10" t="n">
+      <c r="W24" s="10" t="n">
         <v>369696</v>
       </c>
-      <c r="V24" s="10" t="n">
+      <c r="X24" s="10" t="n">
         <v>588423</v>
       </c>
     </row>
@@ -2196,55 +2428,65 @@
       </c>
       <c r="D25" s="5" t="inlineStr"/>
       <c r="E25" s="5" t="inlineStr"/>
-      <c r="F25" s="6" t="n">
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>曇</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>曇</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="n">
         <v>907553</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="I25" s="6" t="n">
         <v>825217</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="J25" s="6" t="n">
         <v>425649</v>
       </c>
-      <c r="I25" s="6" t="n">
+      <c r="K25" s="6" t="n">
         <v>18397</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="L25" s="6" t="n">
         <v>460079</v>
       </c>
-      <c r="K25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="6" t="n">
+      <c r="M25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="6" t="n">
         <v>14875</v>
       </c>
-      <c r="M25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="O25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="6" t="n">
         <v>688450</v>
       </c>
-      <c r="P25" s="6" t="n">
+      <c r="R25" s="6" t="n">
         <v>116280</v>
       </c>
-      <c r="Q25" s="6" t="n">
+      <c r="S25" s="6" t="n">
         <v>5850</v>
       </c>
-      <c r="R25" s="6" t="n">
+      <c r="T25" s="6" t="n">
         <v>96973</v>
       </c>
-      <c r="S25" s="6" t="n">
+      <c r="U25" s="6" t="n">
         <v>127</v>
       </c>
-      <c r="T25" s="6" t="n">
+      <c r="V25" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="U25" s="6" t="n">
+      <c r="W25" s="6" t="n">
         <v>608118</v>
       </c>
-      <c r="V25" s="6" t="n">
+      <c r="X25" s="6" t="n">
         <v>299435</v>
       </c>
     </row>
@@ -2264,55 +2506,65 @@
       </c>
       <c r="D26" s="9" t="inlineStr"/>
       <c r="E26" s="9" t="inlineStr"/>
-      <c r="F26" s="10" t="n">
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>曇</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>曇一時雨</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="n">
         <v>929773</v>
       </c>
-      <c r="G26" s="10" t="n">
+      <c r="I26" s="10" t="n">
         <v>845640</v>
       </c>
-      <c r="H26" s="10" t="n">
+      <c r="J26" s="10" t="n">
         <v>367866</v>
       </c>
-      <c r="I26" s="10" t="n">
+      <c r="K26" s="10" t="n">
         <v>139264</v>
       </c>
-      <c r="J26" s="10" t="n">
+      <c r="L26" s="10" t="n">
         <v>245824</v>
       </c>
-      <c r="K26" s="10" t="n">
+      <c r="M26" s="10" t="n">
         <v>97990</v>
       </c>
-      <c r="L26" s="10" t="n">
+      <c r="N26" s="10" t="n">
         <v>36112</v>
       </c>
-      <c r="M26" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="10" t="n">
+      <c r="O26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="10" t="n">
         <v>42717</v>
       </c>
-      <c r="O26" s="10" t="n">
+      <c r="Q26" s="10" t="n">
         <v>718850</v>
       </c>
-      <c r="P26" s="10" t="n">
+      <c r="R26" s="10" t="n">
         <v>104590</v>
       </c>
-      <c r="Q26" s="10" t="n">
+      <c r="S26" s="10" t="n">
         <v>2100</v>
       </c>
-      <c r="R26" s="10" t="n">
+      <c r="T26" s="10" t="n">
         <v>104233</v>
       </c>
-      <c r="S26" s="10" t="n">
+      <c r="U26" s="10" t="n">
         <v>152</v>
       </c>
-      <c r="T26" s="10" t="n">
+      <c r="V26" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="U26" s="10" t="n">
+      <c r="W26" s="10" t="n">
         <v>540889</v>
       </c>
-      <c r="V26" s="10" t="n">
+      <c r="X26" s="10" t="n">
         <v>388884</v>
       </c>
     </row>
@@ -2336,11 +2588,15 @@
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr"/>
-      <c r="F27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="6" t="n">
-        <v>0</v>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>曇</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>曇時々晴</t>
+        </is>
       </c>
       <c r="H27" s="6" t="n">
         <v>0</v>
@@ -2385,6 +2641,12 @@
         <v>0</v>
       </c>
       <c r="V27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2404,55 +2666,65 @@
       </c>
       <c r="D28" s="9" t="inlineStr"/>
       <c r="E28" s="9" t="inlineStr"/>
-      <c r="F28" s="10" t="n">
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>曇</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>曇</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="n">
         <v>437884</v>
       </c>
-      <c r="G28" s="10" t="n">
+      <c r="I28" s="10" t="n">
         <v>398268</v>
       </c>
-      <c r="H28" s="10" t="n">
+      <c r="J28" s="10" t="n">
         <v>190643</v>
       </c>
-      <c r="I28" s="10" t="n">
+      <c r="K28" s="10" t="n">
         <v>126632</v>
       </c>
-      <c r="J28" s="10" t="n">
+      <c r="L28" s="10" t="n">
         <v>92512</v>
       </c>
-      <c r="K28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="10" t="n">
+      <c r="M28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="10" t="n">
         <v>28097</v>
       </c>
-      <c r="M28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="O28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="10" t="n">
         <v>354010</v>
       </c>
-      <c r="P28" s="10" t="n">
+      <c r="R28" s="10" t="n">
         <v>47010</v>
       </c>
-      <c r="Q28" s="10" t="n">
+      <c r="S28" s="10" t="n">
         <v>3050</v>
       </c>
-      <c r="R28" s="10" t="n">
+      <c r="T28" s="10" t="n">
         <v>33814</v>
       </c>
-      <c r="S28" s="10" t="n">
+      <c r="U28" s="10" t="n">
         <v>85</v>
       </c>
-      <c r="T28" s="10" t="n">
+      <c r="V28" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="U28" s="10" t="n">
+      <c r="W28" s="10" t="n">
         <v>329787</v>
       </c>
-      <c r="V28" s="10" t="n">
+      <c r="X28" s="10" t="n">
         <v>108097</v>
       </c>
     </row>
@@ -2472,55 +2744,65 @@
       </c>
       <c r="D29" s="5" t="inlineStr"/>
       <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="6" t="n">
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>曇</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>曇</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="n">
         <v>823370</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="I29" s="6" t="n">
         <v>749518</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="J29" s="6" t="n">
         <v>266045</v>
       </c>
-      <c r="I29" s="6" t="n">
+      <c r="K29" s="6" t="n">
         <v>50914</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="L29" s="6" t="n">
         <v>369086</v>
       </c>
-      <c r="K29" s="6" t="n">
+      <c r="M29" s="6" t="n">
         <v>114617</v>
       </c>
-      <c r="L29" s="6" t="n">
+      <c r="N29" s="6" t="n">
         <v>22708</v>
       </c>
-      <c r="M29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="O29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="6" t="n">
         <v>546240</v>
       </c>
-      <c r="P29" s="6" t="n">
+      <c r="R29" s="6" t="n">
         <v>128890</v>
       </c>
-      <c r="Q29" s="6" t="n">
+      <c r="S29" s="6" t="n">
         <v>6800</v>
       </c>
-      <c r="R29" s="6" t="n">
+      <c r="T29" s="6" t="n">
         <v>141440</v>
       </c>
-      <c r="S29" s="6" t="n">
+      <c r="U29" s="6" t="n">
         <v>127</v>
       </c>
-      <c r="T29" s="6" t="n">
+      <c r="V29" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="U29" s="6" t="n">
+      <c r="W29" s="6" t="n">
         <v>343996</v>
       </c>
-      <c r="V29" s="6" t="n">
+      <c r="X29" s="6" t="n">
         <v>479374</v>
       </c>
     </row>
@@ -2540,55 +2822,65 @@
       </c>
       <c r="D30" s="9" t="inlineStr"/>
       <c r="E30" s="9" t="inlineStr"/>
-      <c r="F30" s="10" t="n">
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>曇</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>曇</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="n">
         <v>484499</v>
       </c>
-      <c r="G30" s="10" t="n">
+      <c r="I30" s="10" t="n">
         <v>440484</v>
       </c>
-      <c r="H30" s="10" t="n">
+      <c r="J30" s="10" t="n">
         <v>145770</v>
       </c>
-      <c r="I30" s="10" t="n">
+      <c r="K30" s="10" t="n">
         <v>97078</v>
       </c>
-      <c r="J30" s="10" t="n">
+      <c r="L30" s="10" t="n">
         <v>226823</v>
       </c>
-      <c r="K30" s="10" t="n">
+      <c r="M30" s="10" t="n">
         <v>2400</v>
       </c>
-      <c r="L30" s="10" t="n">
+      <c r="N30" s="10" t="n">
         <v>12428</v>
       </c>
-      <c r="M30" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="O30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="10" t="n">
         <v>265060</v>
       </c>
-      <c r="P30" s="10" t="n">
+      <c r="R30" s="10" t="n">
         <v>82100</v>
       </c>
-      <c r="Q30" s="10" t="n">
+      <c r="S30" s="10" t="n">
         <v>1400</v>
       </c>
-      <c r="R30" s="10" t="n">
+      <c r="T30" s="10" t="n">
         <v>135939</v>
       </c>
-      <c r="S30" s="10" t="n">
+      <c r="U30" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="T30" s="10" t="n">
+      <c r="V30" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="U30" s="10" t="n">
+      <c r="W30" s="10" t="n">
         <v>119351</v>
       </c>
-      <c r="V30" s="10" t="n">
+      <c r="X30" s="10" t="n">
         <v>365148</v>
       </c>
     </row>
@@ -2608,55 +2900,65 @@
       </c>
       <c r="D31" s="5" t="inlineStr"/>
       <c r="E31" s="5" t="inlineStr"/>
-      <c r="F31" s="6" t="n">
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>晴時々曇</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="n">
         <v>1312705</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="I31" s="6" t="n">
         <v>1196944</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="J31" s="6" t="n">
         <v>395202</v>
       </c>
-      <c r="I31" s="6" t="n">
+      <c r="K31" s="6" t="n">
         <v>540034</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="L31" s="6" t="n">
         <v>134814</v>
       </c>
-      <c r="K31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="6" t="n">
+      <c r="M31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="6" t="n">
         <v>3520</v>
       </c>
-      <c r="M31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="6" t="n">
+      <c r="O31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="6" t="n">
         <v>239135</v>
       </c>
-      <c r="O31" s="6" t="n">
+      <c r="Q31" s="6" t="n">
         <v>758930</v>
       </c>
-      <c r="P31" s="6" t="n">
+      <c r="R31" s="6" t="n">
         <v>222560</v>
       </c>
-      <c r="Q31" s="6" t="n">
+      <c r="S31" s="6" t="n">
         <v>8300</v>
       </c>
-      <c r="R31" s="6" t="n">
+      <c r="T31" s="6" t="n">
         <v>322915</v>
       </c>
-      <c r="S31" s="6" t="n">
+      <c r="U31" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="T31" s="6" t="n">
+      <c r="V31" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="U31" s="6" t="n">
+      <c r="W31" s="6" t="n">
         <v>440945</v>
       </c>
-      <c r="V31" s="6" t="n">
+      <c r="X31" s="6" t="n">
         <v>871760</v>
       </c>
     </row>
@@ -2676,55 +2978,65 @@
       </c>
       <c r="D32" s="9" t="inlineStr"/>
       <c r="E32" s="9" t="inlineStr"/>
-      <c r="F32" s="10" t="n">
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>晴</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>晴のち曇</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="n">
         <v>1076938</v>
       </c>
-      <c r="G32" s="10" t="n">
+      <c r="I32" s="10" t="n">
         <v>979348</v>
       </c>
-      <c r="H32" s="10" t="n">
+      <c r="J32" s="10" t="n">
         <v>455076</v>
       </c>
-      <c r="I32" s="10" t="n">
+      <c r="K32" s="10" t="n">
         <v>48048</v>
       </c>
-      <c r="J32" s="10" t="n">
+      <c r="L32" s="10" t="n">
         <v>342921</v>
       </c>
-      <c r="K32" s="10" t="n">
+      <c r="M32" s="10" t="n">
         <v>70373</v>
       </c>
-      <c r="L32" s="10" t="n">
+      <c r="N32" s="10" t="n">
         <v>62020</v>
       </c>
-      <c r="M32" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="10" t="n">
+      <c r="O32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="10" t="n">
         <v>98500</v>
       </c>
-      <c r="O32" s="10" t="n">
+      <c r="Q32" s="10" t="n">
         <v>826070</v>
       </c>
-      <c r="P32" s="10" t="n">
+      <c r="R32" s="10" t="n">
         <v>125410</v>
       </c>
-      <c r="Q32" s="10" t="n">
+      <c r="S32" s="10" t="n">
         <v>10500</v>
       </c>
-      <c r="R32" s="10" t="n">
+      <c r="T32" s="10" t="n">
         <v>114958</v>
       </c>
-      <c r="S32" s="10" t="n">
+      <c r="U32" s="10" t="n">
         <v>133</v>
       </c>
-      <c r="T32" s="10" t="n">
+      <c r="V32" s="10" t="n">
         <v>66</v>
       </c>
-      <c r="U32" s="10" t="n">
+      <c r="W32" s="10" t="n">
         <v>574140</v>
       </c>
-      <c r="V32" s="10" t="n">
+      <c r="X32" s="10" t="n">
         <v>502798</v>
       </c>
     </row>
@@ -2744,55 +3056,65 @@
       </c>
       <c r="D33" s="5" t="inlineStr"/>
       <c r="E33" s="5" t="inlineStr"/>
-      <c r="F33" s="6" t="n">
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>曇</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>曇のち晴</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="n">
         <v>686502</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="I33" s="6" t="n">
         <v>624614</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="J33" s="6" t="n">
         <v>470425</v>
       </c>
-      <c r="I33" s="6" t="n">
+      <c r="K33" s="6" t="n">
         <v>43053</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="L33" s="6" t="n">
         <v>121921</v>
       </c>
-      <c r="K33" s="6" t="n">
+      <c r="M33" s="6" t="n">
         <v>4800</v>
       </c>
-      <c r="L33" s="6" t="n">
+      <c r="N33" s="6" t="n">
         <v>46303</v>
       </c>
-      <c r="M33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="O33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="6" t="n">
         <v>520390</v>
       </c>
-      <c r="P33" s="6" t="n">
+      <c r="R33" s="6" t="n">
         <v>82680</v>
       </c>
-      <c r="Q33" s="6" t="n">
+      <c r="S33" s="6" t="n">
         <v>15400</v>
       </c>
-      <c r="R33" s="6" t="n">
+      <c r="T33" s="6" t="n">
         <v>68032</v>
       </c>
-      <c r="S33" s="6" t="n">
+      <c r="U33" s="6" t="n">
         <v>147</v>
       </c>
-      <c r="T33" s="6" t="n">
+      <c r="V33" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="U33" s="6" t="n">
+      <c r="W33" s="6" t="n">
         <v>479636</v>
       </c>
-      <c r="V33" s="6" t="n">
+      <c r="X33" s="6" t="n">
         <v>206866</v>
       </c>
     </row>
@@ -2802,62 +3124,62 @@
           <t>合 計</t>
         </is>
       </c>
-      <c r="F34" s="11" t="n">
+      <c r="H34" s="11" t="n">
         <v>20989657</v>
       </c>
-      <c r="G34" s="11" t="n">
+      <c r="I34" s="11" t="n">
         <v>19097801</v>
       </c>
-      <c r="H34" s="11" t="n">
+      <c r="J34" s="11" t="n">
         <v>8692051</v>
       </c>
-      <c r="I34" s="11" t="n">
+      <c r="K34" s="11" t="n">
         <v>3806445</v>
       </c>
-      <c r="J34" s="11" t="n">
+      <c r="L34" s="11" t="n">
         <v>5643149</v>
       </c>
-      <c r="K34" s="11" t="n">
+      <c r="M34" s="11" t="n">
         <v>567876</v>
       </c>
-      <c r="L34" s="11" t="n">
+      <c r="N34" s="11" t="n">
         <v>1076179</v>
       </c>
-      <c r="M34" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="11" t="n">
+      <c r="O34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="11" t="n">
         <v>1215401</v>
       </c>
-      <c r="O34" s="11" t="n">
+      <c r="Q34" s="11" t="n">
         <v>14975700</v>
       </c>
-      <c r="P34" s="11" t="n">
+      <c r="R34" s="11" t="n">
         <v>3000230</v>
       </c>
-      <c r="Q34" s="11" t="n">
+      <c r="S34" s="11" t="n">
         <v>230260</v>
       </c>
-      <c r="R34" s="11" t="n">
+      <c r="T34" s="11" t="n">
         <v>2783467</v>
       </c>
-      <c r="S34" s="11" t="n">
+      <c r="U34" s="11" t="n">
         <v>2520</v>
       </c>
-      <c r="T34" s="11" t="n">
+      <c r="V34" s="11" t="n">
         <v>1534</v>
       </c>
-      <c r="U34" s="11" t="n">
+      <c r="W34" s="11" t="n">
         <v>9681482</v>
       </c>
-      <c r="V34" s="11" t="n">
+      <c r="X34" s="11" t="n">
         <v>11308175</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A1:X1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/frontend/public/data/daily_2026_5.xlsx
+++ b/frontend/public/data/daily_2026_5.xlsx
@@ -519,7 +519,7 @@
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
@@ -574,12 +574,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>天気</t>
+          <t>昼天気</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>天気概況</t>
+          <t>夜天気</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>雨のち晴</t>
+          <t>晴</t>
         </is>
       </c>
       <c r="H3" s="6" t="n">
@@ -769,7 +769,7 @@
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>晴のち曇</t>
+          <t>曇</t>
         </is>
       </c>
       <c r="H4" s="10" t="n">
@@ -851,7 +851,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>曇のち雨</t>
+          <t>雨</t>
         </is>
       </c>
       <c r="H5" s="6" t="n">
@@ -933,7 +933,7 @@
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>曇時々雨</t>
+          <t>曇</t>
         </is>
       </c>
       <c r="H6" s="10" t="n">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>曇のち晴</t>
+          <t>晴</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>曇一時雨</t>
+          <t>曇</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>曇のち晴</t>
+          <t>晴</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>晴のち曇</t>
+          <t>曇</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>曇のち晴</t>
+          <t>晴</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>晴のち曇</t>
+          <t>曇</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>曇のち雨</t>
+          <t>雨</t>
         </is>
       </c>
       <c r="H22" s="10" t="n">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>雨のち曇</t>
+          <t>曇</t>
         </is>
       </c>
       <c r="H24" s="10" t="n">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>曇一時雨</t>
+          <t>曇</t>
         </is>
       </c>
       <c r="H26" s="10" t="n">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>曇時々晴</t>
+          <t>曇</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>晴時々曇</t>
+          <t>晴</t>
         </is>
       </c>
       <c r="H31" s="6" t="n">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>晴のち曇</t>
+          <t>曇</t>
         </is>
       </c>
       <c r="H32" s="10" t="n">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>曇のち晴</t>
+          <t>晴</t>
         </is>
       </c>
       <c r="H33" s="6" t="n">

--- a/frontend/public/data/daily_2026_5.xlsx
+++ b/frontend/public/data/daily_2026_5.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,55 +26,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="0000B4FF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="0000B4FF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <color rgb="00D0E8FF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="0000F5A0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FF9F1C"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0008123A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0004091F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00030718"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -82,69 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="000F2D4A"/>
-      </left>
-      <right style="thin">
-        <color rgb="000F2D4A"/>
-      </right>
-      <top style="thin">
-        <color rgb="000F2D4A"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000F2D4A"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -510,2677 +414,2225 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X34"/>
+  <dimension ref="A1:X33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="5" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>2026年5月 日次データ</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>曜日</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>定休</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>祝日</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>昼天気</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>夜天気</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>総売上高</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>純売上高</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>現金</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>JCB</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>千葉銀行</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>アクアコイン</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>PayPay</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>ふるさと納税</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>売掛金</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>FOOD</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>DRINK</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>売店</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>昼食客数</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>夕食客数</t>
         </is>
       </c>
-      <c r="W2" s="2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>昼食売上</t>
         </is>
       </c>
-      <c r="X2" s="2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>夕食売上</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026/05/01</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr"/>
-      <c r="E3" s="5" t="inlineStr"/>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>雨</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>晴</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="n">
+      <c r="H3" t="n">
         <v>499613</v>
       </c>
-      <c r="I3" s="6" t="n">
+      <c r="I3" t="n">
         <v>454329</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="J3" t="n">
         <v>211160</v>
       </c>
-      <c r="K3" s="6" t="n">
+      <c r="K3" t="n">
         <v>35549</v>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="L3" t="n">
         <v>111102</v>
       </c>
-      <c r="M3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" s="6" t="n">
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
         <v>51778</v>
       </c>
-      <c r="O3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="6" t="n">
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
         <v>90024</v>
       </c>
-      <c r="Q3" s="6" t="n">
+      <c r="Q3" t="n">
         <v>379200</v>
       </c>
-      <c r="R3" s="6" t="n">
+      <c r="R3" t="n">
         <v>64960</v>
       </c>
-      <c r="S3" s="6" t="n">
+      <c r="S3" t="n">
         <v>2800</v>
       </c>
-      <c r="T3" s="6" t="n">
+      <c r="T3" t="n">
         <v>52653</v>
       </c>
-      <c r="U3" s="6" t="n">
+      <c r="U3" t="n">
         <v>16</v>
       </c>
-      <c r="V3" s="6" t="n">
+      <c r="V3" t="n">
         <v>60</v>
       </c>
-      <c r="W3" s="6" t="n">
+      <c r="W3" t="n">
         <v>146538</v>
       </c>
-      <c r="X3" s="6" t="n">
+      <c r="X3" t="n">
         <v>353075</v>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026/05/02</t>
         </is>
       </c>
-      <c r="B4" s="8" t="n">
+      <c r="B4" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>土</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr"/>
-      <c r="E4" s="9" t="inlineStr"/>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>晴</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>曇</t>
-        </is>
-      </c>
-      <c r="H4" s="10" t="n">
+      <c r="H4" t="n">
         <v>765280</v>
       </c>
-      <c r="I4" s="10" t="n">
+      <c r="I4" t="n">
         <v>696016</v>
       </c>
-      <c r="J4" s="10" t="n">
+      <c r="J4" t="n">
         <v>209533</v>
       </c>
-      <c r="K4" s="10" t="n">
+      <c r="K4" t="n">
         <v>115718</v>
       </c>
-      <c r="L4" s="10" t="n">
+      <c r="L4" t="n">
         <v>359914</v>
       </c>
-      <c r="M4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="10" t="n">
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>80115</v>
       </c>
-      <c r="O4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="10" t="n">
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>615550</v>
       </c>
-      <c r="R4" s="10" t="n">
+      <c r="R4" t="n">
         <v>65180</v>
       </c>
-      <c r="S4" s="10" t="n">
+      <c r="S4" t="n">
         <v>11130</v>
       </c>
-      <c r="T4" s="10" t="n">
+      <c r="T4" t="n">
         <v>73420</v>
       </c>
-      <c r="U4" s="10" t="n">
+      <c r="U4" t="n">
         <v>113</v>
       </c>
-      <c r="V4" s="10" t="n">
+      <c r="V4" t="n">
         <v>62</v>
       </c>
-      <c r="W4" s="10" t="n">
+      <c r="W4" t="n">
         <v>438470</v>
       </c>
-      <c r="X4" s="10" t="n">
+      <c r="X4" t="n">
         <v>326810</v>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2026/05/03</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>祝</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>曇</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>雨</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" t="n">
         <v>980555</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" t="n">
         <v>891802</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="J5" t="n">
         <v>421724</v>
       </c>
-      <c r="K5" s="6" t="n">
+      <c r="K5" t="n">
         <v>240432</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="L5" t="n">
         <v>248934</v>
       </c>
-      <c r="M5" s="6" t="n">
+      <c r="M5" t="n">
         <v>26705</v>
       </c>
-      <c r="N5" s="6" t="n">
+      <c r="N5" t="n">
         <v>42760</v>
       </c>
-      <c r="O5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="6" t="n">
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>766130</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="R5" t="n">
         <v>100960</v>
       </c>
-      <c r="S5" s="6" t="n">
+      <c r="S5" t="n">
         <v>12650</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="T5" t="n">
         <v>100815</v>
       </c>
-      <c r="U5" s="6" t="n">
+      <c r="U5" t="n">
         <v>155</v>
       </c>
-      <c r="V5" s="6" t="n">
+      <c r="V5" t="n">
         <v>62</v>
       </c>
-      <c r="W5" s="6" t="n">
+      <c r="W5" t="n">
         <v>545222</v>
       </c>
-      <c r="X5" s="6" t="n">
+      <c r="X5" t="n">
         <v>435333</v>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2026/05/04</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr"/>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>祝</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>曇</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>曇</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="n">
+      <c r="H6" t="n">
         <v>674091</v>
       </c>
-      <c r="I6" s="10" t="n">
+      <c r="I6" t="n">
         <v>612910</v>
       </c>
-      <c r="J6" s="10" t="n">
+      <c r="J6" t="n">
         <v>249308</v>
       </c>
-      <c r="K6" s="10" t="n">
+      <c r="K6" t="n">
         <v>141596</v>
       </c>
-      <c r="L6" s="10" t="n">
+      <c r="L6" t="n">
         <v>181060</v>
       </c>
-      <c r="M6" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="10" t="n">
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>102127</v>
       </c>
-      <c r="O6" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="10" t="n">
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>530470</v>
       </c>
-      <c r="R6" s="10" t="n">
+      <c r="R6" t="n">
         <v>88760</v>
       </c>
-      <c r="S6" s="10" t="n">
+      <c r="S6" t="n">
         <v>2800</v>
       </c>
-      <c r="T6" s="10" t="n">
+      <c r="T6" t="n">
         <v>52061</v>
       </c>
-      <c r="U6" s="10" t="n">
+      <c r="U6" t="n">
         <v>101</v>
       </c>
-      <c r="V6" s="10" t="n">
+      <c r="V6" t="n">
         <v>58</v>
       </c>
-      <c r="W6" s="10" t="n">
+      <c r="W6" t="n">
         <v>312196</v>
       </c>
-      <c r="X6" s="10" t="n">
+      <c r="X6" t="n">
         <v>361895</v>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>2026/05/05</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>祝</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>曇</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>晴</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" t="n">
         <v>1166590</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="I7" t="n">
         <v>1060626</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J7" t="n">
         <v>264278</v>
       </c>
-      <c r="K7" s="6" t="n">
+      <c r="K7" t="n">
         <v>409193</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="L7" t="n">
         <v>410274</v>
       </c>
-      <c r="M7" s="6" t="n">
+      <c r="M7" t="n">
         <v>68245</v>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="N7" t="n">
         <v>14600</v>
       </c>
-      <c r="O7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="6" t="n">
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>952030</v>
       </c>
-      <c r="R7" s="6" t="n">
+      <c r="R7" t="n">
         <v>97280</v>
       </c>
-      <c r="S7" s="6" t="n">
+      <c r="S7" t="n">
         <v>3420</v>
       </c>
-      <c r="T7" s="6" t="n">
+      <c r="T7" t="n">
         <v>113860</v>
       </c>
-      <c r="U7" s="6" t="n">
+      <c r="U7" t="n">
         <v>151</v>
       </c>
-      <c r="V7" s="6" t="n">
+      <c r="V7" t="n">
         <v>95</v>
       </c>
-      <c r="W7" s="6" t="n">
+      <c r="W7" t="n">
         <v>560265</v>
       </c>
-      <c r="X7" s="6" t="n">
+      <c r="X7" t="n">
         <v>606325</v>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2026/05/06</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr"/>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>振</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>晴</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>晴</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="n">
+      <c r="H8" t="n">
         <v>457199</v>
       </c>
-      <c r="I8" s="10" t="n">
+      <c r="I8" t="n">
         <v>415759</v>
       </c>
-      <c r="J8" s="10" t="n">
+      <c r="J8" t="n">
         <v>265539</v>
       </c>
-      <c r="K8" s="10" t="n">
+      <c r="K8" t="n">
         <v>48837</v>
       </c>
-      <c r="L8" s="10" t="n">
+      <c r="L8" t="n">
         <v>120495</v>
       </c>
-      <c r="M8" s="10" t="n">
+      <c r="M8" t="n">
         <v>4900</v>
       </c>
-      <c r="N8" s="10" t="n">
+      <c r="N8" t="n">
         <v>17428</v>
       </c>
-      <c r="O8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="10" t="n">
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>344540</v>
       </c>
-      <c r="R8" s="10" t="n">
+      <c r="R8" t="n">
         <v>79940</v>
       </c>
-      <c r="S8" s="10" t="n">
+      <c r="S8" t="n">
         <v>2100</v>
       </c>
-      <c r="T8" s="10" t="n">
+      <c r="T8" t="n">
         <v>30619</v>
       </c>
-      <c r="U8" s="10" t="n">
+      <c r="U8" t="n">
         <v>95</v>
       </c>
-      <c r="V8" s="10" t="n">
+      <c r="V8" t="n">
         <v>23</v>
       </c>
-      <c r="W8" s="10" t="n">
+      <c r="W8" t="n">
         <v>311799</v>
       </c>
-      <c r="X8" s="10" t="n">
+      <c r="X8" t="n">
         <v>145400</v>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2026/05/07</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>休</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr"/>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>曇</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>曇</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>2026/05/08</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n">
+      <c r="B10" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr"/>
-      <c r="E10" s="9" t="inlineStr"/>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>曇</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>曇</t>
-        </is>
-      </c>
-      <c r="H10" s="10" t="n">
+      <c r="H10" t="n">
         <v>486530</v>
       </c>
-      <c r="I10" s="10" t="n">
+      <c r="I10" t="n">
         <v>442430</v>
       </c>
-      <c r="J10" s="10" t="n">
+      <c r="J10" t="n">
         <v>218257</v>
       </c>
-      <c r="K10" s="10" t="n">
+      <c r="K10" t="n">
         <v>88404</v>
       </c>
-      <c r="L10" s="10" t="n">
+      <c r="L10" t="n">
         <v>156661</v>
       </c>
-      <c r="M10" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="10" t="n">
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
         <v>23208</v>
       </c>
-      <c r="O10" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="10" t="n">
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>357990</v>
       </c>
-      <c r="R10" s="10" t="n">
+      <c r="R10" t="n">
         <v>67600</v>
       </c>
-      <c r="S10" s="10" t="n">
+      <c r="S10" t="n">
         <v>1500</v>
       </c>
-      <c r="T10" s="10" t="n">
+      <c r="T10" t="n">
         <v>59440</v>
       </c>
-      <c r="U10" s="10" t="n">
+      <c r="U10" t="n">
         <v>62</v>
       </c>
-      <c r="V10" s="10" t="n">
+      <c r="V10" t="n">
         <v>19</v>
       </c>
-      <c r="W10" s="10" t="n">
+      <c r="W10" t="n">
         <v>275206</v>
       </c>
-      <c r="X10" s="10" t="n">
+      <c r="X10" t="n">
         <v>211324</v>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>2026/05/09</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>土</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>曇</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>晴</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" t="n">
         <v>833405</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="I11" t="n">
         <v>758053</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" t="n">
         <v>147213</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="K11" t="n">
         <v>342521</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="L11" t="n">
         <v>218549</v>
       </c>
-      <c r="M11" s="6" t="n">
+      <c r="M11" t="n">
         <v>24594</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="N11" t="n">
         <v>100528</v>
       </c>
-      <c r="O11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="6" t="n">
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>605600</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="R11" t="n">
         <v>113960</v>
       </c>
-      <c r="S11" s="6" t="n">
+      <c r="S11" t="n">
         <v>11000</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="T11" t="n">
         <v>102845</v>
       </c>
-      <c r="U11" s="6" t="n">
+      <c r="U11" t="n">
         <v>78</v>
       </c>
-      <c r="V11" s="6" t="n">
+      <c r="V11" t="n">
         <v>84</v>
       </c>
-      <c r="W11" s="6" t="n">
+      <c r="W11" t="n">
         <v>241664</v>
       </c>
-      <c r="X11" s="6" t="n">
+      <c r="X11" t="n">
         <v>591741</v>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>2026/05/10</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n">
+      <c r="B12" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr"/>
-      <c r="E12" s="9" t="inlineStr"/>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>晴</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>晴</t>
-        </is>
-      </c>
-      <c r="H12" s="10" t="n">
+      <c r="H12" t="n">
         <v>649148</v>
       </c>
-      <c r="I12" s="10" t="n">
+      <c r="I12" t="n">
         <v>591125</v>
       </c>
-      <c r="J12" s="10" t="n">
+      <c r="J12" t="n">
         <v>443278</v>
       </c>
-      <c r="K12" s="10" t="n">
+      <c r="K12" t="n">
         <v>43819</v>
       </c>
-      <c r="L12" s="10" t="n">
+      <c r="L12" t="n">
         <v>88768</v>
       </c>
-      <c r="M12" s="10" t="n">
+      <c r="M12" t="n">
         <v>21939</v>
       </c>
-      <c r="N12" s="10" t="n">
+      <c r="N12" t="n">
         <v>51344</v>
       </c>
-      <c r="O12" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="10" t="n">
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>490610</v>
       </c>
-      <c r="R12" s="10" t="n">
+      <c r="R12" t="n">
         <v>52770</v>
       </c>
-      <c r="S12" s="10" t="n">
+      <c r="S12" t="n">
         <v>14000</v>
       </c>
-      <c r="T12" s="10" t="n">
+      <c r="T12" t="n">
         <v>91768</v>
       </c>
-      <c r="U12" s="10" t="n">
+      <c r="U12" t="n">
         <v>121</v>
       </c>
-      <c r="V12" s="10" t="n">
+      <c r="V12" t="n">
         <v>25</v>
       </c>
-      <c r="W12" s="10" t="n">
+      <c r="W12" t="n">
         <v>452742</v>
       </c>
-      <c r="X12" s="10" t="n">
+      <c r="X12" t="n">
         <v>196406</v>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>2026/05/11</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>休</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr"/>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>晴</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>晴</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>2026/05/12</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n">
+      <c r="B14" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr"/>
-      <c r="E14" s="9" t="inlineStr"/>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>晴</t>
-        </is>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>晴</t>
-        </is>
-      </c>
-      <c r="H14" s="10" t="n">
+      <c r="H14" t="n">
         <v>800419</v>
       </c>
-      <c r="I14" s="10" t="n">
+      <c r="I14" t="n">
         <v>730315</v>
       </c>
-      <c r="J14" s="10" t="n">
+      <c r="J14" t="n">
         <v>533858</v>
       </c>
-      <c r="K14" s="10" t="n">
+      <c r="K14" t="n">
         <v>52935</v>
       </c>
-      <c r="L14" s="10" t="n">
+      <c r="L14" t="n">
         <v>92720</v>
       </c>
-      <c r="M14" s="10" t="n">
+      <c r="M14" t="n">
         <v>30590</v>
       </c>
-      <c r="N14" s="10" t="n">
+      <c r="N14" t="n">
         <v>55756</v>
       </c>
-      <c r="O14" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="10" t="n">
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
         <v>34560</v>
       </c>
-      <c r="Q14" s="10" t="n">
+      <c r="Q14" t="n">
         <v>532270</v>
       </c>
-      <c r="R14" s="10" t="n">
+      <c r="R14" t="n">
         <v>81340</v>
       </c>
-      <c r="S14" s="10" t="n">
+      <c r="S14" t="n">
         <v>4900</v>
       </c>
-      <c r="T14" s="10" t="n">
+      <c r="T14" t="n">
         <v>181909</v>
       </c>
-      <c r="U14" s="10" t="n">
+      <c r="U14" t="n">
         <v>72</v>
       </c>
-      <c r="V14" s="10" t="n">
+      <c r="V14" t="n">
         <v>148</v>
       </c>
-      <c r="W14" s="10" t="n">
+      <c r="W14" t="n">
         <v>264150</v>
       </c>
-      <c r="X14" s="10" t="n">
+      <c r="X14" t="n">
         <v>536269</v>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>2026/05/13</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>晴</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>曇</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="n">
+      <c r="H15" t="n">
         <v>639456</v>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="I15" t="n">
         <v>581484</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="J15" t="n">
         <v>198301</v>
       </c>
-      <c r="K15" s="6" t="n">
+      <c r="K15" t="n">
         <v>126708</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="L15" t="n">
         <v>129461</v>
       </c>
-      <c r="M15" s="6" t="n">
+      <c r="M15" t="n">
         <v>5148</v>
       </c>
-      <c r="N15" s="6" t="n">
+      <c r="N15" t="n">
         <v>25031</v>
       </c>
-      <c r="O15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="6" t="n">
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
         <v>154807</v>
       </c>
-      <c r="Q15" s="6" t="n">
+      <c r="Q15" t="n">
         <v>478020</v>
       </c>
-      <c r="R15" s="6" t="n">
+      <c r="R15" t="n">
         <v>84710</v>
       </c>
-      <c r="S15" s="6" t="n">
+      <c r="S15" t="n">
         <v>7000</v>
       </c>
-      <c r="T15" s="6" t="n">
+      <c r="T15" t="n">
         <v>69726</v>
       </c>
-      <c r="U15" s="6" t="n">
+      <c r="U15" t="n">
         <v>74</v>
       </c>
-      <c r="V15" s="6" t="n">
+      <c r="V15" t="n">
         <v>34</v>
       </c>
-      <c r="W15" s="6" t="n">
+      <c r="W15" t="n">
         <v>219079</v>
       </c>
-      <c r="X15" s="6" t="n">
+      <c r="X15" t="n">
         <v>420377</v>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>2026/05/14</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n">
+      <c r="B16" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr"/>
-      <c r="E16" s="9" t="inlineStr"/>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>曇</t>
-        </is>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>曇</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="n">
+      <c r="H16" t="n">
         <v>855834</v>
       </c>
-      <c r="I16" s="10" t="n">
+      <c r="I16" t="n">
         <v>778282</v>
       </c>
-      <c r="J16" s="10" t="n">
+      <c r="J16" t="n">
         <v>576310</v>
       </c>
-      <c r="K16" s="10" t="n">
+      <c r="K16" t="n">
         <v>118397</v>
       </c>
-      <c r="L16" s="10" t="n">
+      <c r="L16" t="n">
         <v>134247</v>
       </c>
-      <c r="M16" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="10" t="n">
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
         <v>26880</v>
       </c>
-      <c r="O16" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="10" t="n">
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>611540</v>
       </c>
-      <c r="R16" s="10" t="n">
+      <c r="R16" t="n">
         <v>148470</v>
       </c>
-      <c r="S16" s="10" t="n">
+      <c r="S16" t="n">
         <v>17792</v>
       </c>
-      <c r="T16" s="10" t="n">
+      <c r="T16" t="n">
         <v>78032</v>
       </c>
-      <c r="U16" s="10" t="n">
+      <c r="U16" t="n">
         <v>94</v>
       </c>
-      <c r="V16" s="10" t="n">
+      <c r="V16" t="n">
         <v>44</v>
       </c>
-      <c r="W16" s="10" t="n">
+      <c r="W16" t="n">
         <v>415078</v>
       </c>
-      <c r="X16" s="10" t="n">
+      <c r="X16" t="n">
         <v>440756</v>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>2026/05/15</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>曇</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>晴</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="n">
+      <c r="H17" t="n">
         <v>890323</v>
       </c>
-      <c r="I17" s="6" t="n">
+      <c r="I17" t="n">
         <v>809403</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="J17" t="n">
         <v>28994</v>
       </c>
-      <c r="K17" s="6" t="n">
+      <c r="K17" t="n">
         <v>335459</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="L17" t="n">
         <v>513132</v>
       </c>
-      <c r="M17" s="6" t="n">
+      <c r="M17" t="n">
         <v>4900</v>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="N17" t="n">
         <v>7838</v>
       </c>
-      <c r="O17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="6" t="n">
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>642970</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="R17" t="n">
         <v>165370</v>
       </c>
-      <c r="S17" s="6" t="n">
+      <c r="S17" t="n">
         <v>700</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="T17" t="n">
         <v>81283</v>
       </c>
-      <c r="U17" s="6" t="n">
+      <c r="U17" t="n">
         <v>12</v>
       </c>
-      <c r="V17" s="6" t="n">
+      <c r="V17" t="n">
         <v>99</v>
       </c>
-      <c r="W17" s="6" t="n">
+      <c r="W17" t="n">
         <v>106190</v>
       </c>
-      <c r="X17" s="6" t="n">
+      <c r="X17" t="n">
         <v>784133</v>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>2026/05/16</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n">
+      <c r="B18" t="n">
         <v>16</v>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>土</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr"/>
-      <c r="E18" s="9" t="inlineStr"/>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>晴</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>晴</t>
-        </is>
-      </c>
-      <c r="H18" s="10" t="n">
+      <c r="H18" t="n">
         <v>1008132</v>
       </c>
-      <c r="I18" s="10" t="n">
+      <c r="I18" t="n">
         <v>917550</v>
       </c>
-      <c r="J18" s="10" t="n">
+      <c r="J18" t="n">
         <v>629414</v>
       </c>
-      <c r="K18" s="10" t="n">
+      <c r="K18" t="n">
         <v>62580</v>
       </c>
-      <c r="L18" s="10" t="n">
+      <c r="L18" t="n">
         <v>281876</v>
       </c>
-      <c r="M18" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="10" t="n">
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
         <v>34262</v>
       </c>
-      <c r="O18" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="10" t="n">
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>734500</v>
       </c>
-      <c r="R18" s="10" t="n">
+      <c r="R18" t="n">
         <v>121570</v>
       </c>
-      <c r="S18" s="10" t="n">
+      <c r="S18" t="n">
         <v>49100</v>
       </c>
-      <c r="T18" s="10" t="n">
+      <c r="T18" t="n">
         <v>102962</v>
       </c>
-      <c r="U18" s="10" t="n">
+      <c r="U18" t="n">
         <v>197</v>
       </c>
-      <c r="V18" s="10" t="n">
+      <c r="V18" t="n">
         <v>56</v>
       </c>
-      <c r="W18" s="10" t="n">
+      <c r="W18" t="n">
         <v>497480</v>
       </c>
-      <c r="X18" s="10" t="n">
+      <c r="X18" t="n">
         <v>510652</v>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>2026/05/17</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" t="n">
         <v>17</v>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr"/>
-      <c r="E19" s="5" t="inlineStr"/>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>晴</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>晴</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="n">
+      <c r="H19" t="n">
         <v>836061</v>
       </c>
-      <c r="I19" s="6" t="n">
+      <c r="I19" t="n">
         <v>760517</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="J19" t="n">
         <v>469044</v>
       </c>
-      <c r="K19" s="6" t="n">
+      <c r="K19" t="n">
         <v>122711</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="L19" t="n">
         <v>207963</v>
       </c>
-      <c r="M19" s="6" t="n">
+      <c r="M19" t="n">
         <v>10800</v>
       </c>
-      <c r="N19" s="6" t="n">
+      <c r="N19" t="n">
         <v>25540</v>
       </c>
-      <c r="O19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="6" t="n">
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>622570</v>
       </c>
-      <c r="R19" s="6" t="n">
+      <c r="R19" t="n">
         <v>128580</v>
       </c>
-      <c r="S19" s="6" t="n">
+      <c r="S19" t="n">
         <v>14750</v>
       </c>
-      <c r="T19" s="6" t="n">
+      <c r="T19" t="n">
         <v>70161</v>
       </c>
-      <c r="U19" s="6" t="n">
+      <c r="U19" t="n">
         <v>179</v>
       </c>
-      <c r="V19" s="6" t="n">
+      <c r="V19" t="n">
         <v>44</v>
       </c>
-      <c r="W19" s="6" t="n">
+      <c r="W19" t="n">
         <v>559411</v>
       </c>
-      <c r="X19" s="6" t="n">
+      <c r="X19" t="n">
         <v>276650</v>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>2026/05/18</t>
         </is>
       </c>
-      <c r="B20" s="8" t="n">
+      <c r="B20" t="n">
         <v>18</v>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>休</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr"/>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>晴</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>晴</t>
-        </is>
-      </c>
-      <c r="H20" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n">
+      <c r="B21" t="n">
         <v>19</v>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr"/>
-      <c r="E21" s="5" t="inlineStr"/>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>晴</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>曇</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="n">
+      <c r="H21" t="n">
         <v>656558</v>
       </c>
-      <c r="I21" s="6" t="n">
+      <c r="I21" t="n">
         <v>596921</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="J21" t="n">
         <v>221169</v>
       </c>
-      <c r="K21" s="6" t="n">
+      <c r="K21" t="n">
         <v>171740</v>
       </c>
-      <c r="L21" s="6" t="n">
+      <c r="L21" t="n">
         <v>69682</v>
       </c>
-      <c r="M21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="6" t="n">
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>32930</v>
       </c>
-      <c r="O21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="6" t="n">
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
         <v>161037</v>
       </c>
-      <c r="Q21" s="6" t="n">
+      <c r="Q21" t="n">
         <v>457120</v>
       </c>
-      <c r="R21" s="6" t="n">
+      <c r="R21" t="n">
         <v>93190</v>
       </c>
-      <c r="S21" s="6" t="n">
+      <c r="S21" t="n">
         <v>2100</v>
       </c>
-      <c r="T21" s="6" t="n">
+      <c r="T21" t="n">
         <v>104148</v>
       </c>
-      <c r="U21" s="6" t="n">
+      <c r="U21" t="n">
         <v>61</v>
       </c>
-      <c r="V21" s="6" t="n">
+      <c r="V21" t="n">
         <v>37</v>
       </c>
-      <c r="W21" s="6" t="n">
+      <c r="W21" t="n">
         <v>189226</v>
       </c>
-      <c r="X21" s="6" t="n">
+      <c r="X21" t="n">
         <v>467332</v>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>2026/05/20</t>
         </is>
       </c>
-      <c r="B22" s="8" t="n">
+      <c r="B22" t="n">
         <v>20</v>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr"/>
-      <c r="E22" s="9" t="inlineStr"/>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>曇</t>
-        </is>
-      </c>
-      <c r="G22" s="9" t="inlineStr">
-        <is>
-          <t>雨</t>
-        </is>
-      </c>
-      <c r="H22" s="10" t="n">
+      <c r="H22" t="n">
         <v>322120</v>
       </c>
-      <c r="I22" s="10" t="n">
+      <c r="I22" t="n">
         <v>293087</v>
       </c>
-      <c r="J22" s="10" t="n">
+      <c r="J22" t="n">
         <v>147756</v>
       </c>
-      <c r="K22" s="10" t="n">
+      <c r="K22" t="n">
         <v>36099</v>
       </c>
-      <c r="L22" s="10" t="n">
+      <c r="L22" t="n">
         <v>63308</v>
       </c>
-      <c r="M22" s="10" t="n">
+      <c r="M22" t="n">
         <v>59279</v>
       </c>
-      <c r="N22" s="10" t="n">
+      <c r="N22" t="n">
         <v>15678</v>
       </c>
-      <c r="O22" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="10" t="n">
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
         <v>231040</v>
       </c>
-      <c r="R22" s="10" t="n">
+      <c r="R22" t="n">
         <v>54270</v>
       </c>
-      <c r="S22" s="10" t="n">
+      <c r="S22" t="n">
         <v>1400</v>
       </c>
-      <c r="T22" s="10" t="n">
+      <c r="T22" t="n">
         <v>35410</v>
       </c>
-      <c r="U22" s="10" t="n">
+      <c r="U22" t="n">
         <v>49</v>
       </c>
-      <c r="V22" s="10" t="n">
+      <c r="V22" t="n">
         <v>20</v>
       </c>
-      <c r="W22" s="10" t="n">
+      <c r="W22" t="n">
         <v>186595</v>
       </c>
-      <c r="X22" s="10" t="n">
+      <c r="X22" t="n">
         <v>135525</v>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>2026/05/21</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n">
+      <c r="B23" t="n">
         <v>21</v>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>雨</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>雨</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="n">
+      <c r="H23" t="n">
         <v>851000</v>
       </c>
-      <c r="I23" s="6" t="n">
+      <c r="I23" t="n">
         <v>773884</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="J23" t="n">
         <v>506886</v>
       </c>
-      <c r="K23" s="6" t="n">
+      <c r="K23" t="n">
         <v>152221</v>
       </c>
-      <c r="L23" s="6" t="n">
+      <c r="L23" t="n">
         <v>149626</v>
       </c>
-      <c r="M23" s="6" t="n">
+      <c r="M23" t="n">
         <v>7326</v>
       </c>
-      <c r="N23" s="6" t="n">
+      <c r="N23" t="n">
         <v>34941</v>
       </c>
-      <c r="O23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="6" t="n">
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>448340</v>
       </c>
-      <c r="R23" s="6" t="n">
+      <c r="R23" t="n">
         <v>341560</v>
       </c>
-      <c r="S23" s="6" t="n">
+      <c r="S23" t="n">
         <v>4250</v>
       </c>
-      <c r="T23" s="6" t="n">
+      <c r="T23" t="n">
         <v>56850</v>
       </c>
-      <c r="U23" s="6" t="n">
+      <c r="U23" t="n">
         <v>48</v>
       </c>
-      <c r="V23" s="6" t="n">
+      <c r="V23" t="n">
         <v>53</v>
       </c>
-      <c r="W23" s="6" t="n">
+      <c r="W23" t="n">
         <v>153613</v>
       </c>
-      <c r="X23" s="6" t="n">
+      <c r="X23" t="n">
         <v>697387</v>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="B24" s="8" t="n">
+      <c r="B24" t="n">
         <v>22</v>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr"/>
-      <c r="E24" s="9" t="inlineStr"/>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>雨</t>
-        </is>
-      </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>曇</t>
-        </is>
-      </c>
-      <c r="H24" s="10" t="n">
+      <c r="H24" t="n">
         <v>958119</v>
       </c>
-      <c r="I24" s="10" t="n">
+      <c r="I24" t="n">
         <v>873275</v>
       </c>
-      <c r="J24" s="10" t="n">
+      <c r="J24" t="n">
         <v>233353</v>
       </c>
-      <c r="K24" s="10" t="n">
+      <c r="K24" t="n">
         <v>98106</v>
       </c>
-      <c r="L24" s="10" t="n">
+      <c r="L24" t="n">
         <v>111397</v>
       </c>
-      <c r="M24" s="10" t="n">
+      <c r="M24" t="n">
         <v>13270</v>
       </c>
-      <c r="N24" s="10" t="n">
+      <c r="N24" t="n">
         <v>107372</v>
       </c>
-      <c r="O24" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="10" t="n">
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
         <v>394621</v>
       </c>
-      <c r="Q24" s="10" t="n">
+      <c r="Q24" t="n">
         <v>497210</v>
       </c>
-      <c r="R24" s="10" t="n">
+      <c r="R24" t="n">
         <v>140240</v>
       </c>
-      <c r="S24" s="10" t="n">
+      <c r="S24" t="n">
         <v>13468</v>
       </c>
-      <c r="T24" s="10" t="n">
+      <c r="T24" t="n">
         <v>307201</v>
       </c>
-      <c r="U24" s="10" t="n">
+      <c r="U24" t="n">
         <v>21</v>
       </c>
-      <c r="V24" s="10" t="n">
+      <c r="V24" t="n">
         <v>92</v>
       </c>
-      <c r="W24" s="10" t="n">
+      <c r="W24" t="n">
         <v>369696</v>
       </c>
-      <c r="X24" s="10" t="n">
+      <c r="X24" t="n">
         <v>588423</v>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>2026/05/23</t>
         </is>
       </c>
-      <c r="B25" s="4" t="n">
+      <c r="B25" t="n">
         <v>23</v>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>土</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr"/>
-      <c r="E25" s="5" t="inlineStr"/>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>曇</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>曇</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="n">
+      <c r="H25" t="n">
         <v>907553</v>
       </c>
-      <c r="I25" s="6" t="n">
+      <c r="I25" t="n">
         <v>825217</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="J25" t="n">
         <v>425649</v>
       </c>
-      <c r="K25" s="6" t="n">
+      <c r="K25" t="n">
         <v>18397</v>
       </c>
-      <c r="L25" s="6" t="n">
+      <c r="L25" t="n">
         <v>460079</v>
       </c>
-      <c r="M25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="6" t="n">
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
         <v>14875</v>
       </c>
-      <c r="O25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="6" t="n">
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
         <v>688450</v>
       </c>
-      <c r="R25" s="6" t="n">
+      <c r="R25" t="n">
         <v>116280</v>
       </c>
-      <c r="S25" s="6" t="n">
+      <c r="S25" t="n">
         <v>5850</v>
       </c>
-      <c r="T25" s="6" t="n">
+      <c r="T25" t="n">
         <v>96973</v>
       </c>
-      <c r="U25" s="6" t="n">
+      <c r="U25" t="n">
         <v>127</v>
       </c>
-      <c r="V25" s="6" t="n">
+      <c r="V25" t="n">
         <v>30</v>
       </c>
-      <c r="W25" s="6" t="n">
+      <c r="W25" t="n">
         <v>608118</v>
       </c>
-      <c r="X25" s="6" t="n">
+      <c r="X25" t="n">
         <v>299435</v>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>2026/05/24</t>
         </is>
       </c>
-      <c r="B26" s="8" t="n">
+      <c r="B26" t="n">
         <v>24</v>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr"/>
-      <c r="E26" s="9" t="inlineStr"/>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>曇</t>
-        </is>
-      </c>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>曇</t>
-        </is>
-      </c>
-      <c r="H26" s="10" t="n">
+      <c r="H26" t="n">
         <v>929773</v>
       </c>
-      <c r="I26" s="10" t="n">
+      <c r="I26" t="n">
         <v>845640</v>
       </c>
-      <c r="J26" s="10" t="n">
+      <c r="J26" t="n">
         <v>367866</v>
       </c>
-      <c r="K26" s="10" t="n">
+      <c r="K26" t="n">
         <v>139264</v>
       </c>
-      <c r="L26" s="10" t="n">
+      <c r="L26" t="n">
         <v>245824</v>
       </c>
-      <c r="M26" s="10" t="n">
+      <c r="M26" t="n">
         <v>97990</v>
       </c>
-      <c r="N26" s="10" t="n">
+      <c r="N26" t="n">
         <v>36112</v>
       </c>
-      <c r="O26" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="10" t="n">
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
         <v>42717</v>
       </c>
-      <c r="Q26" s="10" t="n">
+      <c r="Q26" t="n">
         <v>718850</v>
       </c>
-      <c r="R26" s="10" t="n">
+      <c r="R26" t="n">
         <v>104590</v>
       </c>
-      <c r="S26" s="10" t="n">
+      <c r="S26" t="n">
         <v>2100</v>
       </c>
-      <c r="T26" s="10" t="n">
+      <c r="T26" t="n">
         <v>104233</v>
       </c>
-      <c r="U26" s="10" t="n">
+      <c r="U26" t="n">
         <v>152</v>
       </c>
-      <c r="V26" s="10" t="n">
+      <c r="V26" t="n">
         <v>42</v>
       </c>
-      <c r="W26" s="10" t="n">
+      <c r="W26" t="n">
         <v>540889</v>
       </c>
-      <c r="X26" s="10" t="n">
+      <c r="X26" t="n">
         <v>388884</v>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>2026/05/25</t>
         </is>
       </c>
-      <c r="B27" s="4" t="n">
+      <c r="B27" t="n">
         <v>25</v>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>休</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr"/>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>曇</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>曇</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>2026/05/26</t>
         </is>
       </c>
-      <c r="B28" s="8" t="n">
+      <c r="B28" t="n">
         <v>26</v>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr"/>
-      <c r="E28" s="9" t="inlineStr"/>
-      <c r="F28" s="9" t="inlineStr">
-        <is>
-          <t>曇</t>
-        </is>
-      </c>
-      <c r="G28" s="9" t="inlineStr">
-        <is>
-          <t>曇</t>
-        </is>
-      </c>
-      <c r="H28" s="10" t="n">
+      <c r="H28" t="n">
         <v>437884</v>
       </c>
-      <c r="I28" s="10" t="n">
+      <c r="I28" t="n">
         <v>398268</v>
       </c>
-      <c r="J28" s="10" t="n">
+      <c r="J28" t="n">
         <v>190643</v>
       </c>
-      <c r="K28" s="10" t="n">
+      <c r="K28" t="n">
         <v>126632</v>
       </c>
-      <c r="L28" s="10" t="n">
+      <c r="L28" t="n">
         <v>92512</v>
       </c>
-      <c r="M28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="10" t="n">
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
         <v>28097</v>
       </c>
-      <c r="O28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="10" t="n">
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
         <v>354010</v>
       </c>
-      <c r="R28" s="10" t="n">
+      <c r="R28" t="n">
         <v>47010</v>
       </c>
-      <c r="S28" s="10" t="n">
+      <c r="S28" t="n">
         <v>3050</v>
       </c>
-      <c r="T28" s="10" t="n">
+      <c r="T28" t="n">
         <v>33814</v>
       </c>
-      <c r="U28" s="10" t="n">
+      <c r="U28" t="n">
         <v>85</v>
       </c>
-      <c r="V28" s="10" t="n">
+      <c r="V28" t="n">
         <v>19</v>
       </c>
-      <c r="W28" s="10" t="n">
+      <c r="W28" t="n">
         <v>329787</v>
       </c>
-      <c r="X28" s="10" t="n">
+      <c r="X28" t="n">
         <v>108097</v>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>2026/05/27</t>
         </is>
       </c>
-      <c r="B29" s="4" t="n">
+      <c r="B29" t="n">
         <v>27</v>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>曇</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>曇</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="n">
+      <c r="H29" t="n">
         <v>823370</v>
       </c>
-      <c r="I29" s="6" t="n">
+      <c r="I29" t="n">
         <v>749518</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="J29" t="n">
         <v>266045</v>
       </c>
-      <c r="K29" s="6" t="n">
+      <c r="K29" t="n">
         <v>50914</v>
       </c>
-      <c r="L29" s="6" t="n">
+      <c r="L29" t="n">
         <v>369086</v>
       </c>
-      <c r="M29" s="6" t="n">
+      <c r="M29" t="n">
         <v>114617</v>
       </c>
-      <c r="N29" s="6" t="n">
+      <c r="N29" t="n">
         <v>22708</v>
       </c>
-      <c r="O29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="6" t="n">
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
         <v>546240</v>
       </c>
-      <c r="R29" s="6" t="n">
+      <c r="R29" t="n">
         <v>128890</v>
       </c>
-      <c r="S29" s="6" t="n">
+      <c r="S29" t="n">
         <v>6800</v>
       </c>
-      <c r="T29" s="6" t="n">
+      <c r="T29" t="n">
         <v>141440</v>
       </c>
-      <c r="U29" s="6" t="n">
+      <c r="U29" t="n">
         <v>127</v>
       </c>
-      <c r="V29" s="6" t="n">
+      <c r="V29" t="n">
         <v>42</v>
       </c>
-      <c r="W29" s="6" t="n">
+      <c r="W29" t="n">
         <v>343996</v>
       </c>
-      <c r="X29" s="6" t="n">
+      <c r="X29" t="n">
         <v>479374</v>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>2026/05/28</t>
         </is>
       </c>
-      <c r="B30" s="8" t="n">
+      <c r="B30" t="n">
         <v>28</v>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr"/>
-      <c r="E30" s="9" t="inlineStr"/>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>曇</t>
-        </is>
-      </c>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>曇</t>
-        </is>
-      </c>
-      <c r="H30" s="10" t="n">
+      <c r="H30" t="n">
         <v>484499</v>
       </c>
-      <c r="I30" s="10" t="n">
+      <c r="I30" t="n">
         <v>440484</v>
       </c>
-      <c r="J30" s="10" t="n">
+      <c r="J30" t="n">
         <v>145770</v>
       </c>
-      <c r="K30" s="10" t="n">
+      <c r="K30" t="n">
         <v>97078</v>
       </c>
-      <c r="L30" s="10" t="n">
+      <c r="L30" t="n">
         <v>226823</v>
       </c>
-      <c r="M30" s="10" t="n">
+      <c r="M30" t="n">
         <v>2400</v>
       </c>
-      <c r="N30" s="10" t="n">
+      <c r="N30" t="n">
         <v>12428</v>
       </c>
-      <c r="O30" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="10" t="n">
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
         <v>265060</v>
       </c>
-      <c r="R30" s="10" t="n">
+      <c r="R30" t="n">
         <v>82100</v>
       </c>
-      <c r="S30" s="10" t="n">
+      <c r="S30" t="n">
         <v>1400</v>
       </c>
-      <c r="T30" s="10" t="n">
+      <c r="T30" t="n">
         <v>135939</v>
       </c>
-      <c r="U30" s="10" t="n">
+      <c r="U30" t="n">
         <v>33</v>
       </c>
-      <c r="V30" s="10" t="n">
+      <c r="V30" t="n">
         <v>35</v>
       </c>
-      <c r="W30" s="10" t="n">
+      <c r="W30" t="n">
         <v>119351</v>
       </c>
-      <c r="X30" s="10" t="n">
+      <c r="X30" t="n">
         <v>365148</v>
       </c>
     </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>2026/05/29</t>
         </is>
       </c>
-      <c r="B31" s="4" t="n">
+      <c r="B31" t="n">
         <v>29</v>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr"/>
-      <c r="E31" s="5" t="inlineStr"/>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>晴</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>晴</t>
-        </is>
-      </c>
-      <c r="H31" s="6" t="n">
+      <c r="H31" t="n">
         <v>1312705</v>
       </c>
-      <c r="I31" s="6" t="n">
+      <c r="I31" t="n">
         <v>1196944</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="J31" t="n">
         <v>395202</v>
       </c>
-      <c r="K31" s="6" t="n">
+      <c r="K31" t="n">
         <v>540034</v>
       </c>
-      <c r="L31" s="6" t="n">
+      <c r="L31" t="n">
         <v>134814</v>
       </c>
-      <c r="M31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="6" t="n">
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
         <v>3520</v>
       </c>
-      <c r="O31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" s="6" t="n">
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
         <v>239135</v>
       </c>
-      <c r="Q31" s="6" t="n">
+      <c r="Q31" t="n">
         <v>758930</v>
       </c>
-      <c r="R31" s="6" t="n">
+      <c r="R31" t="n">
         <v>222560</v>
       </c>
-      <c r="S31" s="6" t="n">
+      <c r="S31" t="n">
         <v>8300</v>
       </c>
-      <c r="T31" s="6" t="n">
+      <c r="T31" t="n">
         <v>322915</v>
       </c>
-      <c r="U31" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="V31" s="6" t="n">
-        <v>160</v>
-      </c>
-      <c r="W31" s="6" t="n">
+      <c r="U31" t="n">
+        <v>107</v>
+      </c>
+      <c r="V31" t="n">
+        <v>70</v>
+      </c>
+      <c r="W31" t="n">
         <v>440945</v>
       </c>
-      <c r="X31" s="6" t="n">
+      <c r="X31" t="n">
         <v>871760</v>
       </c>
     </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>2026/05/30</t>
         </is>
       </c>
-      <c r="B32" s="8" t="n">
+      <c r="B32" t="n">
         <v>30</v>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>土</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr"/>
-      <c r="E32" s="9" t="inlineStr"/>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>晴</t>
-        </is>
-      </c>
-      <c r="G32" s="9" t="inlineStr">
-        <is>
-          <t>曇</t>
-        </is>
-      </c>
-      <c r="H32" s="10" t="n">
+      <c r="H32" t="n">
         <v>1076938</v>
       </c>
-      <c r="I32" s="10" t="n">
+      <c r="I32" t="n">
         <v>979348</v>
       </c>
-      <c r="J32" s="10" t="n">
+      <c r="J32" t="n">
         <v>455076</v>
       </c>
-      <c r="K32" s="10" t="n">
+      <c r="K32" t="n">
         <v>48048</v>
       </c>
-      <c r="L32" s="10" t="n">
+      <c r="L32" t="n">
         <v>342921</v>
       </c>
-      <c r="M32" s="10" t="n">
+      <c r="M32" t="n">
         <v>70373</v>
       </c>
-      <c r="N32" s="10" t="n">
+      <c r="N32" t="n">
         <v>62020</v>
       </c>
-      <c r="O32" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="10" t="n">
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
         <v>98500</v>
       </c>
-      <c r="Q32" s="10" t="n">
+      <c r="Q32" t="n">
         <v>826070</v>
       </c>
-      <c r="R32" s="10" t="n">
+      <c r="R32" t="n">
         <v>125410</v>
       </c>
-      <c r="S32" s="10" t="n">
+      <c r="S32" t="n">
         <v>10500</v>
       </c>
-      <c r="T32" s="10" t="n">
+      <c r="T32" t="n">
         <v>114958</v>
       </c>
-      <c r="U32" s="10" t="n">
+      <c r="U32" t="n">
         <v>133</v>
       </c>
-      <c r="V32" s="10" t="n">
+      <c r="V32" t="n">
         <v>66</v>
       </c>
-      <c r="W32" s="10" t="n">
+      <c r="W32" t="n">
         <v>574140</v>
       </c>
-      <c r="X32" s="10" t="n">
+      <c r="X32" t="n">
         <v>502798</v>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>2026/05/31</t>
         </is>
       </c>
-      <c r="B33" s="4" t="n">
+      <c r="B33" t="n">
         <v>31</v>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr"/>
-      <c r="E33" s="5" t="inlineStr"/>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>曇</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>晴</t>
-        </is>
-      </c>
-      <c r="H33" s="6" t="n">
+      <c r="H33" t="n">
         <v>686502</v>
       </c>
-      <c r="I33" s="6" t="n">
+      <c r="I33" t="n">
         <v>624614</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="J33" t="n">
         <v>470425</v>
       </c>
-      <c r="K33" s="6" t="n">
+      <c r="K33" t="n">
         <v>43053</v>
       </c>
-      <c r="L33" s="6" t="n">
+      <c r="L33" t="n">
         <v>121921</v>
       </c>
-      <c r="M33" s="6" t="n">
+      <c r="M33" t="n">
         <v>4800</v>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="N33" t="n">
         <v>46303</v>
       </c>
-      <c r="O33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="6" t="n">
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
         <v>520390</v>
       </c>
-      <c r="R33" s="6" t="n">
+      <c r="R33" t="n">
         <v>82680</v>
       </c>
-      <c r="S33" s="6" t="n">
+      <c r="S33" t="n">
         <v>15400</v>
       </c>
-      <c r="T33" s="6" t="n">
+      <c r="T33" t="n">
         <v>68032</v>
       </c>
-      <c r="U33" s="6" t="n">
+      <c r="U33" t="n">
         <v>147</v>
       </c>
-      <c r="V33" s="6" t="n">
+      <c r="V33" t="n">
         <v>25</v>
       </c>
-      <c r="W33" s="6" t="n">
+      <c r="W33" t="n">
         <v>479636</v>
       </c>
-      <c r="X33" s="6" t="n">
+      <c r="X33" t="n">
         <v>206866</v>
       </c>
     </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>合 計</t>
-        </is>
-      </c>
-      <c r="H34" s="11" t="n">
-        <v>20989657</v>
-      </c>
-      <c r="I34" s="11" t="n">
-        <v>19097801</v>
-      </c>
-      <c r="J34" s="11" t="n">
-        <v>8692051</v>
-      </c>
-      <c r="K34" s="11" t="n">
-        <v>3806445</v>
-      </c>
-      <c r="L34" s="11" t="n">
-        <v>5643149</v>
-      </c>
-      <c r="M34" s="11" t="n">
-        <v>567876</v>
-      </c>
-      <c r="N34" s="11" t="n">
-        <v>1076179</v>
-      </c>
-      <c r="O34" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" s="11" t="n">
-        <v>1215401</v>
-      </c>
-      <c r="Q34" s="11" t="n">
-        <v>14975700</v>
-      </c>
-      <c r="R34" s="11" t="n">
-        <v>3000230</v>
-      </c>
-      <c r="S34" s="11" t="n">
-        <v>230260</v>
-      </c>
-      <c r="T34" s="11" t="n">
-        <v>2783467</v>
-      </c>
-      <c r="U34" s="11" t="n">
-        <v>2520</v>
-      </c>
-      <c r="V34" s="11" t="n">
-        <v>1534</v>
-      </c>
-      <c r="W34" s="11" t="n">
-        <v>9681482</v>
-      </c>
-      <c r="X34" s="11" t="n">
-        <v>11308175</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A1:X1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3191,4498 +2643,4428 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L96"/>
+  <dimension ref="A1:L95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="5" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="12" t="n"/>
-      <c r="B1" s="12" t="n"/>
-      <c r="C1" s="12" t="n"/>
-      <c r="D1" s="12" t="n"/>
-      <c r="E1" s="13" t="inlineStr">
+    <row r="1">
+      <c r="E1" t="inlineStr">
         <is>
           <t>FOOD</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>DRINK</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>曜日</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>順位</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>F商品名</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>F単価</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>F数量</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>F金額</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>D商品名</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>D単価</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>D数量</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>D金額</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026/05/01</t>
         </is>
       </c>
-      <c r="B3" s="8" t="n">
+      <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>1位</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>宴会コース</t>
         </is>
       </c>
-      <c r="F3" s="10" t="n">
+      <c r="F3" t="n">
         <v>8000</v>
       </c>
-      <c r="G3" s="10" t="n">
+      <c r="G3" t="n">
         <v>6</v>
       </c>
-      <c r="H3" s="10" t="n">
+      <c r="H3" t="n">
         <v>48000</v>
       </c>
-      <c r="I3" s="14" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>プレミアムモルツ生</t>
         </is>
       </c>
-      <c r="J3" s="10" t="n">
+      <c r="J3" t="n">
         <v>880</v>
       </c>
-      <c r="K3" s="10" t="n">
+      <c r="K3" t="n">
         <v>17</v>
       </c>
-      <c r="L3" s="10" t="n">
+      <c r="L3" t="n">
         <v>14960</v>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026/05/01</t>
         </is>
       </c>
-      <c r="B4" s="8" t="n">
+      <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>2位</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>あさり膳ハーフ</t>
         </is>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="F4" t="n">
         <v>2500</v>
       </c>
-      <c r="G4" s="10" t="n">
+      <c r="G4" t="n">
         <v>15</v>
       </c>
-      <c r="H4" s="10" t="n">
+      <c r="H4" t="n">
         <v>37500</v>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>赤霧島ボトル</t>
         </is>
       </c>
-      <c r="J4" s="10" t="n">
+      <c r="J4" t="n">
         <v>7500</v>
       </c>
-      <c r="K4" s="10" t="n">
+      <c r="K4" t="n">
         <v>1</v>
       </c>
-      <c r="L4" s="10" t="n">
+      <c r="L4" t="n">
         <v>7500</v>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2026/05/01</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>3位</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>和牛ヒレ</t>
         </is>
       </c>
-      <c r="F5" s="10" t="n">
+      <c r="F5" t="n">
         <v>11000</v>
       </c>
-      <c r="G5" s="10" t="n">
+      <c r="G5" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="10" t="n">
+      <c r="H5" t="n">
         <v>22000</v>
       </c>
-      <c r="I5" s="14" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>角ハイボール</t>
         </is>
       </c>
-      <c r="J5" s="10" t="n">
+      <c r="J5" t="n">
         <v>680</v>
       </c>
-      <c r="K5" s="10" t="n">
+      <c r="K5" t="n">
         <v>7</v>
       </c>
-      <c r="L5" s="10" t="n">
+      <c r="L5" t="n">
         <v>4760</v>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2026/05/02</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>土</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>1位</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>宴会コース</t>
         </is>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" t="n">
         <v>6000</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" t="n">
         <v>12</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" t="n">
         <v>72000</v>
       </c>
-      <c r="I6" s="15" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>プレミアムモルツ生</t>
         </is>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="J6" t="n">
         <v>880</v>
       </c>
-      <c r="K6" s="6" t="n">
+      <c r="K6" t="n">
         <v>12</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="L6" t="n">
         <v>10560</v>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>2026/05/02</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>土</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>2位</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>あさり膳ハーフ</t>
         </is>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" t="n">
         <v>2500</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" t="n">
         <v>24</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" t="n">
         <v>60000</v>
       </c>
-      <c r="I7" s="15" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>プレミアムモルツ中瓶</t>
         </is>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J7" t="n">
         <v>980</v>
       </c>
-      <c r="K7" s="6" t="n">
+      <c r="K7" t="n">
         <v>9</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="L7" t="n">
         <v>8820</v>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2026/05/02</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>土</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>3位</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>宝家膳</t>
         </is>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" t="n">
         <v>5000</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G8" t="n">
         <v>8</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" t="n">
         <v>40000</v>
       </c>
-      <c r="I8" s="15" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>ウーロン茶</t>
         </is>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J8" t="n">
         <v>400</v>
       </c>
-      <c r="K8" s="6" t="n">
+      <c r="K8" t="n">
         <v>19</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="L8" t="n">
         <v>7600</v>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2026/05/03</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n">
+      <c r="B9" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>1位</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>あさり膳ハーフ</t>
         </is>
       </c>
-      <c r="F9" s="10" t="n">
+      <c r="F9" t="n">
         <v>2500</v>
       </c>
-      <c r="G9" s="10" t="n">
+      <c r="G9" t="n">
         <v>63</v>
       </c>
-      <c r="H9" s="10" t="n">
+      <c r="H9" t="n">
         <v>157500</v>
       </c>
-      <c r="I9" s="14" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>山崎ボトル</t>
         </is>
       </c>
-      <c r="J9" s="10" t="n">
+      <c r="J9" t="n">
         <v>29800</v>
       </c>
-      <c r="K9" s="10" t="n">
+      <c r="K9" t="n">
         <v>1</v>
       </c>
-      <c r="L9" s="10" t="n">
+      <c r="L9" t="n">
         <v>29800</v>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>2026/05/03</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n">
+      <c r="B10" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>2位</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>宴会コース</t>
         </is>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F10" t="n">
         <v>5000</v>
       </c>
-      <c r="G10" s="10" t="n">
+      <c r="G10" t="n">
         <v>12</v>
       </c>
-      <c r="H10" s="10" t="n">
+      <c r="H10" t="n">
         <v>60000</v>
       </c>
-      <c r="I10" s="14" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>プレミアムモルツ生</t>
         </is>
       </c>
-      <c r="J10" s="10" t="n">
+      <c r="J10" t="n">
         <v>880</v>
       </c>
-      <c r="K10" s="10" t="n">
+      <c r="K10" t="n">
         <v>23</v>
       </c>
-      <c r="L10" s="10" t="n">
+      <c r="L10" t="n">
         <v>20240</v>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>2026/05/03</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n">
+      <c r="B11" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>3位</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>あさり膳ハーフ夜</t>
         </is>
       </c>
-      <c r="F11" s="10" t="n">
+      <c r="F11" t="n">
         <v>3500</v>
       </c>
-      <c r="G11" s="10" t="n">
+      <c r="G11" t="n">
         <v>14</v>
       </c>
-      <c r="H11" s="10" t="n">
+      <c r="H11" t="n">
         <v>49000</v>
       </c>
-      <c r="I11" s="14" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>オールフリー</t>
         </is>
       </c>
-      <c r="J11" s="10" t="n">
+      <c r="J11" t="n">
         <v>680</v>
       </c>
-      <c r="K11" s="10" t="n">
+      <c r="K11" t="n">
         <v>15</v>
       </c>
-      <c r="L11" s="10" t="n">
+      <c r="L11" t="n">
         <v>10200</v>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>2026/05/04</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" t="n">
         <v>4</v>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>1位</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>あさり膳ハーフ</t>
         </is>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" t="n">
         <v>2500</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="G12" t="n">
         <v>26</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H12" t="n">
         <v>65000</v>
       </c>
-      <c r="I12" s="15" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>プレミアムモルツ生</t>
         </is>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="J12" t="n">
         <v>880</v>
       </c>
-      <c r="K12" s="6" t="n">
+      <c r="K12" t="n">
         <v>28</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="L12" t="n">
         <v>24640</v>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>2026/05/04</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" t="n">
         <v>4</v>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>2位</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>あさり膳ハーフ夜</t>
         </is>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F13" t="n">
         <v>3500</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="G13" t="n">
         <v>14</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="H13" t="n">
         <v>49000</v>
       </c>
-      <c r="I13" s="15" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Free日本酒</t>
         </is>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="J13" t="n">
         <v>980</v>
       </c>
-      <c r="K13" s="6" t="n">
+      <c r="K13" t="n">
         <v>8</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="L13" t="n">
         <v>7840</v>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>2026/05/04</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" t="n">
         <v>4</v>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>3位</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>あさり膳刺身</t>
         </is>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="F14" t="n">
         <v>2400</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="G14" t="n">
         <v>13</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="H14" t="n">
         <v>31200</v>
       </c>
-      <c r="I14" s="15" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>ウーロン茶</t>
         </is>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="J14" t="n">
         <v>400</v>
       </c>
-      <c r="K14" s="6" t="n">
+      <c r="K14" t="n">
         <v>15</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="L14" t="n">
         <v>6000</v>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>2026/05/05</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n">
+      <c r="B15" t="n">
         <v>5</v>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>1位</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>あさり膳ハーフ</t>
         </is>
       </c>
-      <c r="F15" s="10" t="n">
+      <c r="F15" t="n">
         <v>2500</v>
       </c>
-      <c r="G15" s="10" t="n">
+      <c r="G15" t="n">
         <v>42</v>
       </c>
-      <c r="H15" s="10" t="n">
+      <c r="H15" t="n">
         <v>105000</v>
       </c>
-      <c r="I15" s="14" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>プレミアムモルツ生</t>
         </is>
       </c>
-      <c r="J15" s="10" t="n">
+      <c r="J15" t="n">
         <v>880</v>
       </c>
-      <c r="K15" s="10" t="n">
+      <c r="K15" t="n">
         <v>19</v>
       </c>
-      <c r="L15" s="10" t="n">
+      <c r="L15" t="n">
         <v>16720</v>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>2026/05/05</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n">
+      <c r="B16" t="n">
         <v>5</v>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>2位</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>宝家膳</t>
         </is>
       </c>
-      <c r="F16" s="10" t="n">
+      <c r="F16" t="n">
         <v>6500</v>
       </c>
-      <c r="G16" s="10" t="n">
+      <c r="G16" t="n">
         <v>6</v>
       </c>
-      <c r="H16" s="10" t="n">
+      <c r="H16" t="n">
         <v>39000</v>
       </c>
-      <c r="I16" s="14" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>オールフリー</t>
         </is>
       </c>
-      <c r="J16" s="10" t="n">
+      <c r="J16" t="n">
         <v>680</v>
       </c>
-      <c r="K16" s="10" t="n">
+      <c r="K16" t="n">
         <v>23</v>
       </c>
-      <c r="L16" s="10" t="n">
+      <c r="L16" t="n">
         <v>15640</v>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>2026/05/05</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n">
+      <c r="B17" t="n">
         <v>5</v>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>3位</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Freeゲストハウス</t>
         </is>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="F17" t="n">
         <v>17000</v>
       </c>
-      <c r="G17" s="10" t="n">
+      <c r="G17" t="n">
         <v>2</v>
       </c>
-      <c r="H17" s="10" t="n">
+      <c r="H17" t="n">
         <v>34000</v>
       </c>
-      <c r="I17" s="14" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>吉四六ボトル</t>
         </is>
       </c>
-      <c r="J17" s="10" t="n">
+      <c r="J17" t="n">
         <v>7980</v>
       </c>
-      <c r="K17" s="10" t="n">
+      <c r="K17" t="n">
         <v>1</v>
       </c>
-      <c r="L17" s="10" t="n">
+      <c r="L17" t="n">
         <v>7980</v>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>2026/05/06</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" t="n">
         <v>6</v>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>1位</t>
         </is>
       </c>
-      <c r="E18" s="15" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>あさり膳ハーフ</t>
         </is>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="F18" t="n">
         <v>2500</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="G18" t="n">
         <v>44</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="H18" t="n">
         <v>110000</v>
       </c>
-      <c r="I18" s="15" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>プレミアムモルツ生</t>
         </is>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="J18" t="n">
         <v>880</v>
       </c>
-      <c r="K18" s="6" t="n">
+      <c r="K18" t="n">
         <v>16</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="L18" t="n">
         <v>14080</v>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>2026/05/06</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" t="n">
         <v>6</v>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>2位</t>
         </is>
       </c>
-      <c r="E19" s="15" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>あさり膳串揚げ</t>
         </is>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="F19" t="n">
         <v>2400</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="G19" t="n">
         <v>11</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="H19" t="n">
         <v>26400</v>
       </c>
-      <c r="I19" s="15" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>角ハイボール</t>
         </is>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="J19" t="n">
         <v>680</v>
       </c>
-      <c r="K19" s="6" t="n">
+      <c r="K19" t="n">
         <v>18</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="L19" t="n">
         <v>12240</v>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>2026/05/06</t>
         </is>
       </c>
-      <c r="B20" s="4" t="n">
+      <c r="B20" t="n">
         <v>6</v>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>3位</t>
         </is>
       </c>
-      <c r="E20" s="15" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>あさり膳刺身</t>
         </is>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="F20" t="n">
         <v>2400</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="G20" t="n">
         <v>10</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="H20" t="n">
         <v>24000</v>
       </c>
-      <c r="I20" s="15" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>オールフリー</t>
         </is>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="J20" t="n">
         <v>680</v>
       </c>
-      <c r="K20" s="6" t="n">
+      <c r="K20" t="n">
         <v>14</v>
       </c>
-      <c r="L20" s="6" t="n">
+      <c r="L20" t="n">
         <v>9520</v>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>2026/05/07</t>
         </is>
       </c>
-      <c r="B21" s="8" t="n">
+      <c r="B21" t="n">
         <v>7</v>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>1位</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr"/>
-      <c r="F21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="14" t="inlineStr"/>
-      <c r="J21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>2026/05/07</t>
         </is>
       </c>
-      <c r="B22" s="8" t="n">
+      <c r="B22" t="n">
         <v>7</v>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>2位</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr"/>
-      <c r="F22" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="14" t="inlineStr"/>
-      <c r="J22" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>2026/05/07</t>
         </is>
       </c>
-      <c r="B23" s="8" t="n">
+      <c r="B23" t="n">
         <v>7</v>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>3位</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr"/>
-      <c r="F23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="14" t="inlineStr"/>
-      <c r="J23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>2026/05/08</t>
         </is>
       </c>
-      <c r="B24" s="4" t="n">
+      <c r="B24" t="n">
         <v>8</v>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>1位</t>
         </is>
       </c>
-      <c r="E24" s="15" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>宴会コース</t>
         </is>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="F24" t="n">
         <v>5000</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="G24" t="n">
         <v>17</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="H24" t="n">
         <v>85000</v>
       </c>
-      <c r="I24" s="15" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>プレミアムモルツ生</t>
         </is>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="J24" t="n">
         <v>880</v>
       </c>
-      <c r="K24" s="6" t="n">
+      <c r="K24" t="n">
         <v>21</v>
       </c>
-      <c r="L24" s="6" t="n">
+      <c r="L24" t="n">
         <v>18480</v>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>2026/05/08</t>
         </is>
       </c>
-      <c r="B25" s="4" t="n">
+      <c r="B25" t="n">
         <v>8</v>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>2位</t>
         </is>
       </c>
-      <c r="E25" s="15" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>あさり膳ハーフ</t>
         </is>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="F25" t="n">
         <v>2500</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="G25" t="n">
         <v>23</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="H25" t="n">
         <v>57500</v>
       </c>
-      <c r="I25" s="15" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>オールフリー</t>
         </is>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="J25" t="n">
         <v>680</v>
       </c>
-      <c r="K25" s="6" t="n">
+      <c r="K25" t="n">
         <v>20</v>
       </c>
-      <c r="L25" s="6" t="n">
+      <c r="L25" t="n">
         <v>13600</v>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>2026/05/08</t>
         </is>
       </c>
-      <c r="B26" s="4" t="n">
+      <c r="B26" t="n">
         <v>8</v>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>3位</t>
         </is>
       </c>
-      <c r="E26" s="15" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>季節の一品</t>
         </is>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="F26" t="n">
         <v>1980</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="G26" t="n">
         <v>11</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="H26" t="n">
         <v>21780</v>
       </c>
-      <c r="I26" s="15" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>角ハイボール</t>
         </is>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="J26" t="n">
         <v>680</v>
       </c>
-      <c r="K26" s="6" t="n">
+      <c r="K26" t="n">
         <v>13</v>
       </c>
-      <c r="L26" s="6" t="n">
+      <c r="L26" t="n">
         <v>8840</v>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>2026/05/09</t>
         </is>
       </c>
-      <c r="B27" s="8" t="n">
+      <c r="B27" t="n">
         <v>9</v>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>土</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>1位</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>あさり膳ハーフ</t>
         </is>
       </c>
-      <c r="F27" s="10" t="n">
+      <c r="F27" t="n">
         <v>2500</v>
       </c>
-      <c r="G27" s="10" t="n">
+      <c r="G27" t="n">
         <v>30</v>
       </c>
-      <c r="H27" s="10" t="n">
+      <c r="H27" t="n">
         <v>75000</v>
       </c>
-      <c r="I27" s="14" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>プレミアムモルツ生</t>
         </is>
       </c>
-      <c r="J27" s="10" t="n">
+      <c r="J27" t="n">
         <v>880</v>
       </c>
-      <c r="K27" s="10" t="n">
+      <c r="K27" t="n">
         <v>36</v>
       </c>
-      <c r="L27" s="10" t="n">
+      <c r="L27" t="n">
         <v>31680</v>
       </c>
     </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>2026/05/09</t>
         </is>
       </c>
-      <c r="B28" s="8" t="n">
+      <c r="B28" t="n">
         <v>9</v>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>土</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>2位</t>
         </is>
       </c>
-      <c r="E28" s="14" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>宴会コース</t>
         </is>
       </c>
-      <c r="F28" s="10" t="n">
+      <c r="F28" t="n">
         <v>8000</v>
       </c>
-      <c r="G28" s="10" t="n">
+      <c r="G28" t="n">
         <v>5</v>
       </c>
-      <c r="H28" s="10" t="n">
+      <c r="H28" t="n">
         <v>40000</v>
       </c>
-      <c r="I28" s="14" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>飲み放題</t>
         </is>
       </c>
-      <c r="J28" s="10" t="n">
+      <c r="J28" t="n">
         <v>4000</v>
       </c>
-      <c r="K28" s="10" t="n">
+      <c r="K28" t="n">
         <v>5</v>
       </c>
-      <c r="L28" s="10" t="n">
+      <c r="L28" t="n">
         <v>20000</v>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>2026/05/09</t>
         </is>
       </c>
-      <c r="B29" s="8" t="n">
+      <c r="B29" t="n">
         <v>9</v>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>土</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>3位</t>
         </is>
       </c>
-      <c r="E29" s="14" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Freeゲストハウス</t>
         </is>
       </c>
-      <c r="F29" s="10" t="n">
+      <c r="F29" t="n">
         <v>12000</v>
       </c>
-      <c r="G29" s="10" t="n">
+      <c r="G29" t="n">
         <v>3</v>
       </c>
-      <c r="H29" s="10" t="n">
+      <c r="H29" t="n">
         <v>36000</v>
       </c>
-      <c r="I29" s="14" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>吉四六ボトル</t>
         </is>
       </c>
-      <c r="J29" s="10" t="n">
+      <c r="J29" t="n">
         <v>7980</v>
       </c>
-      <c r="K29" s="10" t="n">
+      <c r="K29" t="n">
         <v>2</v>
       </c>
-      <c r="L29" s="10" t="n">
+      <c r="L29" t="n">
         <v>15960</v>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>2026/05/10</t>
         </is>
       </c>
-      <c r="B30" s="4" t="n">
+      <c r="B30" t="n">
         <v>10</v>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>1位</t>
         </is>
       </c>
-      <c r="E30" s="15" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>宴会コース</t>
         </is>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="F30" t="n">
         <v>5000</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="G30" t="n">
         <v>13</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="H30" t="n">
         <v>65000</v>
       </c>
-      <c r="I30" s="15" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>プレミアムモルツ生</t>
         </is>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="J30" t="n">
         <v>880</v>
       </c>
-      <c r="K30" s="6" t="n">
+      <c r="K30" t="n">
         <v>20</v>
       </c>
-      <c r="L30" s="6" t="n">
+      <c r="L30" t="n">
         <v>17600</v>
       </c>
     </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>2026/05/10</t>
         </is>
       </c>
-      <c r="B31" s="4" t="n">
+      <c r="B31" t="n">
         <v>10</v>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>2位</t>
         </is>
       </c>
-      <c r="E31" s="15" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>あさり膳刺身</t>
         </is>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="F31" t="n">
         <v>2400</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="G31" t="n">
         <v>23</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="H31" t="n">
         <v>55200</v>
       </c>
-      <c r="I31" s="15" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>プレミアムモルツ中瓶</t>
         </is>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="J31" t="n">
         <v>980</v>
       </c>
-      <c r="K31" s="6" t="n">
+      <c r="K31" t="n">
         <v>5</v>
       </c>
-      <c r="L31" s="6" t="n">
+      <c r="L31" t="n">
         <v>4900</v>
       </c>
     </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>2026/05/10</t>
         </is>
       </c>
-      <c r="B32" s="4" t="n">
+      <c r="B32" t="n">
         <v>10</v>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>3位</t>
         </is>
       </c>
-      <c r="E32" s="15" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>あさり膳ハーフ</t>
         </is>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="F32" t="n">
         <v>2500</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="G32" t="n">
         <v>16</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="H32" t="n">
         <v>40000</v>
       </c>
-      <c r="I32" s="15" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>オールフリー</t>
         </is>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="J32" t="n">
         <v>680</v>
       </c>
-      <c r="K32" s="6" t="n">
+      <c r="K32" t="n">
         <v>6</v>
       </c>
-      <c r="L32" s="6" t="n">
+      <c r="L32" t="n">
         <v>4080</v>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>2026/05/11</t>
         </is>
       </c>
-      <c r="B33" s="8" t="n">
+      <c r="B33" t="n">
         <v>11</v>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>1位</t>
         </is>
       </c>
-      <c r="E33" s="14" t="inlineStr"/>
-      <c r="F33" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="14" t="inlineStr"/>
-      <c r="J33" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>2026/05/11</t>
         </is>
       </c>
-      <c r="B34" s="8" t="n">
+      <c r="B34" t="n">
         <v>11</v>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>2位</t>
         </is>
       </c>
-      <c r="E34" s="14" t="inlineStr"/>
-      <c r="F34" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="14" t="inlineStr"/>
-      <c r="J34" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>2026/05/11</t>
         </is>
       </c>
-      <c r="B35" s="8" t="n">
+      <c r="B35" t="n">
         <v>11</v>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>3位</t>
         </is>
       </c>
-      <c r="E35" s="14" t="inlineStr"/>
-      <c r="F35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="14" t="inlineStr"/>
-      <c r="J35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>2026/05/12</t>
         </is>
       </c>
-      <c r="B36" s="4" t="n">
+      <c r="B36" t="n">
         <v>12</v>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>1位</t>
         </is>
       </c>
-      <c r="E36" s="15" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>宴会コース</t>
         </is>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="F36" t="n">
         <v>10000</v>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="G36" t="n">
         <v>24</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="H36" t="n">
         <v>240000</v>
       </c>
-      <c r="I36" s="15" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>プレミアムモルツ生</t>
         </is>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="J36" t="n">
         <v>880</v>
       </c>
-      <c r="K36" s="6" t="n">
+      <c r="K36" t="n">
         <v>25</v>
       </c>
-      <c r="L36" s="6" t="n">
+      <c r="L36" t="n">
         <v>22000</v>
       </c>
     </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>2026/05/12</t>
         </is>
       </c>
-      <c r="B37" s="4" t="n">
+      <c r="B37" t="n">
         <v>12</v>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>2位</t>
         </is>
       </c>
-      <c r="E37" s="15" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>外販</t>
         </is>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="F37" t="n">
         <v>5000</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="G37" t="n">
         <v>20</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="H37" t="n">
         <v>100000</v>
       </c>
-      <c r="I37" s="15" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>あらごし梅酒</t>
         </is>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="J37" t="n">
         <v>650</v>
       </c>
-      <c r="K37" s="6" t="n">
+      <c r="K37" t="n">
         <v>16</v>
       </c>
-      <c r="L37" s="6" t="n">
+      <c r="L37" t="n">
         <v>10400</v>
       </c>
     </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>2026/05/12</t>
         </is>
       </c>
-      <c r="B38" s="4" t="n">
+      <c r="B38" t="n">
         <v>12</v>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>3位</t>
         </is>
       </c>
-      <c r="E38" s="15" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>あさり膳ハーフ</t>
         </is>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="F38" t="n">
         <v>2400</v>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="G38" t="n">
         <v>34</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="H38" t="n">
         <v>81600</v>
       </c>
-      <c r="I38" s="15" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>峰の精四合</t>
         </is>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="J38" t="n">
         <v>8480</v>
       </c>
-      <c r="K38" s="6" t="n">
+      <c r="K38" t="n">
         <v>1</v>
       </c>
-      <c r="L38" s="6" t="n">
+      <c r="L38" t="n">
         <v>8480</v>
       </c>
     </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>2026/05/13</t>
         </is>
       </c>
-      <c r="B39" s="8" t="n">
+      <c r="B39" t="n">
         <v>13</v>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>1位</t>
         </is>
       </c>
-      <c r="E39" s="14" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>宴会コース</t>
         </is>
       </c>
-      <c r="F39" s="10" t="n">
+      <c r="F39" t="n">
         <v>24000</v>
       </c>
-      <c r="G39" s="10" t="n">
+      <c r="G39" t="n">
         <v>4</v>
       </c>
-      <c r="H39" s="10" t="n">
+      <c r="H39" t="n">
         <v>96000</v>
       </c>
-      <c r="I39" s="14" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>ＦｒｅｅワインＢ</t>
         </is>
       </c>
-      <c r="J39" s="10" t="n">
+      <c r="J39" t="n">
         <v>27800</v>
       </c>
-      <c r="K39" s="10" t="n">
+      <c r="K39" t="n">
         <v>1</v>
       </c>
-      <c r="L39" s="10" t="n">
+      <c r="L39" t="n">
         <v>27800</v>
       </c>
     </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>2026/05/13</t>
         </is>
       </c>
-      <c r="B40" s="8" t="n">
+      <c r="B40" t="n">
         <v>13</v>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>2位</t>
         </is>
       </c>
-      <c r="E40" s="14" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>宴会コース</t>
         </is>
       </c>
-      <c r="F40" s="10" t="n">
+      <c r="F40" t="n">
         <v>8000</v>
       </c>
-      <c r="G40" s="10" t="n">
+      <c r="G40" t="n">
         <v>8</v>
       </c>
-      <c r="H40" s="10" t="n">
+      <c r="H40" t="n">
         <v>64000</v>
       </c>
-      <c r="I40" s="14" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>プレミアムモルツ生</t>
         </is>
       </c>
-      <c r="J40" s="10" t="n">
+      <c r="J40" t="n">
         <v>880</v>
       </c>
-      <c r="K40" s="10" t="n">
+      <c r="K40" t="n">
         <v>20</v>
       </c>
-      <c r="L40" s="10" t="n">
+      <c r="L40" t="n">
         <v>17600</v>
       </c>
     </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>2026/05/13</t>
         </is>
       </c>
-      <c r="B41" s="8" t="n">
+      <c r="B41" t="n">
         <v>13</v>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>3位</t>
         </is>
       </c>
-      <c r="E41" s="14" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>宴会コース</t>
         </is>
       </c>
-      <c r="F41" s="10" t="n">
+      <c r="F41" t="n">
         <v>5000</v>
       </c>
-      <c r="G41" s="10" t="n">
+      <c r="G41" t="n">
         <v>12</v>
       </c>
-      <c r="H41" s="10" t="n">
+      <c r="H41" t="n">
         <v>60000</v>
       </c>
-      <c r="I41" s="14" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>角ハイボール</t>
         </is>
       </c>
-      <c r="J41" s="10" t="n">
+      <c r="J41" t="n">
         <v>680</v>
       </c>
-      <c r="K41" s="10" t="n">
+      <c r="K41" t="n">
         <v>6</v>
       </c>
-      <c r="L41" s="10" t="n">
+      <c r="L41" t="n">
         <v>4080</v>
       </c>
     </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>2026/05/14</t>
         </is>
       </c>
-      <c r="B42" s="4" t="n">
+      <c r="B42" t="n">
         <v>14</v>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>1位</t>
         </is>
       </c>
-      <c r="E42" s="15" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>宝家膳</t>
         </is>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="F42" t="n">
         <v>5000</v>
       </c>
-      <c r="G42" s="6" t="n">
+      <c r="G42" t="n">
         <v>36</v>
       </c>
-      <c r="H42" s="6" t="n">
+      <c r="H42" t="n">
         <v>180000</v>
       </c>
-      <c r="I42" s="15" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>飲み放題</t>
         </is>
       </c>
-      <c r="J42" s="6" t="n">
+      <c r="J42" t="n">
         <v>3000</v>
       </c>
-      <c r="K42" s="6" t="n">
+      <c r="K42" t="n">
         <v>14</v>
       </c>
-      <c r="L42" s="6" t="n">
+      <c r="L42" t="n">
         <v>42000</v>
       </c>
     </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>2026/05/14</t>
         </is>
       </c>
-      <c r="B43" s="4" t="n">
+      <c r="B43" t="n">
         <v>14</v>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>2位</t>
         </is>
       </c>
-      <c r="E43" s="15" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>宴会コース</t>
         </is>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="F43" t="n">
         <v>5000</v>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="G43" t="n">
         <v>18</v>
       </c>
-      <c r="H43" s="6" t="n">
+      <c r="H43" t="n">
         <v>90000</v>
       </c>
-      <c r="I43" s="15" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>プレミアムモルツ生</t>
         </is>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="J43" t="n">
         <v>880</v>
       </c>
-      <c r="K43" s="6" t="n">
+      <c r="K43" t="n">
         <v>32</v>
       </c>
-      <c r="L43" s="6" t="n">
+      <c r="L43" t="n">
         <v>28160</v>
       </c>
     </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>2026/05/14</t>
         </is>
       </c>
-      <c r="B44" s="4" t="n">
+      <c r="B44" t="n">
         <v>14</v>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>3位</t>
         </is>
       </c>
-      <c r="E44" s="15" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>宴会コース</t>
         </is>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="F44" t="n">
         <v>15500</v>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="G44" t="n">
         <v>4</v>
       </c>
-      <c r="H44" s="6" t="n">
+      <c r="H44" t="n">
         <v>62000</v>
       </c>
-      <c r="I44" s="15" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>プレミアムモルツ中瓶</t>
         </is>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="J44" t="n">
         <v>980</v>
       </c>
-      <c r="K44" s="6" t="n">
+      <c r="K44" t="n">
         <v>17</v>
       </c>
-      <c r="L44" s="6" t="n">
+      <c r="L44" t="n">
         <v>16660</v>
       </c>
     </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="7" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>2026/05/15</t>
         </is>
       </c>
-      <c r="B45" s="8" t="n">
+      <c r="B45" t="n">
         <v>15</v>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>1位</t>
         </is>
       </c>
-      <c r="E45" s="14" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>宴会コース</t>
         </is>
       </c>
-      <c r="F45" s="10" t="n">
+      <c r="F45" t="n">
         <v>10000</v>
       </c>
-      <c r="G45" s="10" t="n">
+      <c r="G45" t="n">
         <v>19</v>
       </c>
-      <c r="H45" s="10" t="n">
+      <c r="H45" t="n">
         <v>190000</v>
       </c>
-      <c r="I45" s="14" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>飲み放題</t>
         </is>
       </c>
-      <c r="J45" s="10" t="n">
+      <c r="J45" t="n">
         <v>3500</v>
       </c>
-      <c r="K45" s="10" t="n">
+      <c r="K45" t="n">
         <v>10</v>
       </c>
-      <c r="L45" s="10" t="n">
+      <c r="L45" t="n">
         <v>35000</v>
       </c>
     </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="7" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>2026/05/15</t>
         </is>
       </c>
-      <c r="B46" s="8" t="n">
+      <c r="B46" t="n">
         <v>15</v>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>2位</t>
         </is>
       </c>
-      <c r="E46" s="14" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>あさり膳ハーフ</t>
         </is>
       </c>
-      <c r="F46" s="10" t="n">
+      <c r="F46" t="n">
         <v>2500</v>
       </c>
-      <c r="G46" s="10" t="n">
+      <c r="G46" t="n">
         <v>27</v>
       </c>
-      <c r="H46" s="10" t="n">
+      <c r="H46" t="n">
         <v>67500</v>
       </c>
-      <c r="I46" s="14" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>プレミアムモルツ生</t>
         </is>
       </c>
-      <c r="J46" s="10" t="n">
+      <c r="J46" t="n">
         <v>880</v>
       </c>
-      <c r="K46" s="10" t="n">
+      <c r="K46" t="n">
         <v>36</v>
       </c>
-      <c r="L46" s="10" t="n">
+      <c r="L46" t="n">
         <v>31680</v>
       </c>
     </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="7" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>2026/05/15</t>
         </is>
       </c>
-      <c r="B47" s="8" t="n">
+      <c r="B47" t="n">
         <v>15</v>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>3位</t>
         </is>
       </c>
-      <c r="E47" s="14" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>季節の一品</t>
         </is>
       </c>
-      <c r="F47" s="10" t="n">
+      <c r="F47" t="n">
         <v>1980</v>
       </c>
-      <c r="G47" s="10" t="n">
+      <c r="G47" t="n">
         <v>30</v>
       </c>
-      <c r="H47" s="10" t="n">
+      <c r="H47" t="n">
         <v>59400</v>
       </c>
-      <c r="I47" s="14" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>知多ハイボール</t>
         </is>
       </c>
-      <c r="J47" s="10" t="n">
+      <c r="J47" t="n">
         <v>980</v>
       </c>
-      <c r="K47" s="10" t="n">
+      <c r="K47" t="n">
         <v>25</v>
       </c>
-      <c r="L47" s="10" t="n">
+      <c r="L47" t="n">
         <v>24500</v>
       </c>
     </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>2026/05/16</t>
         </is>
       </c>
-      <c r="B48" s="4" t="n">
+      <c r="B48" t="n">
         <v>16</v>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>土</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>1位</t>
         </is>
       </c>
-      <c r="E48" s="15" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>あさり膳かき揚げ</t>
         </is>
       </c>
-      <c r="F48" s="6" t="n">
+      <c r="F48" t="n">
         <v>2400</v>
       </c>
-      <c r="G48" s="6" t="n">
+      <c r="G48" t="n">
         <v>38</v>
       </c>
-      <c r="H48" s="6" t="n">
+      <c r="H48" t="n">
         <v>91200</v>
       </c>
-      <c r="I48" s="15" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>プレミアムモルツ生</t>
         </is>
       </c>
-      <c r="J48" s="6" t="n">
+      <c r="J48" t="n">
         <v>880</v>
       </c>
-      <c r="K48" s="6" t="n">
+      <c r="K48" t="n">
         <v>22</v>
       </c>
-      <c r="L48" s="6" t="n">
+      <c r="L48" t="n">
         <v>19360</v>
       </c>
     </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>2026/05/16</t>
         </is>
       </c>
-      <c r="B49" s="4" t="n">
+      <c r="B49" t="n">
         <v>16</v>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>土</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>2位</t>
         </is>
       </c>
-      <c r="E49" s="15" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>宴会コース</t>
         </is>
       </c>
-      <c r="F49" s="6" t="n">
+      <c r="F49" t="n">
         <v>6000</v>
       </c>
-      <c r="G49" s="6" t="n">
+      <c r="G49" t="n">
         <v>15</v>
       </c>
-      <c r="H49" s="6" t="n">
+      <c r="H49" t="n">
         <v>90000</v>
       </c>
-      <c r="I49" s="15" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>吉四六ボトル</t>
         </is>
       </c>
-      <c r="J49" s="6" t="n">
+      <c r="J49" t="n">
         <v>7980</v>
       </c>
-      <c r="K49" s="6" t="n">
+      <c r="K49" t="n">
         <v>1</v>
       </c>
-      <c r="L49" s="6" t="n">
+      <c r="L49" t="n">
         <v>7980</v>
       </c>
     </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>2026/05/16</t>
         </is>
       </c>
-      <c r="B50" s="4" t="n">
+      <c r="B50" t="n">
         <v>16</v>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>土</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>3位</t>
         </is>
       </c>
-      <c r="E50" s="15" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>あさり膳ハーフ</t>
         </is>
       </c>
-      <c r="F50" s="6" t="n">
+      <c r="F50" t="n">
         <v>2500</v>
       </c>
-      <c r="G50" s="6" t="n">
+      <c r="G50" t="n">
         <v>26</v>
       </c>
-      <c r="H50" s="6" t="n">
+      <c r="H50" t="n">
         <v>65000</v>
       </c>
-      <c r="I50" s="15" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>プレミアムモルツ中瓶</t>
         </is>
       </c>
-      <c r="J50" s="6" t="n">
+      <c r="J50" t="n">
         <v>980</v>
       </c>
-      <c r="K50" s="6" t="n">
+      <c r="K50" t="n">
         <v>8</v>
       </c>
-      <c r="L50" s="6" t="n">
+      <c r="L50" t="n">
         <v>7840</v>
       </c>
     </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="7" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>2026/05/17</t>
         </is>
       </c>
-      <c r="B51" s="8" t="n">
+      <c r="B51" t="n">
         <v>17</v>
       </c>
-      <c r="C51" s="7" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>1位</t>
         </is>
       </c>
-      <c r="E51" s="14" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>宴会コース</t>
         </is>
       </c>
-      <c r="F51" s="10" t="n">
+      <c r="F51" t="n">
         <v>5000</v>
       </c>
-      <c r="G51" s="10" t="n">
+      <c r="G51" t="n">
         <v>19</v>
       </c>
-      <c r="H51" s="10" t="n">
+      <c r="H51" t="n">
         <v>95000</v>
       </c>
-      <c r="I51" s="14" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>飲み放題</t>
         </is>
       </c>
-      <c r="J51" s="10" t="n">
+      <c r="J51" t="n">
         <v>3300</v>
       </c>
-      <c r="K51" s="10" t="n">
+      <c r="K51" t="n">
         <v>19</v>
       </c>
-      <c r="L51" s="10" t="n">
+      <c r="L51" t="n">
         <v>62700</v>
       </c>
     </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="7" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>2026/05/17</t>
         </is>
       </c>
-      <c r="B52" s="8" t="n">
+      <c r="B52" t="n">
         <v>17</v>
       </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="D52" s="7" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>2位</t>
         </is>
       </c>
-      <c r="E52" s="14" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>あさり膳ハーフ夜</t>
         </is>
       </c>
-      <c r="F52" s="10" t="n">
+      <c r="F52" t="n">
         <v>3500</v>
       </c>
-      <c r="G52" s="10" t="n">
+      <c r="G52" t="n">
         <v>20</v>
       </c>
-      <c r="H52" s="10" t="n">
+      <c r="H52" t="n">
         <v>70000</v>
       </c>
-      <c r="I52" s="14" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>プレミアムモルツ生</t>
         </is>
       </c>
-      <c r="J52" s="10" t="n">
+      <c r="J52" t="n">
         <v>880</v>
       </c>
-      <c r="K52" s="10" t="n">
+      <c r="K52" t="n">
         <v>25</v>
       </c>
-      <c r="L52" s="10" t="n">
+      <c r="L52" t="n">
         <v>22000</v>
       </c>
     </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="7" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>2026/05/17</t>
         </is>
       </c>
-      <c r="B53" s="8" t="n">
+      <c r="B53" t="n">
         <v>17</v>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>3位</t>
         </is>
       </c>
-      <c r="E53" s="14" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>あさり膳刺身</t>
         </is>
       </c>
-      <c r="F53" s="10" t="n">
+      <c r="F53" t="n">
         <v>2400</v>
       </c>
-      <c r="G53" s="10" t="n">
+      <c r="G53" t="n">
         <v>27</v>
       </c>
-      <c r="H53" s="10" t="n">
+      <c r="H53" t="n">
         <v>64800</v>
       </c>
-      <c r="I53" s="14" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>オールフリー</t>
         </is>
       </c>
-      <c r="J53" s="10" t="n">
+      <c r="J53" t="n">
         <v>680</v>
       </c>
-      <c r="K53" s="10" t="n">
+      <c r="K53" t="n">
         <v>12</v>
       </c>
-      <c r="L53" s="10" t="n">
+      <c r="L53" t="n">
         <v>8160</v>
       </c>
     </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>2026/05/18</t>
         </is>
       </c>
-      <c r="B54" s="4" t="n">
+      <c r="B54" t="n">
         <v>18</v>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>1位</t>
         </is>
       </c>
-      <c r="E54" s="15" t="inlineStr"/>
-      <c r="F54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="15" t="inlineStr"/>
-      <c r="J54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>2026/05/18</t>
         </is>
       </c>
-      <c r="B55" s="4" t="n">
+      <c r="B55" t="n">
         <v>18</v>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>2位</t>
         </is>
       </c>
-      <c r="E55" s="15" t="inlineStr"/>
-      <c r="F55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" s="15" t="inlineStr"/>
-      <c r="J55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>2026/05/18</t>
         </is>
       </c>
-      <c r="B56" s="4" t="n">
+      <c r="B56" t="n">
         <v>18</v>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>3位</t>
         </is>
       </c>
-      <c r="E56" s="15" t="inlineStr"/>
-      <c r="F56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="15" t="inlineStr"/>
-      <c r="J56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="7" t="inlineStr">
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="B57" s="8" t="n">
+      <c r="B57" t="n">
         <v>19</v>
       </c>
-      <c r="C57" s="7" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="D57" s="7" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>1位</t>
         </is>
       </c>
-      <c r="E57" s="14" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>宴会コース</t>
         </is>
       </c>
-      <c r="F57" s="10" t="n">
+      <c r="F57" t="n">
         <v>19000</v>
       </c>
-      <c r="G57" s="10" t="n">
+      <c r="G57" t="n">
         <v>6</v>
       </c>
-      <c r="H57" s="10" t="n">
+      <c r="H57" t="n">
         <v>114000</v>
       </c>
-      <c r="I57" s="14" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>プレミアムモルツ生</t>
         </is>
       </c>
-      <c r="J57" s="10" t="n">
+      <c r="J57" t="n">
         <v>880</v>
       </c>
-      <c r="K57" s="10" t="n">
+      <c r="K57" t="n">
         <v>38</v>
       </c>
-      <c r="L57" s="10" t="n">
+      <c r="L57" t="n">
         <v>33440</v>
       </c>
     </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="7" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="B58" s="8" t="n">
+      <c r="B58" t="n">
         <v>19</v>
       </c>
-      <c r="C58" s="7" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="D58" s="7" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>2位</t>
         </is>
       </c>
-      <c r="E58" s="14" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>あさり膳ハーフ</t>
         </is>
       </c>
-      <c r="F58" s="10" t="n">
+      <c r="F58" t="n">
         <v>2500</v>
       </c>
-      <c r="G58" s="10" t="n">
+      <c r="G58" t="n">
         <v>28</v>
       </c>
-      <c r="H58" s="10" t="n">
+      <c r="H58" t="n">
         <v>70000</v>
       </c>
-      <c r="I58" s="14" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>ﾍﾞﾘﾝｼﾞｼﾞｬｰｼｬﾙﾄﾞﾈ</t>
         </is>
       </c>
-      <c r="J58" s="10" t="n">
+      <c r="J58" t="n">
         <v>9800</v>
       </c>
-      <c r="K58" s="10" t="n">
+      <c r="K58" t="n">
         <v>1</v>
       </c>
-      <c r="L58" s="10" t="n">
+      <c r="L58" t="n">
         <v>9800</v>
       </c>
     </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="7" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="B59" s="8" t="n">
+      <c r="B59" t="n">
         <v>19</v>
       </c>
-      <c r="C59" s="7" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>3位</t>
         </is>
       </c>
-      <c r="E59" s="14" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>宴会コース</t>
         </is>
       </c>
-      <c r="F59" s="10" t="n">
+      <c r="F59" t="n">
         <v>8000</v>
       </c>
-      <c r="G59" s="10" t="n">
+      <c r="G59" t="n">
         <v>7</v>
       </c>
-      <c r="H59" s="10" t="n">
+      <c r="H59" t="n">
         <v>56000</v>
       </c>
-      <c r="I59" s="14" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>吉四六ボトル</t>
         </is>
       </c>
-      <c r="J59" s="10" t="n">
+      <c r="J59" t="n">
         <v>7980</v>
       </c>
-      <c r="K59" s="10" t="n">
+      <c r="K59" t="n">
         <v>1</v>
       </c>
-      <c r="L59" s="10" t="n">
+      <c r="L59" t="n">
         <v>7980</v>
       </c>
     </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="3" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>2026/05/20</t>
         </is>
       </c>
-      <c r="B60" s="4" t="n">
+      <c r="B60" t="n">
         <v>20</v>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>1位</t>
         </is>
       </c>
-      <c r="E60" s="15" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>あさり膳ハーフ</t>
         </is>
       </c>
-      <c r="F60" s="6" t="n">
+      <c r="F60" t="n">
         <v>2500</v>
       </c>
-      <c r="G60" s="6" t="n">
+      <c r="G60" t="n">
         <v>30</v>
       </c>
-      <c r="H60" s="6" t="n">
+      <c r="H60" t="n">
         <v>75000</v>
       </c>
-      <c r="I60" s="15" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>吉四六ボトル</t>
         </is>
       </c>
-      <c r="J60" s="6" t="n">
+      <c r="J60" t="n">
         <v>7980</v>
       </c>
-      <c r="K60" s="6" t="n">
+      <c r="K60" t="n">
         <v>2</v>
       </c>
-      <c r="L60" s="6" t="n">
+      <c r="L60" t="n">
         <v>15960</v>
       </c>
     </row>
-    <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>2026/05/20</t>
         </is>
       </c>
-      <c r="B61" s="4" t="n">
+      <c r="B61" t="n">
         <v>20</v>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>2位</t>
         </is>
       </c>
-      <c r="E61" s="15" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>あさり膳ハーフ夜</t>
         </is>
       </c>
-      <c r="F61" s="6" t="n">
+      <c r="F61" t="n">
         <v>3500</v>
       </c>
-      <c r="G61" s="6" t="n">
+      <c r="G61" t="n">
         <v>5</v>
       </c>
-      <c r="H61" s="6" t="n">
+      <c r="H61" t="n">
         <v>17500</v>
       </c>
-      <c r="I61" s="15" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>プレミアムモルツ生</t>
         </is>
       </c>
-      <c r="J61" s="6" t="n">
+      <c r="J61" t="n">
         <v>880</v>
       </c>
-      <c r="K61" s="6" t="n">
+      <c r="K61" t="n">
         <v>13</v>
       </c>
-      <c r="L61" s="6" t="n">
+      <c r="L61" t="n">
         <v>11440</v>
       </c>
     </row>
-    <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="3" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>2026/05/20</t>
         </is>
       </c>
-      <c r="B62" s="4" t="n">
+      <c r="B62" t="n">
         <v>20</v>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>3位</t>
         </is>
       </c>
-      <c r="E62" s="15" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>宴会コース</t>
         </is>
       </c>
-      <c r="F62" s="6" t="n">
+      <c r="F62" t="n">
         <v>5000</v>
       </c>
-      <c r="G62" s="6" t="n">
+      <c r="G62" t="n">
         <v>3</v>
       </c>
-      <c r="H62" s="6" t="n">
+      <c r="H62" t="n">
         <v>15000</v>
       </c>
-      <c r="I62" s="15" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>オールフリー</t>
         </is>
       </c>
-      <c r="J62" s="6" t="n">
+      <c r="J62" t="n">
         <v>680</v>
       </c>
-      <c r="K62" s="6" t="n">
+      <c r="K62" t="n">
         <v>9</v>
       </c>
-      <c r="L62" s="6" t="n">
+      <c r="L62" t="n">
         <v>6120</v>
       </c>
     </row>
-    <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="7" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>2026/05/21</t>
         </is>
       </c>
-      <c r="B63" s="8" t="n">
+      <c r="B63" t="n">
         <v>21</v>
       </c>
-      <c r="C63" s="7" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="D63" s="7" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>1位</t>
         </is>
       </c>
-      <c r="E63" s="14" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>宴会コース</t>
         </is>
       </c>
-      <c r="F63" s="10" t="n">
+      <c r="F63" t="n">
         <v>5500</v>
       </c>
-      <c r="G63" s="10" t="n">
+      <c r="G63" t="n">
         <v>25</v>
       </c>
-      <c r="H63" s="10" t="n">
+      <c r="H63" t="n">
         <v>137500</v>
       </c>
-      <c r="I63" s="14" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>Freeウィスキー</t>
         </is>
       </c>
-      <c r="J63" s="10" t="n">
+      <c r="J63" t="n">
         <v>1500</v>
       </c>
-      <c r="K63" s="10" t="n">
+      <c r="K63" t="n">
         <v>62</v>
       </c>
-      <c r="L63" s="10" t="n">
+      <c r="L63" t="n">
         <v>93000</v>
       </c>
     </row>
-    <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="7" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>2026/05/21</t>
         </is>
       </c>
-      <c r="B64" s="8" t="n">
+      <c r="B64" t="n">
         <v>21</v>
       </c>
-      <c r="C64" s="7" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>2位</t>
         </is>
       </c>
-      <c r="E64" s="14" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>あさり膳ハーフ</t>
         </is>
       </c>
-      <c r="F64" s="10" t="n">
+      <c r="F64" t="n">
         <v>2500</v>
       </c>
-      <c r="G64" s="10" t="n">
+      <c r="G64" t="n">
         <v>34</v>
       </c>
-      <c r="H64" s="10" t="n">
+      <c r="H64" t="n">
         <v>85000</v>
       </c>
-      <c r="I64" s="14" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>飲み放題</t>
         </is>
       </c>
-      <c r="J64" s="10" t="n">
+      <c r="J64" t="n">
         <v>3500</v>
       </c>
-      <c r="K64" s="10" t="n">
+      <c r="K64" t="n">
         <v>25</v>
       </c>
-      <c r="L64" s="10" t="n">
+      <c r="L64" t="n">
         <v>87500</v>
       </c>
     </row>
-    <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="7" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>2026/05/21</t>
         </is>
       </c>
-      <c r="B65" s="8" t="n">
+      <c r="B65" t="n">
         <v>21</v>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>3位</t>
         </is>
       </c>
-      <c r="E65" s="14" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>季節の一品</t>
         </is>
       </c>
-      <c r="F65" s="10" t="n">
+      <c r="F65" t="n">
         <v>10000</v>
       </c>
-      <c r="G65" s="10" t="n">
+      <c r="G65" t="n">
         <v>3</v>
       </c>
-      <c r="H65" s="10" t="n">
+      <c r="H65" t="n">
         <v>30000</v>
       </c>
-      <c r="I65" s="14" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>ＦｒｅｅワインＢ</t>
         </is>
       </c>
-      <c r="J65" s="10" t="n">
+      <c r="J65" t="n">
         <v>55000</v>
       </c>
-      <c r="K65" s="10" t="n">
+      <c r="K65" t="n">
         <v>1</v>
       </c>
-      <c r="L65" s="10" t="n">
+      <c r="L65" t="n">
         <v>55000</v>
       </c>
     </row>
-    <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="3" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="B66" s="4" t="n">
+      <c r="B66" t="n">
         <v>22</v>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>1位</t>
         </is>
       </c>
-      <c r="E66" s="15" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>宴会コース</t>
         </is>
       </c>
-      <c r="F66" s="6" t="n">
+      <c r="F66" t="n">
         <v>8000</v>
       </c>
-      <c r="G66" s="6" t="n">
+      <c r="G66" t="n">
         <v>14</v>
       </c>
-      <c r="H66" s="6" t="n">
+      <c r="H66" t="n">
         <v>112000</v>
       </c>
-      <c r="I66" s="15" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>プレミアムモルツ中瓶</t>
         </is>
       </c>
-      <c r="J66" s="6" t="n">
+      <c r="J66" t="n">
         <v>980</v>
       </c>
-      <c r="K66" s="6" t="n">
+      <c r="K66" t="n">
         <v>30</v>
       </c>
-      <c r="L66" s="6" t="n">
+      <c r="L66" t="n">
         <v>29400</v>
       </c>
     </row>
-    <row r="67" ht="18" customHeight="1">
-      <c r="A67" s="3" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="B67" s="4" t="n">
+      <c r="B67" t="n">
         <v>22</v>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>2位</t>
         </is>
       </c>
-      <c r="E67" s="15" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>外販料理</t>
         </is>
       </c>
-      <c r="F67" s="6" t="n">
+      <c r="F67" t="n">
         <v>2000</v>
       </c>
-      <c r="G67" s="6" t="n">
+      <c r="G67" t="n">
         <v>37</v>
       </c>
-      <c r="H67" s="6" t="n">
+      <c r="H67" t="n">
         <v>74000</v>
       </c>
-      <c r="I67" s="15" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>吟辛1合</t>
         </is>
       </c>
-      <c r="J67" s="6" t="n">
+      <c r="J67" t="n">
         <v>950</v>
       </c>
-      <c r="K67" s="6" t="n">
+      <c r="K67" t="n">
         <v>17</v>
       </c>
-      <c r="L67" s="6" t="n">
+      <c r="L67" t="n">
         <v>16150</v>
       </c>
     </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="3" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="B68" s="4" t="n">
+      <c r="B68" t="n">
         <v>22</v>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>3位</t>
         </is>
       </c>
-      <c r="E68" s="15" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>宴会コース</t>
         </is>
       </c>
-      <c r="F68" s="6" t="n">
+      <c r="F68" t="n">
         <v>7000</v>
       </c>
-      <c r="G68" s="6" t="n">
+      <c r="G68" t="n">
         <v>8</v>
       </c>
-      <c r="H68" s="6" t="n">
+      <c r="H68" t="n">
         <v>56000</v>
       </c>
-      <c r="I68" s="15" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>吉四六ボトル</t>
         </is>
       </c>
-      <c r="J68" s="6" t="n">
+      <c r="J68" t="n">
         <v>7980</v>
       </c>
-      <c r="K68" s="6" t="n">
+      <c r="K68" t="n">
         <v>2</v>
       </c>
-      <c r="L68" s="6" t="n">
+      <c r="L68" t="n">
         <v>15960</v>
       </c>
     </row>
-    <row r="69" ht="18" customHeight="1">
-      <c r="A69" s="7" t="inlineStr">
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>2026/05/23</t>
         </is>
       </c>
-      <c r="B69" s="8" t="n">
+      <c r="B69" t="n">
         <v>23</v>
       </c>
-      <c r="C69" s="7" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>土</t>
         </is>
       </c>
-      <c r="D69" s="7" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>1位</t>
         </is>
       </c>
-      <c r="E69" s="14" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>宴会コース</t>
         </is>
       </c>
-      <c r="F69" s="10" t="n">
+      <c r="F69" t="n">
         <v>5000</v>
       </c>
-      <c r="G69" s="10" t="n">
+      <c r="G69" t="n">
         <v>31</v>
       </c>
-      <c r="H69" s="10" t="n">
+      <c r="H69" t="n">
         <v>155000</v>
       </c>
-      <c r="I69" s="14" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>プレミアムモルツ生</t>
         </is>
       </c>
-      <c r="J69" s="10" t="n">
+      <c r="J69" t="n">
         <v>880</v>
       </c>
-      <c r="K69" s="10" t="n">
+      <c r="K69" t="n">
         <v>37</v>
       </c>
-      <c r="L69" s="10" t="n">
+      <c r="L69" t="n">
         <v>32560</v>
       </c>
     </row>
-    <row r="70" ht="18" customHeight="1">
-      <c r="A70" s="7" t="inlineStr">
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>2026/05/23</t>
         </is>
       </c>
-      <c r="B70" s="8" t="n">
+      <c r="B70" t="n">
         <v>23</v>
       </c>
-      <c r="C70" s="7" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>土</t>
         </is>
       </c>
-      <c r="D70" s="7" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>2位</t>
         </is>
       </c>
-      <c r="E70" s="14" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>あさり膳ハーフ</t>
         </is>
       </c>
-      <c r="F70" s="10" t="n">
+      <c r="F70" t="n">
         <v>2500</v>
       </c>
-      <c r="G70" s="10" t="n">
+      <c r="G70" t="n">
         <v>24</v>
       </c>
-      <c r="H70" s="10" t="n">
+      <c r="H70" t="n">
         <v>60000</v>
       </c>
-      <c r="I70" s="14" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>オールフリー</t>
         </is>
       </c>
-      <c r="J70" s="10" t="n">
+      <c r="J70" t="n">
         <v>680</v>
       </c>
-      <c r="K70" s="10" t="n">
+      <c r="K70" t="n">
         <v>27</v>
       </c>
-      <c r="L70" s="10" t="n">
+      <c r="L70" t="n">
         <v>18360</v>
       </c>
     </row>
-    <row r="71" ht="18" customHeight="1">
-      <c r="A71" s="7" t="inlineStr">
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>2026/05/23</t>
         </is>
       </c>
-      <c r="B71" s="8" t="n">
+      <c r="B71" t="n">
         <v>23</v>
       </c>
-      <c r="C71" s="7" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>土</t>
         </is>
       </c>
-      <c r="D71" s="7" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>3位</t>
         </is>
       </c>
-      <c r="E71" s="14" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>宝家膳</t>
         </is>
       </c>
-      <c r="F71" s="10" t="n">
+      <c r="F71" t="n">
         <v>5000</v>
       </c>
-      <c r="G71" s="10" t="n">
+      <c r="G71" t="n">
         <v>12</v>
       </c>
-      <c r="H71" s="10" t="n">
+      <c r="H71" t="n">
         <v>60000</v>
       </c>
-      <c r="I71" s="14" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>ＦｒｅｅワインＢ</t>
         </is>
       </c>
-      <c r="J71" s="10" t="n">
+      <c r="J71" t="n">
         <v>12800</v>
       </c>
-      <c r="K71" s="10" t="n">
+      <c r="K71" t="n">
         <v>1</v>
       </c>
-      <c r="L71" s="10" t="n">
+      <c r="L71" t="n">
         <v>12800</v>
       </c>
     </row>
-    <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="3" t="inlineStr">
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>2026/05/24</t>
         </is>
       </c>
-      <c r="B72" s="4" t="n">
+      <c r="B72" t="n">
         <v>24</v>
       </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>1位</t>
         </is>
       </c>
-      <c r="E72" s="15" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>宴会コース</t>
         </is>
       </c>
-      <c r="F72" s="6" t="n">
+      <c r="F72" t="n">
         <v>6000</v>
       </c>
-      <c r="G72" s="6" t="n">
+      <c r="G72" t="n">
         <v>18</v>
       </c>
-      <c r="H72" s="6" t="n">
+      <c r="H72" t="n">
         <v>108000</v>
       </c>
-      <c r="I72" s="15" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>プレミアムモルツ生</t>
         </is>
       </c>
-      <c r="J72" s="6" t="n">
+      <c r="J72" t="n">
         <v>880</v>
       </c>
-      <c r="K72" s="6" t="n">
+      <c r="K72" t="n">
         <v>37</v>
       </c>
-      <c r="L72" s="6" t="n">
+      <c r="L72" t="n">
         <v>32560</v>
       </c>
     </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="A73" s="3" t="inlineStr">
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>2026/05/24</t>
         </is>
       </c>
-      <c r="B73" s="4" t="n">
+      <c r="B73" t="n">
         <v>24</v>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>2位</t>
         </is>
       </c>
-      <c r="E73" s="15" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>あさり膳刺身</t>
         </is>
       </c>
-      <c r="F73" s="6" t="n">
+      <c r="F73" t="n">
         <v>2400</v>
       </c>
-      <c r="G73" s="6" t="n">
+      <c r="G73" t="n">
         <v>34</v>
       </c>
-      <c r="H73" s="6" t="n">
+      <c r="H73" t="n">
         <v>81600</v>
       </c>
-      <c r="I73" s="15" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>プレミアムモルツ中瓶</t>
         </is>
       </c>
-      <c r="J73" s="6" t="n">
+      <c r="J73" t="n">
         <v>980</v>
       </c>
-      <c r="K73" s="6" t="n">
+      <c r="K73" t="n">
         <v>15</v>
       </c>
-      <c r="L73" s="6" t="n">
+      <c r="L73" t="n">
         <v>14700</v>
       </c>
     </row>
-    <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="3" t="inlineStr">
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>2026/05/24</t>
         </is>
       </c>
-      <c r="B74" s="4" t="n">
+      <c r="B74" t="n">
         <v>24</v>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="D74" s="3" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>3位</t>
         </is>
       </c>
-      <c r="E74" s="15" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>宴会コース</t>
         </is>
       </c>
-      <c r="F74" s="6" t="n">
+      <c r="F74" t="n">
         <v>19000</v>
       </c>
-      <c r="G74" s="6" t="n">
+      <c r="G74" t="n">
         <v>4</v>
       </c>
-      <c r="H74" s="6" t="n">
+      <c r="H74" t="n">
         <v>76000</v>
       </c>
-      <c r="I74" s="15" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>ウーロン茶</t>
         </is>
       </c>
-      <c r="J74" s="6" t="n">
+      <c r="J74" t="n">
         <v>400</v>
       </c>
-      <c r="K74" s="6" t="n">
+      <c r="K74" t="n">
         <v>21</v>
       </c>
-      <c r="L74" s="6" t="n">
+      <c r="L74" t="n">
         <v>8400</v>
       </c>
     </row>
-    <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="7" t="inlineStr">
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>2026/05/25</t>
         </is>
       </c>
-      <c r="B75" s="8" t="n">
+      <c r="B75" t="n">
         <v>25</v>
       </c>
-      <c r="C75" s="7" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="D75" s="7" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>1位</t>
         </is>
       </c>
-      <c r="E75" s="14" t="inlineStr"/>
-      <c r="F75" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" s="14" t="inlineStr"/>
-      <c r="J75" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" ht="18" customHeight="1">
-      <c r="A76" s="7" t="inlineStr">
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>2026/05/25</t>
         </is>
       </c>
-      <c r="B76" s="8" t="n">
+      <c r="B76" t="n">
         <v>25</v>
       </c>
-      <c r="C76" s="7" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="D76" s="7" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>2位</t>
         </is>
       </c>
-      <c r="E76" s="14" t="inlineStr"/>
-      <c r="F76" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" s="14" t="inlineStr"/>
-      <c r="J76" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="A77" s="7" t="inlineStr">
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>2026/05/25</t>
         </is>
       </c>
-      <c r="B77" s="8" t="n">
+      <c r="B77" t="n">
         <v>25</v>
       </c>
-      <c r="C77" s="7" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="D77" s="7" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>3位</t>
         </is>
       </c>
-      <c r="E77" s="14" t="inlineStr"/>
-      <c r="F77" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" s="14" t="inlineStr"/>
-      <c r="J77" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="3" t="inlineStr">
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>2026/05/26</t>
         </is>
       </c>
-      <c r="B78" s="4" t="n">
+      <c r="B78" t="n">
         <v>26</v>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>1位</t>
         </is>
       </c>
-      <c r="E78" s="15" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>あさり膳ハーフ</t>
         </is>
       </c>
-      <c r="F78" s="6" t="n">
+      <c r="F78" t="n">
         <v>2500</v>
       </c>
-      <c r="G78" s="6" t="n">
+      <c r="G78" t="n">
         <v>32</v>
       </c>
-      <c r="H78" s="6" t="n">
+      <c r="H78" t="n">
         <v>80000</v>
       </c>
-      <c r="I78" s="15" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>プレミアムモルツ生</t>
         </is>
       </c>
-      <c r="J78" s="6" t="n">
+      <c r="J78" t="n">
         <v>880</v>
       </c>
-      <c r="K78" s="6" t="n">
+      <c r="K78" t="n">
         <v>16</v>
       </c>
-      <c r="L78" s="6" t="n">
+      <c r="L78" t="n">
         <v>14080</v>
       </c>
     </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="3" t="inlineStr">
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>2026/05/26</t>
         </is>
       </c>
-      <c r="B79" s="4" t="n">
+      <c r="B79" t="n">
         <v>26</v>
       </c>
-      <c r="C79" s="3" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="D79" s="3" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>2位</t>
         </is>
       </c>
-      <c r="E79" s="15" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>宴会コース</t>
         </is>
       </c>
-      <c r="F79" s="6" t="n">
+      <c r="F79" t="n">
         <v>5000</v>
       </c>
-      <c r="G79" s="6" t="n">
+      <c r="G79" t="n">
         <v>14</v>
       </c>
-      <c r="H79" s="6" t="n">
+      <c r="H79" t="n">
         <v>70000</v>
       </c>
-      <c r="I79" s="15" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>プレミアムモルツ中瓶</t>
         </is>
       </c>
-      <c r="J79" s="6" t="n">
+      <c r="J79" t="n">
         <v>980</v>
       </c>
-      <c r="K79" s="6" t="n">
+      <c r="K79" t="n">
         <v>9</v>
       </c>
-      <c r="L79" s="6" t="n">
+      <c r="L79" t="n">
         <v>8820</v>
       </c>
     </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="3" t="inlineStr">
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>2026/05/26</t>
         </is>
       </c>
-      <c r="B80" s="4" t="n">
+      <c r="B80" t="n">
         <v>26</v>
       </c>
-      <c r="C80" s="3" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="D80" s="3" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>3位</t>
         </is>
       </c>
-      <c r="E80" s="15" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>宴会コース</t>
         </is>
       </c>
-      <c r="F80" s="6" t="n">
+      <c r="F80" t="n">
         <v>5200</v>
       </c>
-      <c r="G80" s="6" t="n">
+      <c r="G80" t="n">
         <v>12</v>
       </c>
-      <c r="H80" s="6" t="n">
+      <c r="H80" t="n">
         <v>62400</v>
       </c>
-      <c r="I80" s="15" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>角ハイボール</t>
         </is>
       </c>
-      <c r="J80" s="6" t="n">
+      <c r="J80" t="n">
         <v>680</v>
       </c>
-      <c r="K80" s="6" t="n">
+      <c r="K80" t="n">
         <v>8</v>
       </c>
-      <c r="L80" s="6" t="n">
+      <c r="L80" t="n">
         <v>5440</v>
       </c>
     </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="7" t="inlineStr">
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>2026/05/27</t>
         </is>
       </c>
-      <c r="B81" s="8" t="n">
+      <c r="B81" t="n">
         <v>27</v>
       </c>
-      <c r="C81" s="7" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="D81" s="7" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>1位</t>
         </is>
       </c>
-      <c r="E81" s="14" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>宴会コース</t>
         </is>
       </c>
-      <c r="F81" s="10" t="n">
+      <c r="F81" t="n">
         <v>7000</v>
       </c>
-      <c r="G81" s="10" t="n">
+      <c r="G81" t="n">
         <v>14</v>
       </c>
-      <c r="H81" s="10" t="n">
+      <c r="H81" t="n">
         <v>98000</v>
       </c>
-      <c r="I81" s="14" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>飲み放題</t>
         </is>
       </c>
-      <c r="J81" s="10" t="n">
+      <c r="J81" t="n">
         <v>3500</v>
       </c>
-      <c r="K81" s="10" t="n">
+      <c r="K81" t="n">
         <v>14</v>
       </c>
-      <c r="L81" s="10" t="n">
+      <c r="L81" t="n">
         <v>49000</v>
       </c>
     </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="A82" s="7" t="inlineStr">
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>2026/05/27</t>
         </is>
       </c>
-      <c r="B82" s="8" t="n">
+      <c r="B82" t="n">
         <v>27</v>
       </c>
-      <c r="C82" s="7" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="D82" s="7" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>2位</t>
         </is>
       </c>
-      <c r="E82" s="14" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>特選牛の網や焼き膳</t>
         </is>
       </c>
-      <c r="F82" s="10" t="n">
+      <c r="F82" t="n">
         <v>2700</v>
       </c>
-      <c r="G82" s="10" t="n">
+      <c r="G82" t="n">
         <v>20</v>
       </c>
-      <c r="H82" s="10" t="n">
+      <c r="H82" t="n">
         <v>54000</v>
       </c>
-      <c r="I82" s="14" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>プレミアムモルツ中瓶</t>
         </is>
       </c>
-      <c r="J82" s="10" t="n">
+      <c r="J82" t="n">
         <v>980</v>
       </c>
-      <c r="K82" s="10" t="n">
+      <c r="K82" t="n">
         <v>22</v>
       </c>
-      <c r="L82" s="10" t="n">
+      <c r="L82" t="n">
         <v>21560</v>
       </c>
     </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="A83" s="7" t="inlineStr">
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t>2026/05/27</t>
         </is>
       </c>
-      <c r="B83" s="8" t="n">
+      <c r="B83" t="n">
         <v>27</v>
       </c>
-      <c r="C83" s="7" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="D83" s="7" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>3位</t>
         </is>
       </c>
-      <c r="E83" s="14" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>あさり膳ハーフ</t>
         </is>
       </c>
-      <c r="F83" s="10" t="n">
+      <c r="F83" t="n">
         <v>2500</v>
       </c>
-      <c r="G83" s="10" t="n">
+      <c r="G83" t="n">
         <v>18</v>
       </c>
-      <c r="H83" s="10" t="n">
+      <c r="H83" t="n">
         <v>45000</v>
       </c>
-      <c r="I83" s="14" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>プレミアムモルツ生</t>
         </is>
       </c>
-      <c r="J83" s="10" t="n">
+      <c r="J83" t="n">
         <v>880</v>
       </c>
-      <c r="K83" s="10" t="n">
+      <c r="K83" t="n">
         <v>11</v>
       </c>
-      <c r="L83" s="10" t="n">
+      <c r="L83" t="n">
         <v>9680</v>
       </c>
     </row>
-    <row r="84" ht="18" customHeight="1">
-      <c r="A84" s="3" t="inlineStr">
+    <row r="84">
+      <c r="A84" t="inlineStr">
         <is>
           <t>2026/05/28</t>
         </is>
       </c>
-      <c r="B84" s="4" t="n">
+      <c r="B84" t="n">
         <v>28</v>
       </c>
-      <c r="C84" s="3" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="D84" s="3" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>1位</t>
         </is>
       </c>
-      <c r="E84" s="15" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>宴会コース</t>
         </is>
       </c>
-      <c r="F84" s="6" t="n">
+      <c r="F84" t="n">
         <v>5000</v>
       </c>
-      <c r="G84" s="6" t="n">
+      <c r="G84" t="n">
         <v>18</v>
       </c>
-      <c r="H84" s="6" t="n">
+      <c r="H84" t="n">
         <v>90000</v>
       </c>
-      <c r="I84" s="15" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>飲み放題</t>
         </is>
       </c>
-      <c r="J84" s="6" t="n">
+      <c r="J84" t="n">
         <v>3000</v>
       </c>
-      <c r="K84" s="6" t="n">
+      <c r="K84" t="n">
         <v>18</v>
       </c>
-      <c r="L84" s="6" t="n">
+      <c r="L84" t="n">
         <v>54000</v>
       </c>
     </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="A85" s="3" t="inlineStr">
+    <row r="85">
+      <c r="A85" t="inlineStr">
         <is>
           <t>2026/05/28</t>
         </is>
       </c>
-      <c r="B85" s="4" t="n">
+      <c r="B85" t="n">
         <v>28</v>
       </c>
-      <c r="C85" s="3" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="D85" s="3" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>2位</t>
         </is>
       </c>
-      <c r="E85" s="15" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>玉代</t>
         </is>
       </c>
-      <c r="F85" s="6" t="n">
+      <c r="F85" t="n">
         <v>14000</v>
       </c>
-      <c r="G85" s="6" t="n">
+      <c r="G85" t="n">
         <v>5</v>
       </c>
-      <c r="H85" s="6" t="n">
+      <c r="H85" t="n">
         <v>70000</v>
       </c>
-      <c r="I85" s="15" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>プレミアムモルツ中瓶</t>
         </is>
       </c>
-      <c r="J85" s="6" t="n">
+      <c r="J85" t="n">
         <v>980</v>
       </c>
-      <c r="K85" s="6" t="n">
+      <c r="K85" t="n">
         <v>7</v>
       </c>
-      <c r="L85" s="6" t="n">
+      <c r="L85" t="n">
         <v>6860</v>
       </c>
     </row>
-    <row r="86" ht="18" customHeight="1">
-      <c r="A86" s="3" t="inlineStr">
+    <row r="86">
+      <c r="A86" t="inlineStr">
         <is>
           <t>2026/05/28</t>
         </is>
       </c>
-      <c r="B86" s="4" t="n">
+      <c r="B86" t="n">
         <v>28</v>
       </c>
-      <c r="C86" s="3" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="D86" s="3" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>3位</t>
         </is>
       </c>
-      <c r="E86" s="15" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>あさり膳ハーフ</t>
         </is>
       </c>
-      <c r="F86" s="6" t="n">
+      <c r="F86" t="n">
         <v>2500</v>
       </c>
-      <c r="G86" s="6" t="n">
+      <c r="G86" t="n">
         <v>13</v>
       </c>
-      <c r="H86" s="6" t="n">
+      <c r="H86" t="n">
         <v>32500</v>
       </c>
-      <c r="I86" s="15" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>グールガゾーｼｬﾙﾄﾞﾈ</t>
         </is>
       </c>
-      <c r="J86" s="6" t="n">
+      <c r="J86" t="n">
         <v>5800</v>
       </c>
-      <c r="K86" s="6" t="n">
+      <c r="K86" t="n">
         <v>1</v>
       </c>
-      <c r="L86" s="6" t="n">
+      <c r="L86" t="n">
         <v>5800</v>
       </c>
     </row>
-    <row r="87" ht="18" customHeight="1">
-      <c r="A87" s="7" t="inlineStr">
+    <row r="87">
+      <c r="A87" t="inlineStr">
         <is>
           <t>2026/05/29</t>
         </is>
       </c>
-      <c r="B87" s="8" t="n">
+      <c r="B87" t="n">
         <v>29</v>
       </c>
-      <c r="C87" s="7" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>1位</t>
         </is>
       </c>
-      <c r="E87" s="14" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>宴会コース</t>
         </is>
       </c>
-      <c r="F87" s="10" t="n">
+      <c r="F87" t="n">
         <v>15000</v>
       </c>
-      <c r="G87" s="10" t="n">
+      <c r="G87" t="n">
         <v>12</v>
       </c>
-      <c r="H87" s="10" t="n">
+      <c r="H87" t="n">
         <v>180000</v>
       </c>
-      <c r="I87" s="14" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>飲み放題</t>
         </is>
       </c>
-      <c r="J87" s="10" t="n">
+      <c r="J87" t="n">
         <v>3000</v>
       </c>
-      <c r="K87" s="10" t="n">
+      <c r="K87" t="n">
         <v>50</v>
       </c>
-      <c r="L87" s="10" t="n">
+      <c r="L87" t="n">
         <v>150000</v>
       </c>
     </row>
-    <row r="88" ht="18" customHeight="1">
-      <c r="A88" s="7" t="inlineStr">
+    <row r="88">
+      <c r="A88" t="inlineStr">
         <is>
           <t>2026/05/29</t>
         </is>
       </c>
-      <c r="B88" s="8" t="n">
+      <c r="B88" t="n">
         <v>29</v>
       </c>
-      <c r="C88" s="7" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="D88" s="7" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>2位</t>
         </is>
       </c>
-      <c r="E88" s="14" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>あさり膳ハーフ</t>
         </is>
       </c>
-      <c r="F88" s="10" t="n">
+      <c r="F88" t="n">
         <v>2500</v>
       </c>
-      <c r="G88" s="10" t="n">
+      <c r="G88" t="n">
         <v>57</v>
       </c>
-      <c r="H88" s="10" t="n">
+      <c r="H88" t="n">
         <v>142500</v>
       </c>
-      <c r="I88" s="14" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>ﾍﾞﾘﾝｼﾞｼﾞｬｰｼｬﾙﾄﾞﾈ</t>
         </is>
       </c>
-      <c r="J88" s="10" t="n">
+      <c r="J88" t="n">
         <v>9800</v>
       </c>
-      <c r="K88" s="10" t="n">
+      <c r="K88" t="n">
         <v>1</v>
       </c>
-      <c r="L88" s="10" t="n">
+      <c r="L88" t="n">
         <v>9800</v>
       </c>
     </row>
-    <row r="89" ht="18" customHeight="1">
-      <c r="A89" s="7" t="inlineStr">
+    <row r="89">
+      <c r="A89" t="inlineStr">
         <is>
           <t>2026/05/29</t>
         </is>
       </c>
-      <c r="B89" s="8" t="n">
+      <c r="B89" t="n">
         <v>29</v>
       </c>
-      <c r="C89" s="7" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="D89" s="7" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>3位</t>
         </is>
       </c>
-      <c r="E89" s="14" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>宴会コース</t>
         </is>
       </c>
-      <c r="F89" s="10" t="n">
+      <c r="F89" t="n">
         <v>6000</v>
       </c>
-      <c r="G89" s="10" t="n">
+      <c r="G89" t="n">
         <v>21</v>
       </c>
-      <c r="H89" s="10" t="n">
+      <c r="H89" t="n">
         <v>126000</v>
       </c>
-      <c r="I89" s="14" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>プレミアムモルツ生</t>
         </is>
       </c>
-      <c r="J89" s="10" t="n">
+      <c r="J89" t="n">
         <v>880</v>
       </c>
-      <c r="K89" s="10" t="n">
+      <c r="K89" t="n">
         <v>10</v>
       </c>
-      <c r="L89" s="10" t="n">
+      <c r="L89" t="n">
         <v>8800</v>
       </c>
     </row>
-    <row r="90" ht="18" customHeight="1">
-      <c r="A90" s="3" t="inlineStr">
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t>2026/05/30</t>
         </is>
       </c>
-      <c r="B90" s="4" t="n">
+      <c r="B90" t="n">
         <v>30</v>
       </c>
-      <c r="C90" s="3" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>土</t>
         </is>
       </c>
-      <c r="D90" s="3" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>1位</t>
         </is>
       </c>
-      <c r="E90" s="15" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>宴会コース</t>
         </is>
       </c>
-      <c r="F90" s="6" t="n">
+      <c r="F90" t="n">
         <v>11500</v>
       </c>
-      <c r="G90" s="6" t="n">
+      <c r="G90" t="n">
         <v>6</v>
       </c>
-      <c r="H90" s="6" t="n">
+      <c r="H90" t="n">
         <v>69000</v>
       </c>
-      <c r="I90" s="15" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>プレミアムモルツ生</t>
         </is>
       </c>
-      <c r="J90" s="6" t="n">
+      <c r="J90" t="n">
         <v>880</v>
       </c>
-      <c r="K90" s="6" t="n">
+      <c r="K90" t="n">
         <v>33</v>
       </c>
-      <c r="L90" s="6" t="n">
+      <c r="L90" t="n">
         <v>29040</v>
       </c>
     </row>
-    <row r="91" ht="18" customHeight="1">
-      <c r="A91" s="3" t="inlineStr">
+    <row r="91">
+      <c r="A91" t="inlineStr">
         <is>
           <t>2026/05/30</t>
         </is>
       </c>
-      <c r="B91" s="4" t="n">
+      <c r="B91" t="n">
         <v>30</v>
       </c>
-      <c r="C91" s="3" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>土</t>
         </is>
       </c>
-      <c r="D91" s="3" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>2位</t>
         </is>
       </c>
-      <c r="E91" s="15" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>季節の一品</t>
         </is>
       </c>
-      <c r="F91" s="6" t="n">
+      <c r="F91" t="n">
         <v>1780</v>
       </c>
-      <c r="G91" s="6" t="n">
+      <c r="G91" t="n">
         <v>36</v>
       </c>
-      <c r="H91" s="6" t="n">
+      <c r="H91" t="n">
         <v>64080</v>
       </c>
-      <c r="I91" s="15" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t>ウーロン茶</t>
         </is>
       </c>
-      <c r="J91" s="6" t="n">
+      <c r="J91" t="n">
         <v>400</v>
       </c>
-      <c r="K91" s="6" t="n">
+      <c r="K91" t="n">
         <v>32</v>
       </c>
-      <c r="L91" s="6" t="n">
+      <c r="L91" t="n">
         <v>12800</v>
       </c>
     </row>
-    <row r="92" ht="18" customHeight="1">
-      <c r="A92" s="3" t="inlineStr">
+    <row r="92">
+      <c r="A92" t="inlineStr">
         <is>
           <t>2026/05/30</t>
         </is>
       </c>
-      <c r="B92" s="4" t="n">
+      <c r="B92" t="n">
         <v>30</v>
       </c>
-      <c r="C92" s="3" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>土</t>
         </is>
       </c>
-      <c r="D92" s="3" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>3位</t>
         </is>
       </c>
-      <c r="E92" s="15" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>宝家膳上</t>
         </is>
       </c>
-      <c r="F92" s="6" t="n">
+      <c r="F92" t="n">
         <v>6500</v>
       </c>
-      <c r="G92" s="6" t="n">
+      <c r="G92" t="n">
         <v>9</v>
       </c>
-      <c r="H92" s="6" t="n">
+      <c r="H92" t="n">
         <v>58500</v>
       </c>
-      <c r="I92" s="15" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t>プレミアムモルツ中瓶</t>
         </is>
       </c>
-      <c r="J92" s="6" t="n">
+      <c r="J92" t="n">
         <v>980</v>
       </c>
-      <c r="K92" s="6" t="n">
+      <c r="K92" t="n">
         <v>11</v>
       </c>
-      <c r="L92" s="6" t="n">
+      <c r="L92" t="n">
         <v>10780</v>
       </c>
     </row>
-    <row r="93" ht="18" customHeight="1">
-      <c r="A93" s="7" t="inlineStr">
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t>2026/05/31</t>
         </is>
       </c>
-      <c r="B93" s="8" t="n">
+      <c r="B93" t="n">
         <v>31</v>
       </c>
-      <c r="C93" s="7" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="D93" s="7" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>1位</t>
         </is>
       </c>
-      <c r="E93" s="14" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>宴会コース</t>
         </is>
       </c>
-      <c r="F93" s="10" t="n">
+      <c r="F93" t="n">
         <v>500</v>
       </c>
-      <c r="G93" s="10" t="n">
+      <c r="G93" t="n">
         <v>21</v>
       </c>
-      <c r="H93" s="10" t="n">
+      <c r="H93" t="n">
         <v>10500</v>
       </c>
-      <c r="I93" s="14" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t>プレミアムモルツ生</t>
         </is>
       </c>
-      <c r="J93" s="10" t="n">
+      <c r="J93" t="n">
         <v>880</v>
       </c>
-      <c r="K93" s="10" t="n">
+      <c r="K93" t="n">
         <v>31</v>
       </c>
-      <c r="L93" s="10" t="n">
+      <c r="L93" t="n">
         <v>27280</v>
       </c>
     </row>
-    <row r="94" ht="18" customHeight="1">
-      <c r="A94" s="7" t="inlineStr">
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t>2026/05/31</t>
         </is>
       </c>
-      <c r="B94" s="8" t="n">
+      <c r="B94" t="n">
         <v>31</v>
       </c>
-      <c r="C94" s="7" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="D94" s="7" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>2位</t>
         </is>
       </c>
-      <c r="E94" s="14" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>あさり膳刺身</t>
         </is>
       </c>
-      <c r="F94" s="10" t="n">
+      <c r="F94" t="n">
         <v>2400</v>
       </c>
-      <c r="G94" s="10" t="n">
+      <c r="G94" t="n">
         <v>30</v>
       </c>
-      <c r="H94" s="10" t="n">
+      <c r="H94" t="n">
         <v>72000</v>
       </c>
-      <c r="I94" s="14" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t>角ハイボール</t>
         </is>
       </c>
-      <c r="J94" s="10" t="n">
+      <c r="J94" t="n">
         <v>680</v>
       </c>
-      <c r="K94" s="10" t="n">
+      <c r="K94" t="n">
         <v>18</v>
       </c>
-      <c r="L94" s="10" t="n">
+      <c r="L94" t="n">
         <v>12240</v>
       </c>
     </row>
-    <row r="95" ht="18" customHeight="1">
-      <c r="A95" s="7" t="inlineStr">
+    <row r="95">
+      <c r="A95" t="inlineStr">
         <is>
           <t>2026/05/31</t>
         </is>
       </c>
-      <c r="B95" s="8" t="n">
+      <c r="B95" t="n">
         <v>31</v>
       </c>
-      <c r="C95" s="7" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="D95" s="7" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>3位</t>
         </is>
       </c>
-      <c r="E95" s="14" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>宴会コース</t>
         </is>
       </c>
-      <c r="F95" s="10" t="n">
+      <c r="F95" t="n">
         <v>4500</v>
       </c>
-      <c r="G95" s="10" t="n">
+      <c r="G95" t="n">
         <v>10</v>
       </c>
-      <c r="H95" s="10" t="n">
+      <c r="H95" t="n">
         <v>45000</v>
       </c>
-      <c r="I95" s="14" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t>ウーロン茶</t>
         </is>
       </c>
-      <c r="J95" s="10" t="n">
+      <c r="J95" t="n">
         <v>400</v>
       </c>
-      <c r="K95" s="10" t="n">
+      <c r="K95" t="n">
         <v>15</v>
       </c>
-      <c r="L95" s="10" t="n">
+      <c r="L95" t="n">
         <v>6000</v>
       </c>
     </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>合 計</t>
-        </is>
-      </c>
-      <c r="E96" s="12" t="n"/>
-      <c r="F96" s="12" t="n"/>
-      <c r="G96" s="11" t="n">
-        <v>1517</v>
-      </c>
-      <c r="H96" s="11" t="n">
-        <v>6023660</v>
-      </c>
-      <c r="I96" s="12" t="n"/>
-      <c r="J96" s="12" t="n"/>
-      <c r="K96" s="11" t="n">
-        <v>1310</v>
-      </c>
-      <c r="L96" s="11" t="n">
-        <v>1703750</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="I1:L1"/>
-    <mergeCell ref="A96:D96"/>
-    <mergeCell ref="E1:H1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/frontend/public/data/daily_2026_5.xlsx
+++ b/frontend/public/data/daily_2026_5.xlsx
@@ -600,10 +600,10 @@
         <v>52653</v>
       </c>
       <c r="U3" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="V3" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="W3" t="n">
         <v>146538</v>
@@ -1554,10 +1554,10 @@
         <v>81283</v>
       </c>
       <c r="U17" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="V17" t="n">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="W17" t="n">
         <v>106190</v>
@@ -2021,10 +2021,10 @@
         <v>307201</v>
       </c>
       <c r="U24" t="n">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="V24" t="n">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="W24" t="n">
         <v>369696</v>
